--- a/CCGX-Modbus-TCP-register-list.xlsx
+++ b/CCGX-Modbus-TCP-register-list.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4822" uniqueCount="1311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4822" uniqueCount="1310">
   <si>
     <t xml:space="preserve">NOTE: Use unit-id 100 for the com.victronenergy.system data, for more information see FAQ.</t>
   </si>
@@ -2274,10 +2274,7 @@
     <t xml:space="preserve">ESS Mode 2 – Same as 2700, but with a different scale factor. Meant for values larger than +-32kW.</t>
   </si>
   <si>
-    <t xml:space="preserve">ESS max discharge current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 to 655350</t>
+    <t xml:space="preserve">ESS max discharge power</t>
   </si>
   <si>
     <t xml:space="preserve">/Settings/Cgwacs/MaxDischargePower</t>
@@ -14432,7 +14429,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
         <v>738</v>
       </c>
@@ -14443,16 +14440,16 @@
         <v>2704</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E336" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="F336" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="G336" s="1" t="s">
         <v>751</v>
-      </c>
-      <c r="G336" s="1" t="s">
-        <v>752</v>
       </c>
       <c r="H336" s="1" t="s">
         <v>23</v>
@@ -14461,7 +14458,7 @@
         <v>31</v>
       </c>
       <c r="J336" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14469,7 +14466,7 @@
         <v>738</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C337" s="1" t="n">
         <v>2705</v>
@@ -14484,7 +14481,7 @@
         <v>60</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H337" s="1" t="s">
         <v>23</v>
@@ -14493,7 +14490,7 @@
         <v>87</v>
       </c>
       <c r="J337" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14501,7 +14498,7 @@
         <v>738</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C338" s="1" t="n">
         <v>2706</v>
@@ -14516,7 +14513,7 @@
         <v>748</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H338" s="1" t="s">
         <v>23</v>
@@ -14525,7 +14522,7 @@
         <v>31</v>
       </c>
       <c r="J338" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14533,7 +14530,7 @@
         <v>738</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C339" s="1" t="n">
         <v>2707</v>
@@ -14545,16 +14542,16 @@
         <v>1</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H339" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I339" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="J339" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="J339" s="1" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14562,7 +14559,7 @@
         <v>738</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C340" s="1" t="n">
         <v>2708</v>
@@ -14574,24 +14571,24 @@
         <v>1</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H340" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I340" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="J340" s="1" t="s">
         <v>766</v>
-      </c>
-      <c r="J340" s="1" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>768</v>
-      </c>
-      <c r="B341" s="1" t="s">
-        <v>769</v>
       </c>
       <c r="C341" s="1" t="n">
         <v>2709</v>
@@ -14603,16 +14600,16 @@
         <v>1</v>
       </c>
       <c r="G341" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="H341" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I341" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="H341" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I341" s="1" t="s">
+      <c r="J341" s="1" t="s">
         <v>771</v>
-      </c>
-      <c r="J341" s="1" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14620,7 +14617,7 @@
         <v>738</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C342" s="1" t="n">
         <v>2710</v>
@@ -14635,7 +14632,7 @@
         <v>80</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H342" s="1" t="s">
         <v>23</v>
@@ -14644,7 +14641,7 @@
         <v>82</v>
       </c>
       <c r="J342" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14652,7 +14649,7 @@
         <v>738</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C343" s="1" t="n">
         <v>2711</v>
@@ -14667,16 +14664,16 @@
         <v>233</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H343" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I343" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="J343" s="1" t="s">
         <v>778</v>
-      </c>
-      <c r="J343" s="1" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14684,7 +14681,7 @@
         <v>738</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C344" s="1" t="n">
         <v>2712</v>
@@ -14699,21 +14696,21 @@
         <v>233</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H344" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>782</v>
-      </c>
-      <c r="B345" s="1" t="s">
-        <v>783</v>
       </c>
       <c r="C345" s="1" t="n">
         <v>2800</v>
@@ -14725,24 +14722,24 @@
         <v>10000000</v>
       </c>
       <c r="F345" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="G345" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="G345" s="1" t="s">
+      <c r="H345" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I345" s="1" t="s">
         <v>785</v>
-      </c>
-      <c r="H345" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I345" s="1" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C346" s="1" t="n">
         <v>2802</v>
@@ -14754,24 +14751,24 @@
         <v>10000000</v>
       </c>
       <c r="F346" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H346" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I346" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C347" s="1" t="n">
         <v>2804</v>
@@ -14786,24 +14783,24 @@
         <v>186</v>
       </c>
       <c r="G347" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="H347" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I347" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="H347" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I347" s="1" t="s">
+      <c r="J347" s="1" t="s">
         <v>791</v>
-      </c>
-      <c r="J347" s="1" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C348" s="1" t="n">
         <v>2805</v>
@@ -14818,24 +14815,24 @@
         <v>186</v>
       </c>
       <c r="G348" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="H348" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I348" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="H348" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I348" s="1" t="s">
+      <c r="J348" s="1" t="s">
         <v>795</v>
-      </c>
-      <c r="J348" s="1" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C349" s="1" t="n">
         <v>2806</v>
@@ -14850,21 +14847,21 @@
         <v>233</v>
       </c>
       <c r="G349" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="H349" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J349" s="1" t="s">
         <v>798</v>
-      </c>
-      <c r="H349" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J349" s="1" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C350" s="1" t="n">
         <v>2807</v>
@@ -14879,7 +14876,7 @@
         <v>233</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H350" s="1" t="s">
         <v>17</v>
@@ -14887,10 +14884,10 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C351" s="1" t="n">
         <v>2808</v>
@@ -14902,16 +14899,16 @@
         <v>10</v>
       </c>
       <c r="F351" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="G351" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="G351" s="1" t="s">
-        <v>804</v>
-      </c>
       <c r="H351" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14919,7 +14916,7 @@
         <v>738</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C352" s="1" t="n">
         <v>2900</v>
@@ -14931,16 +14928,16 @@
         <v>1</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H352" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I352" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="J352" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="J352" s="1" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14948,7 +14945,7 @@
         <v>738</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C353" s="1" t="n">
         <v>2901</v>
@@ -14960,7 +14957,7 @@
         <v>10</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H353" s="1" t="s">
         <v>23</v>
@@ -14969,7 +14966,7 @@
         <v>94</v>
       </c>
       <c r="J353" s="21" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14977,7 +14974,7 @@
         <v>738</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C354" s="1" t="n">
         <v>2902</v>
@@ -14992,13 +14989,13 @@
         <v>233</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H354" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I354" s="22" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="J354" s="21"/>
     </row>
@@ -15007,7 +15004,7 @@
         <v>738</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C355" s="1" t="n">
         <v>2903</v>
@@ -15019,7 +15016,7 @@
         <v>10</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H355" s="1" t="s">
         <v>17</v>
@@ -15028,15 +15025,15 @@
         <v>94</v>
       </c>
       <c r="J355" s="21" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="B356" s="1" t="s">
         <v>818</v>
-      </c>
-      <c r="B356" s="1" t="s">
-        <v>819</v>
       </c>
       <c r="C356" s="1" t="n">
         <v>3000</v>
@@ -15051,7 +15048,7 @@
         <v>233</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H356" s="1" t="s">
         <v>17</v>
@@ -15060,10 +15057,10 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C357" s="1" t="n">
         <v>3001</v>
@@ -15075,7 +15072,7 @@
         <v>10000</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>453</v>
@@ -15084,15 +15081,15 @@
         <v>17</v>
       </c>
       <c r="I357" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C358" s="1" t="n">
         <v>3003</v>
@@ -15107,21 +15104,21 @@
         <v>233</v>
       </c>
       <c r="G358" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="H358" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I358" s="1" t="s">
         <v>825</v>
-      </c>
-      <c r="H358" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I358" s="1" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C359" s="1" t="n">
         <v>3004</v>
@@ -15136,7 +15133,7 @@
         <v>80</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H359" s="1" t="s">
         <v>17</v>
@@ -15147,10 +15144,10 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C360" s="1" t="n">
         <v>3005</v>
@@ -15162,24 +15159,24 @@
         <v>10000</v>
       </c>
       <c r="F360" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="G360" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="H360" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I360" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="G360" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="H360" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I360" s="1" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C361" s="1" t="n">
         <v>3007</v>
@@ -15194,21 +15191,21 @@
         <v>233</v>
       </c>
       <c r="G361" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="H361" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I361" s="1" t="s">
         <v>832</v>
-      </c>
-      <c r="H361" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I361" s="1" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="B362" s="1" t="s">
         <v>834</v>
-      </c>
-      <c r="B362" s="1" t="s">
-        <v>835</v>
       </c>
       <c r="C362" s="1" t="n">
         <v>3100</v>
@@ -15220,7 +15217,7 @@
         <v>10</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G362" s="1" t="s">
         <v>166</v>
@@ -15234,10 +15231,10 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C363" s="1" t="n">
         <v>3101</v>
@@ -15263,10 +15260,10 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C364" s="1" t="n">
         <v>3102</v>
@@ -15287,12 +15284,12 @@
         <v>17</v>
       </c>
       <c r="I364" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>185</v>
@@ -15307,7 +15304,7 @@
         <v>100</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>187</v>
@@ -15321,7 +15318,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>188</v>
@@ -15350,7 +15347,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>379</v>
@@ -15374,15 +15371,15 @@
         <v>17</v>
       </c>
       <c r="I367" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C368" s="1" t="n">
         <v>3111</v>
@@ -15403,15 +15400,15 @@
         <v>17</v>
       </c>
       <c r="I368" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C369" s="1" t="n">
         <v>3112</v>
@@ -15426,18 +15423,18 @@
         <v>233</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H369" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I369" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>377</v>
@@ -15461,15 +15458,15 @@
         <v>17</v>
       </c>
       <c r="I370" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C371" s="1" t="n">
         <v>3114</v>
@@ -15490,15 +15487,15 @@
         <v>17</v>
       </c>
       <c r="I371" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C372" s="1" t="n">
         <v>3115</v>
@@ -15513,18 +15510,18 @@
         <v>233</v>
       </c>
       <c r="G372" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H372" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I372" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>213</v>
@@ -15548,15 +15545,15 @@
         <v>17</v>
       </c>
       <c r="I373" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C374" s="1" t="n">
         <v>3117</v>
@@ -15571,21 +15568,21 @@
         <v>233</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H374" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I374" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C375" s="1" t="n">
         <v>3125</v>
@@ -15600,7 +15597,7 @@
         <v>233</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H375" s="1" t="s">
         <v>17</v>
@@ -15608,10 +15605,10 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C376" s="1" t="n">
         <v>3126</v>
@@ -15632,15 +15629,15 @@
         <v>23</v>
       </c>
       <c r="I376" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C377" s="1" t="n">
         <v>3127</v>
@@ -15655,7 +15652,7 @@
         <v>233</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H377" s="1" t="s">
         <v>17</v>
@@ -15663,10 +15660,10 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C378" s="1" t="n">
         <v>3128</v>
@@ -15687,12 +15684,12 @@
         <v>17</v>
       </c>
       <c r="I378" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>337</v>
@@ -15707,7 +15704,7 @@
         <v>100</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>338</v>
@@ -15721,10 +15718,10 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C380" s="1" t="n">
         <v>3132</v>
@@ -15736,7 +15733,7 @@
         <v>100</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>340</v>
@@ -15750,10 +15747,10 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C381" s="1" t="n">
         <v>3134</v>
@@ -15765,10 +15762,10 @@
         <v>100</v>
       </c>
       <c r="F381" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H381" s="1" t="s">
         <v>17</v>
@@ -15779,10 +15776,10 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C382" s="1" t="n">
         <v>3136</v>
@@ -15794,10 +15791,10 @@
         <v>100</v>
       </c>
       <c r="F382" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H382" s="1" t="s">
         <v>17</v>
@@ -15808,10 +15805,10 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C383" s="1" t="n">
         <v>3138</v>
@@ -15837,7 +15834,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>527</v>
@@ -15866,7 +15863,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>529</v>
@@ -15895,7 +15892,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>531</v>
@@ -15924,7 +15921,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>533</v>
@@ -15953,10 +15950,10 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C388" s="1" t="n">
         <v>3148</v>
@@ -15982,10 +15979,10 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C389" s="1" t="n">
         <v>3149</v>
@@ -16011,10 +16008,10 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C390" s="1" t="n">
         <v>3150</v>
@@ -16040,10 +16037,10 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C391" s="1" t="n">
         <v>3151</v>
@@ -16069,10 +16066,10 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C392" s="1" t="n">
         <v>3152</v>
@@ -16098,10 +16095,10 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C393" s="1" t="n">
         <v>3153</v>
@@ -16127,10 +16124,10 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C394" s="1" t="n">
         <v>3154</v>
@@ -16156,10 +16153,10 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C395" s="1" t="n">
         <v>3155</v>
@@ -16185,10 +16182,10 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C396" s="1" t="n">
         <v>3156</v>
@@ -16214,10 +16211,10 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C397" s="1" t="n">
         <v>3157</v>
@@ -16243,10 +16240,10 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C398" s="1" t="n">
         <v>3158</v>
@@ -16272,10 +16269,10 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C399" s="1" t="n">
         <v>3159</v>
@@ -16301,10 +16298,10 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C400" s="1" t="n">
         <v>3160</v>
@@ -16330,10 +16327,10 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C401" s="1" t="n">
         <v>3161</v>
@@ -16359,10 +16356,10 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C402" s="1" t="n">
         <v>3162</v>
@@ -16388,10 +16385,10 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C403" s="1" t="n">
         <v>3163</v>
@@ -16417,7 +16414,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>568</v>
@@ -16446,7 +16443,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>570</v>
@@ -16475,7 +16472,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>572</v>
@@ -16504,7 +16501,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>574</v>
@@ -16533,10 +16530,10 @@
     </row>
     <row r="408" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C408" s="1" t="n">
         <v>3168</v>
@@ -16557,15 +16554,15 @@
         <v>17</v>
       </c>
       <c r="I408" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B409" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="B409" s="1" t="s">
-        <v>882</v>
       </c>
       <c r="C409" s="1" t="n">
         <v>3200</v>
@@ -16591,10 +16588,10 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C410" s="1" t="n">
         <v>3201</v>
@@ -16620,10 +16617,10 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C411" s="1" t="n">
         <v>3202</v>
@@ -16649,10 +16646,10 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C412" s="1" t="n">
         <v>3203</v>
@@ -16664,7 +16661,7 @@
         <v>10</v>
       </c>
       <c r="F412" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>584</v>
@@ -16678,10 +16675,10 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C413" s="1" t="n">
         <v>3204</v>
@@ -16693,7 +16690,7 @@
         <v>10</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>593</v>
@@ -16707,10 +16704,10 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C414" s="1" t="n">
         <v>3205</v>
@@ -16722,7 +16719,7 @@
         <v>10</v>
       </c>
       <c r="F414" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>602</v>
@@ -16736,10 +16733,10 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C415" s="1" t="n">
         <v>3206</v>
@@ -16751,7 +16748,7 @@
         <v>1</v>
       </c>
       <c r="F415" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>586</v>
@@ -16765,10 +16762,10 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C416" s="1" t="n">
         <v>3207</v>
@@ -16780,7 +16777,7 @@
         <v>1</v>
       </c>
       <c r="F416" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>595</v>
@@ -16794,10 +16791,10 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C417" s="1" t="n">
         <v>3208</v>
@@ -16809,7 +16806,7 @@
         <v>1</v>
       </c>
       <c r="F417" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>604</v>
@@ -16823,10 +16820,10 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C418" s="1" t="n">
         <v>3209</v>
@@ -16838,10 +16835,10 @@
         <v>100</v>
       </c>
       <c r="F418" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H418" s="1" t="s">
         <v>17</v>
@@ -16852,10 +16849,10 @@
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C419" s="1" t="n">
         <v>3210</v>
@@ -16867,10 +16864,10 @@
         <v>100</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H419" s="1" t="s">
         <v>17</v>
@@ -16881,10 +16878,10 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C420" s="1" t="n">
         <v>3211</v>
@@ -16896,10 +16893,10 @@
         <v>100</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H420" s="1" t="s">
         <v>17</v>
@@ -16910,10 +16907,10 @@
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C421" s="1" t="n">
         <v>3212</v>
@@ -16928,7 +16925,7 @@
         <v>233</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H421" s="1" t="s">
         <v>17</v>
@@ -16936,10 +16933,10 @@
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C422" s="1" t="n">
         <v>3213</v>
@@ -16954,18 +16951,18 @@
         <v>233</v>
       </c>
       <c r="G422" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="H422" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I422" s="1" t="s">
         <v>900</v>
-      </c>
-      <c r="H422" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I422" s="1" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>623</v>
@@ -16989,15 +16986,15 @@
         <v>17</v>
       </c>
       <c r="I423" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C424" s="1" t="n">
         <v>3215</v>
@@ -17012,7 +17009,7 @@
         <v>233</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H424" s="1" t="s">
         <v>17</v>
@@ -17023,10 +17020,10 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C425" s="1" t="n">
         <v>3216</v>
@@ -17041,7 +17038,7 @@
         <v>233</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H425" s="1" t="s">
         <v>17</v>
@@ -17052,10 +17049,10 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C426" s="1" t="n">
         <v>3217</v>
@@ -17070,7 +17067,7 @@
         <v>233</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H426" s="1" t="s">
         <v>17</v>
@@ -17081,10 +17078,10 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C427" s="1" t="n">
         <v>3218</v>
@@ -17099,7 +17096,7 @@
         <v>292</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H427" s="1" t="s">
         <v>17</v>
@@ -17110,10 +17107,10 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C428" s="1" t="n">
         <v>3219</v>
@@ -17125,10 +17122,10 @@
         <v>10</v>
       </c>
       <c r="F428" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H428" s="1" t="s">
         <v>17</v>
@@ -17139,10 +17136,10 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C429" s="1" t="n">
         <v>3220</v>
@@ -17154,10 +17151,10 @@
         <v>10</v>
       </c>
       <c r="F429" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H429" s="1" t="s">
         <v>17</v>
@@ -17168,10 +17165,10 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C430" s="1" t="n">
         <v>3221</v>
@@ -17183,10 +17180,10 @@
         <v>10</v>
       </c>
       <c r="F430" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H430" s="1" t="s">
         <v>17</v>
@@ -17197,10 +17194,10 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C431" s="1" t="n">
         <v>3222</v>
@@ -17212,10 +17209,10 @@
         <v>100</v>
       </c>
       <c r="F431" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H431" s="1" t="s">
         <v>17</v>
@@ -17226,10 +17223,10 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C432" s="1" t="n">
         <v>3223</v>
@@ -17244,21 +17241,21 @@
         <v>233</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H432" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I432" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C433" s="1" t="n">
         <v>3300</v>
@@ -17273,7 +17270,7 @@
         <v>233</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H433" s="1" t="s">
         <v>17</v>
@@ -17281,10 +17278,10 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="B434" s="1" t="s">
         <v>922</v>
-      </c>
-      <c r="B434" s="1" t="s">
-        <v>923</v>
       </c>
       <c r="C434" s="1" t="n">
         <v>3301</v>
@@ -17299,7 +17296,7 @@
         <v>186</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H434" s="1" t="s">
         <v>17</v>
@@ -17307,10 +17304,10 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C435" s="1" t="n">
         <v>3302</v>
@@ -17325,7 +17322,7 @@
         <v>142</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H435" s="1" t="s">
         <v>17</v>
@@ -17333,10 +17330,10 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C436" s="1" t="n">
         <v>3303</v>
@@ -17351,21 +17348,21 @@
         <v>233</v>
       </c>
       <c r="G436" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="H436" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I436" s="1" t="s">
         <v>928</v>
-      </c>
-      <c r="H436" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I436" s="1" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C437" s="1" t="n">
         <v>3304</v>
@@ -17380,7 +17377,7 @@
         <v>142</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H437" s="1" t="s">
         <v>17</v>
@@ -17391,10 +17388,10 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C438" s="1" t="n">
         <v>3305</v>
@@ -17409,21 +17406,21 @@
         <v>233</v>
       </c>
       <c r="G438" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="H438" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I438" s="1" t="s">
         <v>832</v>
-      </c>
-      <c r="H438" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I438" s="1" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C439" s="1" t="n">
         <v>3306</v>
@@ -17435,10 +17432,10 @@
         <v>10</v>
       </c>
       <c r="F439" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="G439" s="1" t="s">
         <v>934</v>
-      </c>
-      <c r="G439" s="1" t="s">
-        <v>935</v>
       </c>
       <c r="H439" s="1" t="s">
         <v>17</v>
@@ -17447,15 +17444,15 @@
         <v>94</v>
       </c>
       <c r="J439" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C440" s="1" t="n">
         <v>3307</v>
@@ -17470,24 +17467,24 @@
         <v>186</v>
       </c>
       <c r="G440" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="H440" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I440" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="H440" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I440" s="1" t="s">
+      <c r="J440" s="1" t="s">
         <v>939</v>
-      </c>
-      <c r="J440" s="1" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C441" s="1" t="n">
         <v>3308</v>
@@ -17502,24 +17499,24 @@
         <v>233</v>
       </c>
       <c r="G441" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="H441" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I441" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="H441" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I441" s="1" t="s">
+      <c r="J441" s="1" t="s">
         <v>943</v>
-      </c>
-      <c r="J441" s="1" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="B442" s="1" t="s">
         <v>945</v>
-      </c>
-      <c r="B442" s="1" t="s">
-        <v>946</v>
       </c>
       <c r="C442" s="1" t="n">
         <v>3400</v>
@@ -17534,21 +17531,21 @@
         <v>576</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H442" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I442" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C443" s="1" t="n">
         <v>3402</v>
@@ -17563,7 +17560,7 @@
         <v>576</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H443" s="1" t="s">
         <v>17</v>
@@ -17571,10 +17568,10 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B444" s="1" t="s">
         <v>950</v>
-      </c>
-      <c r="B444" s="1" t="s">
-        <v>951</v>
       </c>
       <c r="C444" s="1" t="n">
         <v>3420</v>
@@ -17589,7 +17586,7 @@
         <v>576</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H444" s="1" t="s">
         <v>17</v>
@@ -17597,7 +17594,7 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>621</v>
@@ -17621,12 +17618,12 @@
         <v>17</v>
       </c>
       <c r="I445" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>363</v>
@@ -17641,10 +17638,10 @@
         <v>1</v>
       </c>
       <c r="F446" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="G446" s="1" t="s">
         <v>953</v>
-      </c>
-      <c r="G446" s="1" t="s">
-        <v>954</v>
       </c>
       <c r="H446" s="1" t="s">
         <v>17</v>
@@ -17655,7 +17652,7 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>5</v>
@@ -17673,21 +17670,21 @@
         <v>233</v>
       </c>
       <c r="G447" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="H447" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I447" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="H447" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I447" s="1" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="B448" s="1" t="s">
         <v>957</v>
-      </c>
-      <c r="B448" s="1" t="s">
-        <v>958</v>
       </c>
       <c r="C448" s="1" t="n">
         <v>3500</v>
@@ -17702,21 +17699,21 @@
         <v>21</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H448" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I448" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C449" s="1" t="n">
         <v>3501</v>
@@ -17731,21 +17728,21 @@
         <v>233</v>
       </c>
       <c r="G449" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="H449" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I449" s="1" t="s">
         <v>962</v>
-      </c>
-      <c r="H449" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I449" s="1" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C450" s="1" t="n">
         <v>3502</v>
@@ -17760,7 +17757,7 @@
         <v>233</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H450" s="1" t="s">
         <v>17</v>
@@ -17771,10 +17768,10 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C451" s="1" t="n">
         <v>3503</v>
@@ -17789,21 +17786,21 @@
         <v>233</v>
       </c>
       <c r="G451" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="H451" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I451" s="1" t="s">
         <v>967</v>
-      </c>
-      <c r="H451" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I451" s="1" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C452" s="1" t="n">
         <v>3504</v>
@@ -17818,7 +17815,7 @@
         <v>576</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H452" s="1" t="s">
         <v>17</v>
@@ -17829,10 +17826,10 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C453" s="1" t="n">
         <v>3506</v>
@@ -17853,15 +17850,15 @@
         <v>17</v>
       </c>
       <c r="I453" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C454" s="1" t="n">
         <v>3507</v>
@@ -17876,24 +17873,24 @@
         <v>233</v>
       </c>
       <c r="G454" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="H454" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I454" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="H454" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I454" s="1" t="s">
+      <c r="J454" s="1" t="s">
         <v>973</v>
-      </c>
-      <c r="J454" s="1" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C455" s="1" t="n">
         <v>3508</v>
@@ -17908,7 +17905,7 @@
         <v>233</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H455" s="1" t="s">
         <v>17</v>
@@ -17919,10 +17916,10 @@
     </row>
     <row r="456" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C456" s="1" t="n">
         <v>3509</v>
@@ -17937,21 +17934,21 @@
         <v>233</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H456" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I456" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="B457" s="22" t="s">
         <v>980</v>
-      </c>
-      <c r="B457" s="22" t="s">
-        <v>981</v>
       </c>
       <c r="C457" s="1" t="n">
         <v>3600</v>
@@ -17966,21 +17963,21 @@
         <v>80</v>
       </c>
       <c r="G457" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="H457" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I457" s="1" t="s">
         <v>982</v>
-      </c>
-      <c r="H457" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I457" s="1" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B458" s="22" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C458" s="1" t="n">
         <v>3601</v>
@@ -17995,21 +17992,21 @@
         <v>80</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H458" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I458" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B459" s="22" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C459" s="1" t="n">
         <v>3602</v>
@@ -18024,7 +18021,7 @@
         <v>85</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H459" s="1" t="s">
         <v>17</v>
@@ -18035,10 +18032,10 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B460" s="22" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C460" s="1" t="n">
         <v>3603</v>
@@ -18053,7 +18050,7 @@
         <v>85</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H460" s="1" t="s">
         <v>17</v>
@@ -18064,10 +18061,10 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C461" s="1" t="n">
         <v>3800</v>
@@ -18082,7 +18079,7 @@
         <v>233</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H461" s="1" t="s">
         <v>17</v>
@@ -18090,10 +18087,10 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C462" s="1" t="n">
         <v>3802</v>
@@ -18108,7 +18105,7 @@
         <v>576</v>
       </c>
       <c r="G462" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H462" s="1" t="s">
         <v>17</v>
@@ -18116,7 +18113,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>608</v>
@@ -18139,10 +18136,10 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="B464" s="1" t="s">
         <v>990</v>
-      </c>
-      <c r="B464" s="1" t="s">
-        <v>991</v>
       </c>
       <c r="C464" s="1" t="n">
         <v>3810</v>
@@ -18154,7 +18151,7 @@
         <v>1</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H464" s="1" t="s">
         <v>17</v>
@@ -18162,10 +18159,10 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C465" s="1" t="n">
         <v>3814</v>
@@ -18180,7 +18177,7 @@
         <v>233</v>
       </c>
       <c r="G465" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H465" s="1" t="s">
         <v>23</v>
@@ -18191,7 +18188,7 @@
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>483</v>
@@ -18215,15 +18212,15 @@
         <v>23</v>
       </c>
       <c r="I466" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C467" s="1" t="n">
         <v>3816</v>
@@ -18235,7 +18232,7 @@
         <v>100</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>734</v>
@@ -18249,7 +18246,7 @@
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>585</v>
@@ -18278,7 +18275,7 @@
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>594</v>
@@ -18307,7 +18304,7 @@
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>603</v>
@@ -18336,10 +18333,10 @@
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C471" s="1" t="n">
         <v>3821</v>
@@ -18365,10 +18362,10 @@
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C472" s="1" t="n">
         <v>3822</v>
@@ -18383,7 +18380,7 @@
         <v>292</v>
       </c>
       <c r="G472" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H472" s="1" t="s">
         <v>17</v>
@@ -18394,10 +18391,10 @@
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C473" s="1" t="n">
         <v>3823</v>
@@ -18412,7 +18409,7 @@
         <v>233</v>
       </c>
       <c r="G473" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H473" s="1" t="s">
         <v>17</v>
@@ -18423,10 +18420,10 @@
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C474" s="1" t="n">
         <v>3824</v>
@@ -18441,21 +18438,21 @@
         <v>233</v>
       </c>
       <c r="G474" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H474" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I474" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C475" s="1" t="n">
         <v>3825</v>
@@ -18470,7 +18467,7 @@
         <v>233</v>
       </c>
       <c r="G475" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H475" s="1" t="s">
         <v>23</v>
@@ -18481,10 +18478,10 @@
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C476" s="1" t="n">
         <v>3826</v>
@@ -18499,18 +18496,18 @@
         <v>233</v>
       </c>
       <c r="G476" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H476" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I476" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>578</v>
@@ -18539,7 +18536,7 @@
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>585</v>
@@ -18568,7 +18565,7 @@
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>594</v>
@@ -18597,7 +18594,7 @@
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>603</v>
@@ -18626,10 +18623,10 @@
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B481" s="1" t="s">
         <v>1007</v>
-      </c>
-      <c r="B481" s="1" t="s">
-        <v>1008</v>
       </c>
       <c r="C481" s="1" t="n">
         <v>3902</v>
@@ -18646,7 +18643,7 @@
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>581</v>
@@ -18675,7 +18672,7 @@
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>583</v>
@@ -18684,7 +18681,7 @@
         <v>3911</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E483" s="1" t="n">
         <v>10</v>
@@ -18704,7 +18701,7 @@
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>590</v>
@@ -18733,7 +18730,7 @@
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>592</v>
@@ -18742,7 +18739,7 @@
         <v>3913</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E485" s="1" t="n">
         <v>10</v>
@@ -18762,7 +18759,7 @@
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>599</v>
@@ -18791,7 +18788,7 @@
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>601</v>
@@ -18800,7 +18797,7 @@
         <v>3915</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E487" s="1" t="n">
         <v>10</v>
@@ -18820,7 +18817,7 @@
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>587</v>
@@ -18835,7 +18832,7 @@
         <v>100</v>
       </c>
       <c r="F488" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>588</v>
@@ -18849,7 +18846,7 @@
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>596</v>
@@ -18864,7 +18861,7 @@
         <v>100</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>597</v>
@@ -18878,7 +18875,7 @@
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>605</v>
@@ -18893,7 +18890,7 @@
         <v>100</v>
       </c>
       <c r="F490" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>606</v>
@@ -18907,7 +18904,7 @@
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="22" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>185</v>
@@ -18936,7 +18933,7 @@
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="22" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>188</v>
@@ -18965,10 +18962,10 @@
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B493" s="1" t="s">
         <v>1010</v>
-      </c>
-      <c r="B493" s="1" t="s">
-        <v>1011</v>
       </c>
       <c r="C493" s="22" t="n">
         <v>4002</v>
@@ -18994,10 +18991,10 @@
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="22" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C494" s="22" t="n">
         <v>4003</v>
@@ -19023,10 +19020,10 @@
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="22" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C495" s="22" t="n">
         <v>4004</v>
@@ -19038,10 +19035,10 @@
         <v>100</v>
       </c>
       <c r="F495" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G495" s="22" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H495" s="1" t="s">
         <v>17</v>
@@ -19052,7 +19049,7 @@
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="22" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>367</v>
@@ -19081,7 +19078,7 @@
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="22" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>369</v>
@@ -19110,10 +19107,10 @@
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="22" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C498" s="22" t="n">
         <v>4008</v>
@@ -19139,10 +19136,10 @@
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="22" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C499" s="22" t="n">
         <v>4009</v>
@@ -19168,7 +19165,7 @@
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="22" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>377</v>
@@ -19197,7 +19194,7 @@
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="22" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>379</v>
@@ -19226,7 +19223,7 @@
     </row>
     <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B502" s="1" t="s">
         <v>185</v>
@@ -19255,7 +19252,7 @@
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>188</v>
@@ -19284,10 +19281,10 @@
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C504" s="22" t="n">
         <v>4102</v>
@@ -19313,10 +19310,10 @@
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C505" s="22" t="n">
         <v>4103</v>
@@ -19342,10 +19339,10 @@
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C506" s="22" t="n">
         <v>4104</v>
@@ -19357,10 +19354,10 @@
         <v>100</v>
       </c>
       <c r="F506" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G506" s="22" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H506" s="1" t="s">
         <v>17</v>
@@ -19371,7 +19368,7 @@
     </row>
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>367</v>
@@ -19400,7 +19397,7 @@
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B508" s="1" t="s">
         <v>369</v>
@@ -19429,10 +19426,10 @@
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C509" s="22" t="n">
         <v>4108</v>
@@ -19458,10 +19455,10 @@
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C510" s="22" t="n">
         <v>4109</v>
@@ -19487,7 +19484,7 @@
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B511" s="1" t="s">
         <v>377</v>
@@ -19516,7 +19513,7 @@
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B512" s="1" t="s">
         <v>379</v>
@@ -19545,10 +19542,10 @@
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="22" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B513" s="1" t="s">
         <v>1016</v>
-      </c>
-      <c r="B513" s="1" t="s">
-        <v>1017</v>
       </c>
       <c r="C513" s="22" t="n">
         <v>4112</v>
@@ -19569,15 +19566,15 @@
         <v>17</v>
       </c>
       <c r="I513" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C514" s="22" t="n">
         <v>4113</v>
@@ -19598,15 +19595,15 @@
         <v>17</v>
       </c>
       <c r="I514" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C515" s="22" t="n">
         <v>4114</v>
@@ -19621,7 +19618,7 @@
         <v>233</v>
       </c>
       <c r="G515" s="22" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H515" s="1" t="s">
         <v>17</v>
@@ -19632,10 +19629,10 @@
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C516" s="22" t="n">
         <v>4115</v>
@@ -19650,7 +19647,7 @@
         <v>233</v>
       </c>
       <c r="G516" s="22" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H516" s="1" t="s">
         <v>17</v>
@@ -19661,10 +19658,10 @@
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="22" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C517" s="22" t="n">
         <v>4116</v>
@@ -19679,7 +19676,7 @@
         <v>233</v>
       </c>
       <c r="G517" s="22" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H517" s="1" t="s">
         <v>17</v>
@@ -19690,7 +19687,7 @@
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B518" s="1" t="s">
         <v>185</v>
@@ -19719,7 +19716,7 @@
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B519" s="1" t="s">
         <v>188</v>
@@ -19748,10 +19745,10 @@
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C520" s="22" t="n">
         <v>4202</v>
@@ -19777,10 +19774,10 @@
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C521" s="22" t="n">
         <v>4203</v>
@@ -19806,10 +19803,10 @@
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C522" s="22" t="n">
         <v>4204</v>
@@ -19821,10 +19818,10 @@
         <v>100</v>
       </c>
       <c r="F522" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G522" s="22" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H522" s="1" t="s">
         <v>17</v>
@@ -19835,7 +19832,7 @@
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B523" s="1" t="s">
         <v>367</v>
@@ -19864,7 +19861,7 @@
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>369</v>
@@ -19893,10 +19890,10 @@
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C525" s="22" t="n">
         <v>4208</v>
@@ -19922,10 +19919,10 @@
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C526" s="22" t="n">
         <v>4209</v>
@@ -19951,7 +19948,7 @@
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>377</v>
@@ -19980,7 +19977,7 @@
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>379</v>
@@ -20009,7 +20006,7 @@
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="22" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>185</v>
@@ -20038,7 +20035,7 @@
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="22" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>188</v>
@@ -20067,10 +20064,10 @@
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="22" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C531" s="22" t="n">
         <v>4302</v>
@@ -20096,10 +20093,10 @@
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="22" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C532" s="22" t="n">
         <v>4303</v>
@@ -20125,10 +20122,10 @@
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="22" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B533" s="1" t="s">
         <v>1025</v>
-      </c>
-      <c r="B533" s="1" t="s">
-        <v>1026</v>
       </c>
       <c r="C533" s="22" t="n">
         <v>4304</v>
@@ -20140,10 +20137,10 @@
         <v>100</v>
       </c>
       <c r="F533" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G533" s="22" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H533" s="1" t="s">
         <v>17</v>
@@ -20154,7 +20151,7 @@
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="22" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>367</v>
@@ -20183,7 +20180,7 @@
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="22" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>369</v>
@@ -20212,10 +20209,10 @@
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="22" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C536" s="22" t="n">
         <v>4308</v>
@@ -20241,10 +20238,10 @@
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="22" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C537" s="22" t="n">
         <v>4309</v>
@@ -20270,7 +20267,7 @@
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="22" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>377</v>
@@ -20299,7 +20296,7 @@
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="22" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>379</v>
@@ -20328,7 +20325,7 @@
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>185</v>
@@ -20357,7 +20354,7 @@
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>188</v>
@@ -20386,10 +20383,10 @@
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C542" s="22" t="n">
         <v>4402</v>
@@ -20415,10 +20412,10 @@
     </row>
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C543" s="22" t="n">
         <v>4403</v>
@@ -20444,10 +20441,10 @@
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C544" s="22" t="n">
         <v>4404</v>
@@ -20459,10 +20456,10 @@
         <v>100</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G544" s="22" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H544" s="1" t="s">
         <v>17</v>
@@ -20473,10 +20470,10 @@
     </row>
     <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C545" s="22" t="n">
         <v>4406</v>
@@ -20488,10 +20485,10 @@
         <v>100</v>
       </c>
       <c r="F545" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G545" s="22" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H545" s="1" t="s">
         <v>17</v>
@@ -20502,7 +20499,7 @@
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>367</v>
@@ -20526,12 +20523,12 @@
         <v>17</v>
       </c>
       <c r="I546" s="22" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B547" s="1" t="s">
         <v>369</v>
@@ -20555,15 +20552,15 @@
         <v>17</v>
       </c>
       <c r="I547" s="22" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C548" s="22" t="n">
         <v>4410</v>
@@ -20589,10 +20586,10 @@
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C549" s="22" t="n">
         <v>4411</v>
@@ -20618,7 +20615,7 @@
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>377</v>
@@ -20647,7 +20644,7 @@
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="22" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>379</v>
@@ -20676,7 +20673,7 @@
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>126</v>
@@ -20694,7 +20691,7 @@
         <v>80</v>
       </c>
       <c r="G552" s="22" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H552" s="22" t="s">
         <v>17</v>
@@ -20705,7 +20702,7 @@
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B553" s="1" t="s">
         <v>129</v>
@@ -20723,7 +20720,7 @@
         <v>80</v>
       </c>
       <c r="G553" s="22" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H553" s="22" t="s">
         <v>17</v>
@@ -20734,7 +20731,7 @@
     </row>
     <row r="554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B554" s="1" t="s">
         <v>131</v>
@@ -20752,7 +20749,7 @@
         <v>80</v>
       </c>
       <c r="G554" s="22" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H554" s="22" t="s">
         <v>17</v>
@@ -20763,7 +20760,7 @@
     </row>
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B555" s="1" t="s">
         <v>133</v>
@@ -20781,7 +20778,7 @@
         <v>80</v>
       </c>
       <c r="G555" s="22" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H555" s="22" t="s">
         <v>17</v>
@@ -20792,7 +20789,7 @@
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B556" s="1" t="s">
         <v>137</v>
@@ -20810,7 +20807,7 @@
         <v>80</v>
       </c>
       <c r="G556" s="22" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H556" s="22" t="s">
         <v>17</v>
@@ -20821,7 +20818,7 @@
     </row>
     <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B557" s="1" t="s">
         <v>139</v>
@@ -20839,7 +20836,7 @@
         <v>80</v>
       </c>
       <c r="G557" s="22" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H557" s="22" t="s">
         <v>17</v>
@@ -20850,10 +20847,10 @@
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C558" s="22" t="n">
         <v>4506</v>
@@ -20862,13 +20859,13 @@
         <v>59</v>
       </c>
       <c r="E558" s="22" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F558" s="3" t="s">
         <v>150</v>
       </c>
       <c r="G558" s="22" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H558" s="22" t="s">
         <v>17</v>
@@ -20879,10 +20876,10 @@
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C559" s="22" t="n">
         <v>4507</v>
@@ -20891,13 +20888,13 @@
         <v>59</v>
       </c>
       <c r="E559" s="22" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F559" s="3" t="s">
         <v>150</v>
       </c>
       <c r="G559" s="22" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H559" s="22" t="s">
         <v>17</v>
@@ -20908,10 +20905,10 @@
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C560" s="22" t="n">
         <v>4508</v>
@@ -20920,13 +20917,13 @@
         <v>59</v>
       </c>
       <c r="E560" s="22" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F560" s="3" t="s">
         <v>150</v>
       </c>
       <c r="G560" s="22" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H560" s="22" t="s">
         <v>17</v>
@@ -20937,10 +20934,10 @@
     </row>
     <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C561" s="22" t="n">
         <v>4509</v>
@@ -20952,7 +20949,7 @@
         <v>100</v>
       </c>
       <c r="G561" s="22" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H561" s="22" t="s">
         <v>17</v>
@@ -20963,7 +20960,7 @@
     </row>
     <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B562" s="1" t="s">
         <v>159</v>
@@ -20992,7 +20989,7 @@
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B563" s="1" t="s">
         <v>161</v>
@@ -21021,7 +21018,7 @@
     </row>
     <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B564" s="1" t="s">
         <v>163</v>
@@ -21050,7 +21047,7 @@
     </row>
     <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>165</v>
@@ -21079,7 +21076,7 @@
     </row>
     <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>168</v>
@@ -21108,7 +21105,7 @@
     </row>
     <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B567" s="1" t="s">
         <v>170</v>
@@ -21137,10 +21134,10 @@
     </row>
     <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C568" s="22" t="n">
         <v>4516</v>
@@ -21149,7 +21146,7 @@
         <v>59</v>
       </c>
       <c r="E568" s="22" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F568" s="3" t="s">
         <v>150</v>
@@ -21166,10 +21163,10 @@
     </row>
     <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A569" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C569" s="22" t="n">
         <v>4517</v>
@@ -21178,7 +21175,7 @@
         <v>59</v>
       </c>
       <c r="E569" s="22" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F569" s="3" t="s">
         <v>150</v>
@@ -21195,10 +21192,10 @@
     </row>
     <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C570" s="22" t="n">
         <v>4518</v>
@@ -21207,7 +21204,7 @@
         <v>59</v>
       </c>
       <c r="E570" s="22" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F570" s="3" t="s">
         <v>150</v>
@@ -21224,7 +21221,7 @@
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B571" s="1" t="s">
         <v>172</v>
@@ -21253,10 +21250,10 @@
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C572" s="22" t="n">
         <v>4520</v>
@@ -21271,21 +21268,21 @@
         <v>233</v>
       </c>
       <c r="G572" s="22" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H572" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I572" s="22" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C573" s="22" t="n">
         <v>4521</v>
@@ -21300,21 +21297,21 @@
         <v>233</v>
       </c>
       <c r="G573" s="22" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H573" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I573" s="22" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C574" s="22" t="n">
         <v>4522</v>
@@ -21329,7 +21326,7 @@
         <v>80</v>
       </c>
       <c r="G574" s="22" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H574" s="22" t="s">
         <v>23</v>
@@ -21340,10 +21337,10 @@
     </row>
     <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C575" s="22" t="n">
         <v>4523</v>
@@ -21358,7 +21355,7 @@
         <v>80</v>
       </c>
       <c r="G575" s="22" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H575" s="22" t="s">
         <v>23</v>
@@ -21369,7 +21366,7 @@
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B576" s="1" t="s">
         <v>191</v>
@@ -21398,10 +21395,10 @@
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C577" s="22" t="n">
         <v>4525</v>
@@ -21427,7 +21424,7 @@
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A578" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B578" s="1" t="s">
         <v>185</v>
@@ -21456,7 +21453,7 @@
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B579" s="1" t="s">
         <v>188</v>
@@ -21485,7 +21482,7 @@
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B580" s="1" t="s">
         <v>275</v>
@@ -21514,10 +21511,10 @@
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B581" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C581" s="22" t="n">
         <v>4529</v>
@@ -21543,10 +21540,10 @@
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C582" s="22" t="n">
         <v>4530</v>
@@ -21572,10 +21569,10 @@
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C583" s="22" t="n">
         <v>4531</v>
@@ -21601,7 +21598,7 @@
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B584" s="1" t="s">
         <v>208</v>
@@ -21630,7 +21627,7 @@
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B585" s="1" t="s">
         <v>369</v>
@@ -21659,10 +21656,10 @@
     </row>
     <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C586" s="22" t="n">
         <v>4534</v>
@@ -21677,7 +21674,7 @@
         <v>233</v>
       </c>
       <c r="G586" s="22" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H586" s="22" t="s">
         <v>17</v>
@@ -21688,10 +21685,10 @@
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B587" s="22" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C587" s="22" t="n">
         <v>4535</v>
@@ -21717,7 +21714,7 @@
     </row>
     <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A588" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B588" s="1" t="s">
         <v>367</v>
@@ -21746,10 +21743,10 @@
     </row>
     <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C589" s="22" t="n">
         <v>4537</v>
@@ -21764,7 +21761,7 @@
         <v>233</v>
       </c>
       <c r="G589" s="22" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H589" s="22" t="s">
         <v>17</v>
@@ -21775,7 +21772,7 @@
     </row>
     <row r="590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A590" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B590" s="22" t="s">
         <v>213</v>
@@ -21804,10 +21801,10 @@
     </row>
     <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A591" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C591" s="22" t="n">
         <v>4539</v>
@@ -21822,7 +21819,7 @@
         <v>233</v>
       </c>
       <c r="G591" s="22" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H591" s="22" t="s">
         <v>17</v>
@@ -21833,7 +21830,7 @@
     </row>
     <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A592" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B592" s="1" t="s">
         <v>519</v>
@@ -21862,7 +21859,7 @@
     </row>
     <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B593" s="1" t="s">
         <v>521</v>
@@ -21891,10 +21888,10 @@
     </row>
     <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C594" s="22" t="n">
         <v>4542</v>
@@ -21920,7 +21917,7 @@
     </row>
     <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B595" s="1" t="s">
         <v>524</v>
@@ -21949,7 +21946,7 @@
     </row>
     <row r="596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B596" s="1" t="s">
         <v>490</v>
@@ -21978,7 +21975,7 @@
     </row>
     <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B597" s="1" t="s">
         <v>516</v>
@@ -22007,10 +22004,10 @@
     </row>
     <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C598" s="22" t="n">
         <v>4546</v>
@@ -22036,10 +22033,10 @@
     </row>
     <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C599" s="22" t="n">
         <v>4548</v>
@@ -22065,10 +22062,10 @@
     </row>
     <row r="600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A600" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C600" s="22" t="n">
         <v>4550</v>
@@ -22094,10 +22091,10 @@
     </row>
     <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A601" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C601" s="22" t="n">
         <v>4552</v>
@@ -22123,10 +22120,10 @@
     </row>
     <row r="602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A602" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C602" s="22" t="n">
         <v>4554</v>
@@ -22152,10 +22149,10 @@
     </row>
     <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A603" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B603" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C603" s="22" t="n">
         <v>4556</v>
@@ -22181,10 +22178,10 @@
     </row>
     <row r="604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A604" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C604" s="22" t="n">
         <v>4558</v>
@@ -22210,10 +22207,10 @@
     </row>
     <row r="605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A605" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B605" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C605" s="22" t="n">
         <v>4560</v>
@@ -22239,7 +22236,7 @@
     </row>
     <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A606" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B606" s="1" t="s">
         <v>337</v>
@@ -22268,10 +22265,10 @@
     </row>
     <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A607" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B607" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C607" s="22" t="n">
         <v>4564</v>
@@ -22297,10 +22294,10 @@
     </row>
     <row r="608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A608" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C608" s="22" t="n">
         <v>4566</v>
@@ -22315,7 +22312,7 @@
         <v>316</v>
       </c>
       <c r="G608" s="22" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H608" s="22" t="s">
         <v>17</v>
@@ -22326,10 +22323,10 @@
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A609" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C609" s="22" t="n">
         <v>4568</v>
@@ -22344,7 +22341,7 @@
         <v>316</v>
       </c>
       <c r="G609" s="22" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H609" s="22" t="s">
         <v>17</v>
@@ -22355,10 +22352,10 @@
     </row>
     <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A610" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C610" s="22" t="n">
         <v>4570</v>
@@ -22373,7 +22370,7 @@
         <v>316</v>
       </c>
       <c r="G610" s="22" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H610" s="22" t="s">
         <v>17</v>
@@ -22384,10 +22381,10 @@
     </row>
     <row r="611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A611" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B611" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C611" s="22" t="n">
         <v>4572</v>
@@ -22402,7 +22399,7 @@
         <v>316</v>
       </c>
       <c r="G611" s="22" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H611" s="22" t="s">
         <v>17</v>
@@ -22413,7 +22410,7 @@
     </row>
     <row r="612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A612" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B612" s="1" t="s">
         <v>504</v>
@@ -22442,7 +22439,7 @@
     </row>
     <row r="613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A613" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B613" s="1" t="s">
         <v>507</v>
@@ -22471,7 +22468,7 @@
     </row>
     <row r="614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A614" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B614" s="1" t="s">
         <v>510</v>
@@ -22500,7 +22497,7 @@
     </row>
     <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A615" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B615" s="1" t="s">
         <v>513</v>
@@ -22529,7 +22526,7 @@
     </row>
     <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B616" s="1" t="s">
         <v>536</v>
@@ -22562,7 +22559,7 @@
     </row>
     <row r="617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A617" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B617" s="1" t="s">
         <v>538</v>
@@ -22595,7 +22592,7 @@
     </row>
     <row r="618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A618" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B618" s="1" t="s">
         <v>540</v>
@@ -22628,7 +22625,7 @@
     </row>
     <row r="619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A619" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B619" s="1" t="s">
         <v>542</v>
@@ -22661,7 +22658,7 @@
     </row>
     <row r="620" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A620" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B620" s="1" t="s">
         <v>544</v>
@@ -22694,7 +22691,7 @@
     </row>
     <row r="621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A621" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B621" s="1" t="s">
         <v>546</v>
@@ -22727,7 +22724,7 @@
     </row>
     <row r="622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A622" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B622" s="1" t="s">
         <v>548</v>
@@ -22760,7 +22757,7 @@
     </row>
     <row r="623" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A623" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B623" s="1" t="s">
         <v>550</v>
@@ -22793,7 +22790,7 @@
     </row>
     <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A624" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B624" s="1" t="s">
         <v>552</v>
@@ -22826,7 +22823,7 @@
     </row>
     <row r="625" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A625" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B625" s="1" t="s">
         <v>554</v>
@@ -22859,7 +22856,7 @@
     </row>
     <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A626" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B626" s="1" t="s">
         <v>556</v>
@@ -22892,7 +22889,7 @@
     </row>
     <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A627" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B627" s="1" t="s">
         <v>558</v>
@@ -22925,7 +22922,7 @@
     </row>
     <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A628" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B628" s="1" t="s">
         <v>560</v>
@@ -22958,7 +22955,7 @@
     </row>
     <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A629" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B629" s="1" t="s">
         <v>562</v>
@@ -22991,7 +22988,7 @@
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B630" s="1" t="s">
         <v>564</v>
@@ -23024,7 +23021,7 @@
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A631" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B631" s="1" t="s">
         <v>566</v>
@@ -23057,7 +23054,7 @@
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A632" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B632" s="1" t="s">
         <v>527</v>
@@ -23086,7 +23083,7 @@
     </row>
     <row r="633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A633" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B633" s="1" t="s">
         <v>529</v>
@@ -23115,7 +23112,7 @@
     </row>
     <row r="634" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A634" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B634" s="1" t="s">
         <v>531</v>
@@ -23144,7 +23141,7 @@
     </row>
     <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A635" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B635" s="1" t="s">
         <v>533</v>
@@ -23173,7 +23170,7 @@
     </row>
     <row r="636" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A636" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B636" s="1" t="s">
         <v>568</v>
@@ -23202,7 +23199,7 @@
     </row>
     <row r="637" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A637" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B637" s="1" t="s">
         <v>570</v>
@@ -23231,7 +23228,7 @@
     </row>
     <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A638" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B638" s="1" t="s">
         <v>572</v>
@@ -23260,7 +23257,7 @@
     </row>
     <row r="639" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A639" s="22" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B639" s="1" t="s">
         <v>574</v>
@@ -23289,10 +23286,10 @@
     </row>
     <row r="640" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C640" s="1" t="n">
         <v>4602</v>
@@ -23313,12 +23310,12 @@
         <v>17</v>
       </c>
       <c r="I640" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="641" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B641" s="1" t="s">
         <v>521</v>
@@ -23350,10 +23347,10 @@
     </row>
     <row r="642" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B642" s="1" t="s">
         <v>1076</v>
-      </c>
-      <c r="B642" s="1" t="s">
-        <v>1077</v>
       </c>
       <c r="C642" s="1" t="n">
         <v>4700</v>
@@ -23374,7 +23371,7 @@
         <v>17</v>
       </c>
       <c r="I642" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="643" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23382,7 +23379,7 @@
         <v>738</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C643" s="1" t="n">
         <v>4701</v>
@@ -23397,7 +23394,7 @@
         <v>233</v>
       </c>
       <c r="G643" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H643" s="1" t="s">
         <v>23</v>
@@ -23426,13 +23423,13 @@
         <v>233</v>
       </c>
       <c r="G644" s="21" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H644" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I644" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="645" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23440,7 +23437,7 @@
         <v>738</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C645" s="1" t="n">
         <v>4703</v>
@@ -23455,7 +23452,7 @@
         <v>92</v>
       </c>
       <c r="G645" s="21" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H645" s="1" t="s">
         <v>23</v>
@@ -23469,7 +23466,7 @@
         <v>738</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C646" s="1" t="n">
         <v>4704</v>
@@ -23484,7 +23481,7 @@
         <v>92</v>
       </c>
       <c r="G646" s="21" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H646" s="1" t="s">
         <v>23</v>
@@ -23501,8 +23498,8 @@
     <hyperlink ref="J355" r:id="rId1" location="UUID-af4a7478-4b75-68ac-cf3c-16c381335d1e" display="This value is maintained by BatteryLife. The Active SOC limit is the lower of this value, and register 2901. Also see https://www.victronenergy.com/media/pg/Energy_Storage_System/en/controlling-depth-of-discharge.html#UUID-af4a7478-4b75-68ac-cf3c-16c381335d1e"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -23526,13 +23523,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B1" s="24" t="s">
         <v>1087</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="C1" s="24" t="s">
         <v>1088</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23543,7 +23540,7 @@
         <v>257</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23554,7 +23551,7 @@
         <v>256</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23565,7 +23562,7 @@
         <v>258</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23576,7 +23573,7 @@
         <v>260</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23587,7 +23584,7 @@
         <v>261</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23598,7 +23595,7 @@
         <v>273</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23609,7 +23606,7 @@
         <v>274</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23620,7 +23617,7 @@
         <v>275</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23631,7 +23628,7 @@
         <v>276</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23642,7 +23639,7 @@
         <v>279</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23653,7 +23650,7 @@
         <v>278</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23664,7 +23661,7 @@
         <v>277</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23675,7 +23672,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23686,7 +23683,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23697,7 +23694,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23708,7 +23705,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23719,7 +23716,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23730,7 +23727,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23741,7 +23738,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23752,7 +23749,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23763,7 +23760,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23774,7 +23771,7 @@
         <v>9</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23785,7 +23782,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23796,7 +23793,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23807,7 +23804,7 @@
         <v>12</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23818,7 +23815,7 @@
         <v>20</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23829,7 +23826,7 @@
         <v>21</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23840,7 +23837,7 @@
         <v>22</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23851,7 +23848,7 @@
         <v>23</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23862,7 +23859,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23873,7 +23870,7 @@
         <v>25</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23884,7 +23881,7 @@
         <v>26</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23895,7 +23892,7 @@
         <v>27</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23906,7 +23903,7 @@
         <v>28</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23917,7 +23914,7 @@
         <v>29</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23928,7 +23925,7 @@
         <v>30</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23939,7 +23936,7 @@
         <v>31</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23950,7 +23947,7 @@
         <v>32</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23961,7 +23958,7 @@
         <v>33</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23972,7 +23969,7 @@
         <v>34</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23983,7 +23980,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23994,7 +23991,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24005,7 +24002,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24016,7 +24013,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24027,7 +24024,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24038,7 +24035,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24049,7 +24046,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24060,7 +24057,7 @@
         <v>288</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24071,7 +24068,7 @@
         <v>289</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24082,7 +24079,7 @@
         <v>290</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24093,7 +24090,7 @@
         <v>291</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24104,7 +24101,7 @@
         <v>292</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24115,7 +24112,7 @@
         <v>293</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24126,7 +24123,7 @@
         <v>294</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24137,7 +24134,7 @@
         <v>295</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24148,7 +24145,7 @@
         <v>296</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24159,12 +24156,12 @@
         <v>512</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="26" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B60" s="26"/>
       <c r="C60" s="26"/>
@@ -24174,7 +24171,7 @@
     </row>
     <row r="61" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="27" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B61" s="27"/>
       <c r="C61" s="27"/>
@@ -24188,8 +24185,8 @@
     <mergeCell ref="A61:F61"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -24213,728 +24210,728 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>1149</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>1151</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>1153</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>1155</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="22" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="22" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="22" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="22" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>1161</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="22" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="22" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>1165</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="22" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="22" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="22" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="22" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="22" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>1172</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>1174</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="22" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="22" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B22" s="22" t="s">
         <v>1178</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="22" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="22" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="22" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="22" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="22" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="22" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="22" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B30" s="22" t="s">
         <v>1187</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="22" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="22" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B33" s="22" t="s">
         <v>1191</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="22" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="22" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="22" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="22" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="22" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B40" s="22" t="s">
         <v>1199</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B41" s="22" t="s">
         <v>1201</v>
-      </c>
-      <c r="B41" s="22" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="22" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="22" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="22" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B44" s="22" t="s">
         <v>1205</v>
-      </c>
-      <c r="B44" s="22" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="22" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="22" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="22" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B47" s="22" t="s">
         <v>1209</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="22" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B48" s="22" t="s">
         <v>1211</v>
-      </c>
-      <c r="B48" s="22" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="22" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="22" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B50" s="22" t="s">
         <v>1214</v>
-      </c>
-      <c r="B50" s="22" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="22" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="22" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="22" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="22" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B55" s="22" t="s">
         <v>1220</v>
-      </c>
-      <c r="B55" s="22" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="22" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B56" s="22" t="s">
         <v>1222</v>
-      </c>
-      <c r="B56" s="22" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="22" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="22" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="22" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B59" s="22" t="s">
         <v>1226</v>
-      </c>
-      <c r="B59" s="22" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="22" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="22" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B61" s="22" t="s">
         <v>1229</v>
-      </c>
-      <c r="B61" s="22" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="22" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B62" s="22" t="s">
         <v>1231</v>
-      </c>
-      <c r="B62" s="22" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="22" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B63" s="22" t="s">
         <v>1233</v>
-      </c>
-      <c r="B63" s="22" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="22" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B64" s="22" t="s">
         <v>1235</v>
-      </c>
-      <c r="B64" s="22" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="22" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B65" s="22" t="s">
         <v>1237</v>
-      </c>
-      <c r="B65" s="22" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="22" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B66" s="22" t="s">
         <v>1239</v>
-      </c>
-      <c r="B66" s="22" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="22" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B67" s="22" t="s">
         <v>1241</v>
-      </c>
-      <c r="B67" s="22" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="22" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B68" s="22" t="s">
         <v>1243</v>
-      </c>
-      <c r="B68" s="22" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="22" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B69" s="22" t="s">
         <v>1245</v>
-      </c>
-      <c r="B69" s="22" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="22" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="22" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="22" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B72" s="22" t="s">
         <v>1249</v>
-      </c>
-      <c r="B72" s="22" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="22" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="22" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B74" s="22" t="s">
         <v>1252</v>
-      </c>
-      <c r="B74" s="22" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="22" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="22" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="22" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="22" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B78" s="22" t="s">
         <v>1257</v>
-      </c>
-      <c r="B78" s="22" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="22" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B79" s="22" t="s">
         <v>1259</v>
-      </c>
-      <c r="B79" s="22" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="22" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B80" s="22" t="s">
         <v>1261</v>
-      </c>
-      <c r="B80" s="22" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="22" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="22" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B82" s="22" t="s">
         <v>1264</v>
-      </c>
-      <c r="B82" s="22" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="22" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="22" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B84" s="22" t="s">
         <v>1267</v>
-      </c>
-      <c r="B84" s="22" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="22" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B85" s="22" t="s">
         <v>1269</v>
-      </c>
-      <c r="B85" s="22" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="22" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="22" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B87" s="22" t="s">
         <v>1272</v>
-      </c>
-      <c r="B87" s="22" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="22" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="22" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B89" s="22" t="s">
         <v>1275</v>
-      </c>
-      <c r="B89" s="22" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="22" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="22" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B91" s="22" t="s">
         <v>1278</v>
-      </c>
-      <c r="B91" s="22" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="22" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B92" s="22" t="s">
         <v>1280</v>
-      </c>
-      <c r="B92" s="22" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="22" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="22" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="22" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="22" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="22" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B97" s="22" t="s">
         <v>1286</v>
-      </c>
-      <c r="B97" s="22" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="22" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="22" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B99" s="22" t="s">
         <v>1289</v>
-      </c>
-      <c r="B99" s="22" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="22" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="22" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="22" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="22" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="22" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B104" s="22" t="s">
         <v>1295</v>
-      </c>
-      <c r="B104" s="22" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="22" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="22" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="22" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="22" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="22" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="22" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="22" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B111" s="22" t="s">
         <v>1303</v>
-      </c>
-      <c r="B111" s="22" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="22" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="22" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="22" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="22" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="22" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B117" s="22" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/CCGX-Modbus-TCP-register-list.xlsx
+++ b/CCGX-Modbus-TCP-register-list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Field list" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Unit ID mapping" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Document versions" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Field list" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Unit ID mapping" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Document versions" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -4976,7 +4976,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5066,10 +5066,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5178,17 +5174,123 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N1048576"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="8.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="26.6"/>
@@ -10432,7 +10534,7 @@
         <v>289</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="E173" s="1" t="n">
         <v>0.01</v>
@@ -16609,7 +16711,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="382" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
         <v>835</v>
       </c>
@@ -16735,7 +16837,7 @@
       <c r="A386" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="B386" s="23" t="s">
+      <c r="B386" s="22" t="s">
         <v>849</v>
       </c>
       <c r="C386" s="1" t="n">
@@ -16744,7 +16846,7 @@
       <c r="D386" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E386" s="23" t="n">
+      <c r="E386" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F386" s="3" t="s">
@@ -16764,7 +16866,7 @@
       <c r="A387" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="B387" s="23" t="s">
+      <c r="B387" s="22" t="s">
         <v>852</v>
       </c>
       <c r="C387" s="1" t="n">
@@ -16773,7 +16875,7 @@
       <c r="D387" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E387" s="23" t="n">
+      <c r="E387" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F387" s="3" t="s">
@@ -16793,7 +16895,7 @@
       <c r="A388" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="B388" s="23" t="s">
+      <c r="B388" s="22" t="s">
         <v>854</v>
       </c>
       <c r="C388" s="1" t="n">
@@ -16802,7 +16904,7 @@
       <c r="D388" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E388" s="23" t="n">
+      <c r="E388" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F388" s="3" t="s">
@@ -16818,7 +16920,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
         <v>835</v>
       </c>
@@ -16831,7 +16933,7 @@
       <c r="D389" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E389" s="23" t="n">
+      <c r="E389" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F389" s="3" t="s">
@@ -17198,7 +17300,7 @@
       <c r="H401" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I401" s="24"/>
+      <c r="I401" s="23"/>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
@@ -27749,19 +27851,19 @@
       <c r="B773" s="1" t="s">
         <v>1229</v>
       </c>
-      <c r="C773" s="25" t="n">
+      <c r="C773" s="24" t="n">
         <v>5200</v>
       </c>
-      <c r="D773" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E773" s="25" t="n">
+      <c r="D773" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E773" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F773" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="G773" s="25" t="s">
+      <c r="G773" s="24" t="s">
         <v>898</v>
       </c>
       <c r="H773" s="1" t="s">
@@ -27775,19 +27877,19 @@
       <c r="B774" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="C774" s="25" t="n">
+      <c r="C774" s="24" t="n">
         <v>5201</v>
       </c>
-      <c r="D774" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E774" s="25" t="n">
+      <c r="D774" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E774" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F774" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="G774" s="25" t="s">
+      <c r="G774" s="24" t="s">
         <v>974</v>
       </c>
       <c r="H774" s="1" t="s">
@@ -27801,19 +27903,19 @@
       <c r="B775" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="C775" s="25" t="n">
+      <c r="C775" s="24" t="n">
         <v>5202</v>
       </c>
-      <c r="D775" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E775" s="25" t="n">
+      <c r="D775" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E775" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F775" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="G775" s="25" t="s">
+      <c r="G775" s="24" t="s">
         <v>564</v>
       </c>
       <c r="H775" s="1" t="s">
@@ -27827,19 +27929,19 @@
       <c r="B776" s="1" t="s">
         <v>1211</v>
       </c>
-      <c r="C776" s="25" t="n">
+      <c r="C776" s="24" t="n">
         <v>5203</v>
       </c>
-      <c r="D776" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E776" s="25" t="n">
+      <c r="D776" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E776" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F776" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="G776" s="25" t="s">
+      <c r="G776" s="24" t="s">
         <v>978</v>
       </c>
       <c r="H776" s="1" t="s">
@@ -27853,19 +27955,19 @@
       <c r="B777" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="C777" s="25" t="n">
+      <c r="C777" s="24" t="n">
         <v>5204</v>
       </c>
-      <c r="D777" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E777" s="25" t="n">
+      <c r="D777" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E777" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F777" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="G777" s="25" t="s">
+      <c r="G777" s="24" t="s">
         <v>994</v>
       </c>
       <c r="H777" s="1" t="s">
@@ -27882,19 +27984,19 @@
       <c r="B778" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="C778" s="25" t="n">
+      <c r="C778" s="24" t="n">
         <v>5205</v>
       </c>
-      <c r="D778" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E778" s="25" t="n">
+      <c r="D778" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E778" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F778" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G778" s="25" t="s">
+      <c r="G778" s="24" t="s">
         <v>213</v>
       </c>
       <c r="H778" s="1" t="s">
@@ -27911,19 +28013,19 @@
       <c r="B779" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="C779" s="25" t="n">
+      <c r="C779" s="24" t="n">
         <v>5206</v>
       </c>
-      <c r="D779" s="25" t="s">
+      <c r="D779" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E779" s="25" t="n">
+      <c r="E779" s="24" t="n">
         <v>10</v>
       </c>
       <c r="F779" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G779" s="25" t="s">
+      <c r="G779" s="24" t="s">
         <v>215</v>
       </c>
       <c r="H779" s="1" t="s">
@@ -27937,22 +28039,22 @@
       <c r="A780" s="22" t="s">
         <v>1228</v>
       </c>
-      <c r="B780" s="25" t="s">
+      <c r="B780" s="24" t="s">
         <v>979</v>
       </c>
-      <c r="C780" s="25" t="n">
+      <c r="C780" s="24" t="n">
         <v>5207</v>
       </c>
-      <c r="D780" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E780" s="25" t="n">
+      <c r="D780" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E780" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F780" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="G780" s="25" t="s">
+      <c r="G780" s="24" t="s">
         <v>980</v>
       </c>
       <c r="H780" s="1" t="s">
@@ -27969,19 +28071,19 @@
       <c r="B781" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="C781" s="25" t="n">
+      <c r="C781" s="24" t="n">
         <v>5208</v>
       </c>
-      <c r="D781" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E781" s="25" t="n">
+      <c r="D781" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E781" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F781" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="G781" s="25" t="s">
+      <c r="G781" s="24" t="s">
         <v>982</v>
       </c>
       <c r="H781" s="1" t="s">
@@ -27998,19 +28100,19 @@
       <c r="B782" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="C782" s="25" t="n">
+      <c r="C782" s="24" t="n">
         <v>5209</v>
       </c>
-      <c r="D782" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E782" s="25" t="s">
+      <c r="D782" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E782" s="24" t="s">
         <v>1235</v>
       </c>
       <c r="F782" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="G782" s="25" t="s">
+      <c r="G782" s="24" t="s">
         <v>984</v>
       </c>
       <c r="H782" s="1" t="s">
@@ -28024,22 +28126,22 @@
       <c r="A783" s="22" t="s">
         <v>1228</v>
       </c>
-      <c r="B783" s="25" t="s">
+      <c r="B783" s="24" t="s">
         <v>985</v>
       </c>
-      <c r="C783" s="25" t="n">
+      <c r="C783" s="24" t="n">
         <v>5210</v>
       </c>
-      <c r="D783" s="25" t="s">
+      <c r="D783" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E783" s="25" t="n">
+      <c r="E783" s="24" t="n">
         <v>10</v>
       </c>
       <c r="F783" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G783" s="25" t="s">
+      <c r="G783" s="24" t="s">
         <v>986</v>
       </c>
       <c r="H783" s="1" t="s">
@@ -28053,22 +28155,22 @@
       <c r="A784" s="22" t="s">
         <v>1228</v>
       </c>
-      <c r="B784" s="25" t="s">
+      <c r="B784" s="24" t="s">
         <v>1237</v>
       </c>
-      <c r="C784" s="25" t="n">
+      <c r="C784" s="24" t="n">
         <v>5211</v>
       </c>
-      <c r="D784" s="25" t="s">
+      <c r="D784" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E784" s="25" t="n">
+      <c r="E784" s="24" t="n">
         <v>10</v>
       </c>
       <c r="F784" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G784" s="25" t="s">
+      <c r="G784" s="24" t="s">
         <v>988</v>
       </c>
       <c r="H784" s="1" t="s">
@@ -28082,22 +28184,22 @@
       <c r="A785" s="22" t="s">
         <v>1228</v>
       </c>
-      <c r="B785" s="25" t="s">
+      <c r="B785" s="24" t="s">
         <v>989</v>
       </c>
-      <c r="C785" s="25" t="n">
+      <c r="C785" s="24" t="n">
         <v>5212</v>
       </c>
-      <c r="D785" s="25" t="s">
+      <c r="D785" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E785" s="25" t="n">
+      <c r="E785" s="24" t="n">
         <v>10</v>
       </c>
       <c r="F785" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G785" s="25" t="s">
+      <c r="G785" s="24" t="s">
         <v>990</v>
       </c>
       <c r="H785" s="1" t="s">
@@ -28111,22 +28213,22 @@
       <c r="A786" s="22" t="s">
         <v>1228</v>
       </c>
-      <c r="B786" s="25" t="s">
+      <c r="B786" s="24" t="s">
         <v>400</v>
       </c>
-      <c r="C786" s="25" t="n">
+      <c r="C786" s="24" t="n">
         <v>5213</v>
       </c>
-      <c r="D786" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E786" s="25" t="n">
+      <c r="D786" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E786" s="24" t="n">
         <v>100</v>
       </c>
       <c r="F786" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G786" s="25" t="s">
+      <c r="G786" s="24" t="s">
         <v>992</v>
       </c>
       <c r="H786" s="1" t="s">
@@ -28143,19 +28245,19 @@
       <c r="B787" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="C787" s="25" t="n">
+      <c r="C787" s="24" t="n">
         <v>5214</v>
       </c>
-      <c r="D787" s="25" t="s">
+      <c r="D787" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E787" s="25" t="n">
+      <c r="E787" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F787" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G787" s="25" t="s">
+      <c r="G787" s="24" t="s">
         <v>998</v>
       </c>
       <c r="H787" s="1" t="s">
@@ -28169,22 +28271,22 @@
       <c r="A788" s="22" t="s">
         <v>1228</v>
       </c>
-      <c r="B788" s="25" t="s">
+      <c r="B788" s="24" t="s">
         <v>1234</v>
       </c>
-      <c r="C788" s="25" t="n">
+      <c r="C788" s="24" t="n">
         <v>5215</v>
       </c>
-      <c r="D788" s="25" t="s">
+      <c r="D788" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E788" s="25" t="n">
+      <c r="E788" s="24" t="n">
         <v>10</v>
       </c>
       <c r="F788" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G788" s="25" t="s">
+      <c r="G788" s="24" t="s">
         <v>1238</v>
       </c>
       <c r="H788" s="1" t="s">
@@ -28201,19 +28303,19 @@
       <c r="B789" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="C789" s="25" t="n">
+      <c r="C789" s="24" t="n">
         <v>5216</v>
       </c>
-      <c r="D789" s="25" t="s">
+      <c r="D789" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E789" s="25" t="n">
+      <c r="E789" s="24" t="n">
         <v>1</v>
       </c>
       <c r="F789" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G789" s="25" t="s">
+      <c r="G789" s="24" t="s">
         <v>1001</v>
       </c>
       <c r="H789" s="1" t="s">
@@ -28227,19 +28329,19 @@
       <c r="A790" s="22" t="s">
         <v>1228</v>
       </c>
-      <c r="B790" s="25" t="s">
+      <c r="B790" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="C790" s="25" t="n">
+      <c r="C790" s="24" t="n">
         <v>5217</v>
       </c>
-      <c r="D790" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E790" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G790" s="25" t="s">
+      <c r="D790" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E790" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G790" s="24" t="s">
         <v>130</v>
       </c>
       <c r="H790" s="1" t="s">
@@ -28253,16 +28355,16 @@
       <c r="B791" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="C791" s="25" t="n">
+      <c r="C791" s="24" t="n">
         <v>5218</v>
       </c>
-      <c r="D791" s="25" t="s">
+      <c r="D791" s="24" t="s">
         <v>1003</v>
       </c>
-      <c r="E791" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G791" s="25" t="s">
+      <c r="E791" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G791" s="24" t="s">
         <v>1005</v>
       </c>
       <c r="H791" s="1" t="s">
@@ -28279,16 +28381,16 @@
       <c r="B792" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="C792" s="25" t="n">
+      <c r="C792" s="24" t="n">
         <v>5234</v>
       </c>
-      <c r="D792" s="25" t="s">
+      <c r="D792" s="24" t="s">
         <v>1003</v>
       </c>
-      <c r="E792" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G792" s="25" t="s">
+      <c r="E792" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G792" s="24" t="s">
         <v>1008</v>
       </c>
       <c r="H792" s="1" t="s">
@@ -28302,16 +28404,16 @@
       <c r="B793" s="1" t="s">
         <v>1009</v>
       </c>
-      <c r="C793" s="25" t="n">
+      <c r="C793" s="24" t="n">
         <v>5250</v>
       </c>
-      <c r="D793" s="25" t="s">
+      <c r="D793" s="24" t="s">
         <v>1003</v>
       </c>
-      <c r="E793" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G793" s="25" t="s">
+      <c r="E793" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G793" s="24" t="s">
         <v>1010</v>
       </c>
       <c r="H793" s="1" t="s">
@@ -28325,16 +28427,16 @@
       <c r="B794" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="C794" s="25" t="n">
+      <c r="C794" s="24" t="n">
         <v>5266</v>
       </c>
-      <c r="D794" s="25" t="s">
+      <c r="D794" s="24" t="s">
         <v>1003</v>
       </c>
-      <c r="E794" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G794" s="25" t="s">
+      <c r="E794" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G794" s="24" t="s">
         <v>1012</v>
       </c>
       <c r="H794" s="1" t="s">
@@ -28348,16 +28450,16 @@
       <c r="B795" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="C795" s="25" t="n">
+      <c r="C795" s="24" t="n">
         <v>5282</v>
       </c>
-      <c r="D795" s="25" t="s">
+      <c r="D795" s="24" t="s">
         <v>1003</v>
       </c>
-      <c r="E795" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G795" s="25" t="s">
+      <c r="E795" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G795" s="24" t="s">
         <v>1014</v>
       </c>
       <c r="H795" s="1" t="s">
@@ -28371,16 +28473,16 @@
       <c r="B796" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="C796" s="25" t="n">
+      <c r="C796" s="24" t="n">
         <v>5298</v>
       </c>
-      <c r="D796" s="25" t="s">
+      <c r="D796" s="24" t="s">
         <v>1003</v>
       </c>
-      <c r="E796" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G796" s="25" t="s">
+      <c r="E796" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G796" s="24" t="s">
         <v>1016</v>
       </c>
       <c r="H796" s="1" t="s">
@@ -28394,16 +28496,16 @@
       <c r="B797" s="1" t="s">
         <v>1017</v>
       </c>
-      <c r="C797" s="25" t="n">
+      <c r="C797" s="24" t="n">
         <v>5314</v>
       </c>
-      <c r="D797" s="25" t="s">
+      <c r="D797" s="24" t="s">
         <v>1003</v>
       </c>
-      <c r="E797" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G797" s="25" t="s">
+      <c r="E797" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G797" s="24" t="s">
         <v>1018</v>
       </c>
       <c r="H797" s="1" t="s">
@@ -28417,16 +28519,16 @@
       <c r="B798" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="C798" s="25" t="n">
+      <c r="C798" s="24" t="n">
         <v>5330</v>
       </c>
-      <c r="D798" s="25" t="s">
+      <c r="D798" s="24" t="s">
         <v>1003</v>
       </c>
-      <c r="E798" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G798" s="25" t="s">
+      <c r="E798" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G798" s="24" t="s">
         <v>1020</v>
       </c>
       <c r="H798" s="1" t="s">
@@ -28437,7 +28539,7 @@
       <c r="A799" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B799" s="25" t="s">
+      <c r="B799" s="24" t="s">
         <v>1239</v>
       </c>
       <c r="C799" s="1" t="n">
@@ -28524,7 +28626,7 @@
       <c r="A802" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B802" s="26" t="s">
+      <c r="B802" s="25" t="s">
         <v>1248</v>
       </c>
       <c r="C802" s="1" t="n">
@@ -28968,8 +29070,8 @@
     <hyperlink ref="I791" r:id="rId3" location="error-codes" display="See https://github.com/victronenergy/venus/wiki/dbus#error-codes"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -28978,27 +29080,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F1048576"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="7.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="7.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="22" width="65.01"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="4" style="22" width="8.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>1284</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>1285</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>1286</v>
       </c>
     </row>
@@ -29166,24 +29268,24 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="n">
+      <c r="A22" s="27" t="n">
         <v>223</v>
       </c>
-      <c r="B22" s="28" t="n">
+      <c r="B22" s="27" t="n">
         <v>277</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="27" t="s">
         <v>1288</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="n">
+      <c r="A23" s="27" t="n">
         <v>224</v>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="27" t="n">
         <v>278</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="27" t="s">
         <v>1289</v>
       </c>
     </row>
@@ -29199,57 +29301,57 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="n">
+      <c r="A25" s="27" t="n">
         <v>226</v>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="27" t="n">
         <v>279</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="27" t="s">
         <v>1291</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="n">
+      <c r="A26" s="27" t="n">
         <v>227</v>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="27" t="n">
         <v>276</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>1292</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28" t="n">
+      <c r="A27" s="27" t="n">
         <v>228</v>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="27" t="n">
         <v>275</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="27" t="s">
         <v>1293</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="28" t="n">
+      <c r="A28" s="27" t="n">
         <v>229</v>
       </c>
-      <c r="B28" s="28" t="n">
+      <c r="B28" s="27" t="n">
         <v>274</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="27" t="s">
         <v>1294</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="28" t="n">
+      <c r="A29" s="27" t="n">
         <v>230</v>
       </c>
-      <c r="B29" s="28" t="n">
+      <c r="B29" s="27" t="n">
         <v>273</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="27" t="s">
         <v>1295</v>
       </c>
     </row>
@@ -29353,35 +29455,35 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="28" t="n">
+      <c r="A39" s="27" t="n">
         <v>242</v>
       </c>
-      <c r="B39" s="28" t="n">
+      <c r="B39" s="27" t="n">
         <v>261</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="27" t="s">
         <v>1305</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="28" t="n">
+      <c r="A40" s="27" t="n">
         <v>243</v>
       </c>
-      <c r="B40" s="28" t="n">
+      <c r="B40" s="27" t="n">
         <v>260</v>
       </c>
-      <c r="C40" s="28" t="s">
+      <c r="C40" s="27" t="s">
         <v>1306</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="28" t="n">
+      <c r="A41" s="27" t="n">
         <v>244</v>
       </c>
-      <c r="B41" s="28" t="n">
-        <v>259</v>
-      </c>
-      <c r="C41" s="28"/>
+      <c r="B41" s="27" t="n">
+        <v>259</v>
+      </c>
+      <c r="C41" s="27"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="n">
@@ -29390,7 +29492,7 @@
       <c r="B42" s="22" t="n">
         <v>258</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C42" s="27" t="s">
         <v>1307</v>
       </c>
     </row>
@@ -29417,24 +29519,24 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="28" t="s">
         <v>1310</v>
       </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
     </row>
     <row r="47" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="29" t="s">
         <v>1311</v>
       </c>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
     </row>
     <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -29456,8 +29558,8 @@
     <mergeCell ref="A47:F47"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -29466,12 +29568,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C1048576"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="8.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="3.43"/>
@@ -29703,7 +29805,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="54.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="30" t="s">
         <v>1361</v>
       </c>
     </row>
@@ -30407,8 +30509,8 @@
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/CCGX-Modbus-TCP-register-list.xlsx
+++ b/CCGX-Modbus-TCP-register-list.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6798" uniqueCount="1691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6798" uniqueCount="1692">
   <si>
     <t xml:space="preserve">NOTE: Use unit-id 100 for the com.victronenergy.system data, for more information see FAQ.</t>
   </si>
@@ -4531,6 +4531,9 @@
   </si>
   <si>
     <t xml:space="preserve">/Settings/DynamicEss/Schedule/0/Restrictions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0=No restrictions between battery and the grid;1=Battery to grid energy flow is restricted;2=Grid to battery energy flow is restricted;3=No energy flow between battery and grid</t>
   </si>
   <si>
     <t xml:space="preserve">Target SOC for this schedule</t>
@@ -5866,7 +5869,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N960"/>
-  <sheetFormatPr defaultColWidth="9.01171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.01171875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.43"/>
@@ -5893,7 +5896,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="9"/>
     </row>
-    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
@@ -20038,7 +20041,7 @@
       </c>
       <c r="J479" s="21"/>
     </row>
-    <row r="480" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="21" t="s">
         <v>912</v>
       </c>
@@ -22844,7 +22847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="579" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="579" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="s">
         <v>1069</v>
       </c>
@@ -22870,7 +22873,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="580" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="580" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
         <v>1069</v>
       </c>
@@ -22893,7 +22896,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="581" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="581" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
         <v>1069</v>
       </c>
@@ -22916,7 +22919,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="582" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="582" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
         <v>1069</v>
       </c>
@@ -22939,7 +22942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="583" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="583" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
         <v>1069</v>
       </c>
@@ -22962,7 +22965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="584" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="584" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
         <v>1069</v>
       </c>
@@ -22985,7 +22988,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="585" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="585" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
         <v>1069</v>
       </c>
@@ -23008,7 +23011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="586" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="586" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="s">
         <v>1069</v>
       </c>
@@ -23292,7 +23295,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="596" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="596" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
         <v>1132</v>
       </c>
@@ -23324,7 +23327,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="597" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="597" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
         <v>1132</v>
       </c>
@@ -23356,7 +23359,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="598" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="598" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
         <v>1132</v>
       </c>
@@ -23385,7 +23388,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="599" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="599" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
         <v>1132</v>
       </c>
@@ -23417,7 +23420,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="600" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="600" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="s">
         <v>1132</v>
       </c>
@@ -32316,7 +32319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="921" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="921" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A921" s="22" t="s">
         <v>1363</v>
       </c>
@@ -32342,7 +32345,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="922" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="922" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A922" s="22" t="s">
         <v>1363</v>
       </c>
@@ -32365,7 +32368,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="923" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="923" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A923" s="22" t="s">
         <v>1363</v>
       </c>
@@ -32388,7 +32391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="924" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="924" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A924" s="22" t="s">
         <v>1363</v>
       </c>
@@ -32411,7 +32414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="925" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="925" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A925" s="22" t="s">
         <v>1363</v>
       </c>
@@ -32434,7 +32437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="926" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="926" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A926" s="22" t="s">
         <v>1363</v>
       </c>
@@ -32457,7 +32460,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="927" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="927" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A927" s="22" t="s">
         <v>1363</v>
       </c>
@@ -32480,7 +32483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="928" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="928" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A928" s="22" t="s">
         <v>1363</v>
       </c>
@@ -32590,7 +32593,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="932" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="932" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A932" s="1" t="s">
         <v>12</v>
       </c>
@@ -32932,7 +32935,7 @@
         <v>23</v>
       </c>
       <c r="I943" s="1" t="s">
-        <v>1390</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="944" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32940,7 +32943,7 @@
         <v>912</v>
       </c>
       <c r="B944" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="C944" s="1" t="n">
         <v>5427</v>
@@ -32955,7 +32958,7 @@
         <v>264</v>
       </c>
       <c r="G944" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H944" s="1" t="s">
         <v>23</v>
@@ -32969,7 +32972,7 @@
         <v>912</v>
       </c>
       <c r="B945" s="1" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C945" s="1" t="n">
         <v>5428</v>
@@ -32984,7 +32987,7 @@
         <v>140</v>
       </c>
       <c r="G945" s="1" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H945" s="1" t="s">
         <v>23</v>
@@ -32995,7 +32998,7 @@
         <v>912</v>
       </c>
       <c r="B946" s="1" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="C946" s="1" t="n">
         <v>5429</v>
@@ -33010,7 +33013,7 @@
         <v>264</v>
       </c>
       <c r="G946" s="1" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H946" s="1" t="s">
         <v>23</v>
@@ -33021,7 +33024,7 @@
     </row>
     <row r="947" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A947" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B947" s="1" t="s">
         <v>1006</v>
@@ -33047,10 +33050,10 @@
     </row>
     <row r="948" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A948" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B948" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="C948" s="1" t="n">
         <v>5501</v>
@@ -33071,15 +33074,15 @@
         <v>17</v>
       </c>
       <c r="I948" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="949" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A949" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B949" s="1" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="C949" s="1" t="n">
         <v>5502</v>
@@ -33105,7 +33108,7 @@
     </row>
     <row r="950" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A950" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B950" s="1" t="s">
         <v>1271</v>
@@ -33134,10 +33137,10 @@
     </row>
     <row r="951" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A951" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B951" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="C951" s="1" t="n">
         <v>5506</v>
@@ -33163,10 +33166,10 @@
     </row>
     <row r="952" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A952" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B952" s="1" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="C952" s="1" t="n">
         <v>5507</v>
@@ -33181,7 +33184,7 @@
         <v>94</v>
       </c>
       <c r="G952" s="1" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H952" s="1" t="s">
         <v>17</v>
@@ -33192,10 +33195,10 @@
     </row>
     <row r="953" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A953" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B953" s="27" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="C953" s="1" t="n">
         <v>5800</v>
@@ -33210,21 +33213,21 @@
         <v>264</v>
       </c>
       <c r="G953" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H953" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I953" s="1" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="954" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A954" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B954" s="1" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C954" s="1" t="n">
         <v>5801</v>
@@ -33239,21 +33242,21 @@
         <v>264</v>
       </c>
       <c r="G954" s="1" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H954" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I954" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="955" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A955" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B955" s="1" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C955" s="1" t="n">
         <v>5802</v>
@@ -33268,32 +33271,32 @@
         <v>264</v>
       </c>
       <c r="G955" s="1" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H955" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I955" s="1" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="956" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A956" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B956" s="27" t="s">
         <v>134</v>
       </c>
       <c r="C956" s="28" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="957" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A957" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B957" s="27" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="C957" s="1" t="n">
         <v>5810</v>
@@ -33308,21 +33311,21 @@
         <v>264</v>
       </c>
       <c r="G957" s="1" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H957" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I957" s="1" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="958" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A958" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B958" s="1" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C958" s="1" t="n">
         <v>5811</v>
@@ -33337,21 +33340,21 @@
         <v>264</v>
       </c>
       <c r="G958" s="1" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H958" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I958" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="959" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A959" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B959" s="1" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C959" s="1" t="n">
         <v>5812</v>
@@ -33366,24 +33369,24 @@
         <v>264</v>
       </c>
       <c r="G959" s="1" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H959" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I959" s="1" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="960" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A960" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B960" s="27" t="s">
         <v>134</v>
       </c>
       <c r="C960" s="28" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
   </sheetData>
@@ -33411,7 +33414,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F1048576"/>
-  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="8.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="16"/>
@@ -33421,7 +33424,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="29" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -33431,7 +33434,7 @@
     </row>
     <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -33446,7 +33449,7 @@
     </row>
     <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -33466,13 +33469,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33483,7 +33486,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33646,7 +33649,7 @@
         <v>277</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33657,7 +33660,7 @@
         <v>278</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33668,7 +33671,7 @@
         <v>512</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33679,7 +33682,7 @@
         <v>279</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33690,7 +33693,7 @@
         <v>276</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33701,7 +33704,7 @@
         <v>275</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33712,7 +33715,7 @@
         <v>274</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33723,7 +33726,7 @@
         <v>273</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33734,7 +33737,7 @@
         <v>295</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33745,7 +33748,7 @@
         <v>294</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33756,7 +33759,7 @@
         <v>293</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33767,7 +33770,7 @@
         <v>296</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33778,7 +33781,7 @@
         <v>292</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33789,7 +33792,7 @@
         <v>291</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33800,7 +33803,7 @@
         <v>290</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33811,7 +33814,7 @@
         <v>289</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33822,7 +33825,7 @@
         <v>288</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33833,7 +33836,7 @@
         <v>261</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33844,7 +33847,7 @@
         <v>260</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33864,7 +33867,7 @@
         <v>258</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33875,7 +33878,7 @@
         <v>257</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33886,7 +33889,7 @@
         <v>256</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -33921,7 +33924,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C169"/>
-  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="8.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="3.43"/>
@@ -33931,1006 +33934,1006 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="22" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="22" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="22" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="22" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="22" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="22" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="22" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="22" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="22" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="22" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="22" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="22" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="22" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="22" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="22" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="22" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="22" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="22" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="22" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="22" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="22" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="22" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="22" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="22" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="22" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="22" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="22" t="s">
-        <v>1518</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="55.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="32" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="22" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="22" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="22" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="22" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="22" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="22" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="22" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="22" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="22" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="22" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="22" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="22" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="22" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="22" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="22" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="22" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="22" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="22" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="22" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="22" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="22" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="22" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="22" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="22" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="22" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="22" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="22" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="22" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="22" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="22" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="22" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="22" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="22" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="22" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="22" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="22" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="22" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="22" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="22" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="22" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="22" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="22" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="22" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="22" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="22" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="22" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="22" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="22" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="22" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B91" s="22" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="22" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="22" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="22" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="22" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="22" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="22" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="22" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="22" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B99" s="22" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="22" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="22" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="22" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="22" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="22" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B104" s="22" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="22" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="22" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="22" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="22" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="22" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="22" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="22" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B111" s="22" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="22" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="22" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="22" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="22" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="22" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B117" s="22" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B118" s="22" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="22" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B119" s="22" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="22" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="22" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="22" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="22" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="22" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="22" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="22" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="22" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="22" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="22" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="22" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="22" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="22" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="22" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="22" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="22" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B135" s="22" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="22" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="22" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="22" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="22" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B139" s="22" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="22" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="22" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="22" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="22" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="22" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="22" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="22" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="22" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B147" s="22" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="22" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="22" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B150" s="22" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="22" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="22" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B153" s="22" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="22" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B155" s="22" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B156" s="22" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B157" s="22" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="22" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B158" s="22" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="22" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B160" s="22" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B161" s="22" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="22" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="22" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B163" s="22" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="22" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="22" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="22" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B167" s="22" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B168" s="22" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="22" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B169" s="22" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
   </sheetData>

--- a/CCGX-Modbus-TCP-register-list.xlsx
+++ b/CCGX-Modbus-TCP-register-list.xlsx
@@ -33476,7 +33476,7 @@
         <v>1442</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>5429</v>
+        <v>5430</v>
       </c>
       <c r="D962" s="29" t="s">
         <v>20</v>

--- a/CCGX-Modbus-TCP-register-list.xlsx
+++ b/CCGX-Modbus-TCP-register-list.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6890" uniqueCount="1720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6899" uniqueCount="1722">
   <si>
     <t xml:space="preserve">NOTE: Use unit-id 100 for the com.victronenergy.system data, for more information see FAQ.</t>
   </si>
@@ -4041,7 +4041,10 @@
     <t xml:space="preserve">0=Manual;1=Auto</t>
   </si>
   <si>
-    <t xml:space="preserve">Energy consumed by charger</t>
+    <t xml:space="preserve">Session Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Session/Energy</t>
   </si>
   <si>
     <t xml:space="preserve">Total power</t>
@@ -4080,12 +4083,6 @@
     <t xml:space="preserve">/Session/Time</t>
   </si>
   <si>
-    <t xml:space="preserve">Session Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Session/Energy</t>
-  </si>
-  <si>
     <t xml:space="preserve">Session Cost</t>
   </si>
   <si>
@@ -4099,6 +4096,9 @@
   </si>
   <si>
     <t xml:space="preserve">/Session/SavedCost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total energy consumed by charger</t>
   </si>
   <si>
     <t xml:space="preserve">com.victronenergy.acload</t>
@@ -5458,6 +5458,12 @@
   </si>
   <si>
     <t xml:space="preserve">Add registers for VE.Bus Nominal inverter power (registers 130 to 136)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make Register 3816 reflect session enery as in the past</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add register 3836 for total EV Charger energy</t>
   </si>
 </sst>
 </file>
@@ -5968,7 +5974,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N976"/>
+  <dimension ref="A1:N977"/>
   <sheetFormatPr defaultColWidth="9.01171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.02"/>
@@ -24628,7 +24634,7 @@
         <v>1059</v>
       </c>
       <c r="G641" s="1" t="s">
-        <v>915</v>
+        <v>1250</v>
       </c>
       <c r="H641" s="1" t="s">
         <v>17</v>
@@ -24729,7 +24735,7 @@
         <v>1243</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="C645" s="1" t="n">
         <v>3821</v>
@@ -24758,7 +24764,7 @@
         <v>1243</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C646" s="1" t="n">
         <v>3822</v>
@@ -24773,7 +24779,7 @@
         <v>323</v>
       </c>
       <c r="G646" s="1" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H646" s="1" t="s">
         <v>17</v>
@@ -24787,7 +24793,7 @@
         <v>1243</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C647" s="1" t="n">
         <v>3823</v>
@@ -24802,7 +24808,7 @@
         <v>264</v>
       </c>
       <c r="G647" s="1" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H647" s="1" t="s">
         <v>17</v>
@@ -24837,7 +24843,7 @@
         <v>17</v>
       </c>
       <c r="I648" s="1" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="649" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24845,7 +24851,7 @@
         <v>1243</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C649" s="1" t="n">
         <v>3825</v>
@@ -24860,7 +24866,7 @@
         <v>264</v>
       </c>
       <c r="G649" s="1" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H649" s="1" t="s">
         <v>23</v>
@@ -24874,7 +24880,7 @@
         <v>1243</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C650" s="1" t="n">
         <v>3826</v>
@@ -24889,7 +24895,7 @@
         <v>264</v>
       </c>
       <c r="G650" s="1" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H650" s="1" t="s">
         <v>23</v>
@@ -24932,7 +24938,7 @@
         <v>1243</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="C652" s="1" t="n">
         <v>3828</v>
@@ -24947,7 +24953,7 @@
         <v>723</v>
       </c>
       <c r="G652" s="1" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H652" s="1" t="s">
         <v>17</v>
@@ -24961,7 +24967,7 @@
         <v>1243</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>1262</v>
+        <v>1249</v>
       </c>
       <c r="C653" s="1" t="n">
         <v>3830</v>
@@ -24976,7 +24982,7 @@
         <v>1059</v>
       </c>
       <c r="G653" s="1" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="H653" s="1" t="s">
         <v>17</v>
@@ -24990,7 +24996,7 @@
         <v>1243</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C654" s="1" t="n">
         <v>3832</v>
@@ -25002,10 +25008,10 @@
         <v>100</v>
       </c>
       <c r="F654" s="28" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G654" s="1" t="s">
         <v>1265</v>
-      </c>
-      <c r="G654" s="1" t="s">
-        <v>1266</v>
       </c>
       <c r="H654" s="1" t="s">
         <v>17</v>
@@ -25016,7 +25022,7 @@
         <v>1243</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C655" s="1" t="n">
         <v>3834</v>
@@ -25028,10 +25034,10 @@
         <v>100</v>
       </c>
       <c r="F655" s="28" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G655" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H655" s="1" t="s">
         <v>17</v>
@@ -25039,31 +25045,31 @@
     </row>
     <row r="656" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="s">
-        <v>1269</v>
+        <v>1243</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>749</v>
+        <v>1268</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>3900</v>
+        <v>3836</v>
       </c>
       <c r="D656" s="2" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F656" s="3" t="s">
-        <v>264</v>
+        <v>1059</v>
       </c>
       <c r="G656" s="1" t="s">
-        <v>750</v>
+        <v>915</v>
       </c>
       <c r="H656" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I656" s="1" t="s">
-        <v>31</v>
+        <v>348</v>
       </c>
     </row>
     <row r="657" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25071,10 +25077,10 @@
         <v>1269</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="D657" s="2" t="s">
         <v>20</v>
@@ -25086,7 +25092,7 @@
         <v>264</v>
       </c>
       <c r="G657" s="1" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="H657" s="1" t="s">
         <v>17</v>
@@ -25100,10 +25106,10 @@
         <v>1269</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="D658" s="2" t="s">
         <v>20</v>
@@ -25115,7 +25121,7 @@
         <v>264</v>
       </c>
       <c r="G658" s="1" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="H658" s="1" t="s">
         <v>17</v>
@@ -25129,19 +25135,28 @@
         <v>1269</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1270</v>
+        <v>767</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="D659" s="2" t="s">
-        <v>773</v>
+        <v>20</v>
+      </c>
+      <c r="E659" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F659" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="G659" s="1" t="s">
-        <v>16</v>
+        <v>768</v>
       </c>
       <c r="H659" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="I659" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="660" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25149,28 +25164,19 @@
         <v>1269</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>745</v>
+        <v>1270</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>3910</v>
+        <v>3903</v>
       </c>
       <c r="D660" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E660" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F660" s="3" t="s">
-        <v>89</v>
+        <v>773</v>
       </c>
       <c r="G660" s="1" t="s">
-        <v>746</v>
+        <v>16</v>
       </c>
       <c r="H660" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I660" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="661" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25178,28 +25184,28 @@
         <v>1269</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="D661" s="2" t="s">
-        <v>1271</v>
+        <v>20</v>
       </c>
       <c r="E661" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F661" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G661" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="H661" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I661" s="1" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
     </row>
     <row r="662" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25207,28 +25213,28 @@
         <v>1269</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>3912</v>
+        <v>3911</v>
       </c>
       <c r="D662" s="2" t="s">
-        <v>20</v>
+        <v>1271</v>
       </c>
       <c r="E662" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F662" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G662" s="1" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="H662" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I662" s="1" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
     </row>
     <row r="663" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25236,28 +25242,28 @@
         <v>1269</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="D663" s="2" t="s">
-        <v>1271</v>
+        <v>20</v>
       </c>
       <c r="E663" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F663" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G663" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="H663" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I663" s="1" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
     </row>
     <row r="664" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25265,28 +25271,28 @@
         <v>1269</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="D664" s="2" t="s">
-        <v>20</v>
+        <v>1271</v>
       </c>
       <c r="E664" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F664" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G664" s="1" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="H664" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I664" s="1" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
     </row>
     <row r="665" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25294,28 +25300,28 @@
         <v>1269</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>3915</v>
+        <v>3914</v>
       </c>
       <c r="D665" s="2" t="s">
-        <v>1271</v>
+        <v>20</v>
       </c>
       <c r="E665" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F665" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G665" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="H665" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I665" s="1" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
     </row>
     <row r="666" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25323,28 +25329,28 @@
         <v>1269</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>3916</v>
+        <v>3915</v>
       </c>
       <c r="D666" s="2" t="s">
-        <v>155</v>
+        <v>1271</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F666" s="3" t="s">
-        <v>1059</v>
+        <v>94</v>
       </c>
       <c r="G666" s="1" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="H666" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I666" s="1" t="s">
-        <v>348</v>
+        <v>207</v>
       </c>
     </row>
     <row r="667" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25352,10 +25358,10 @@
         <v>1269</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>3918</v>
+        <v>3916</v>
       </c>
       <c r="D667" s="2" t="s">
         <v>155</v>
@@ -25367,7 +25373,7 @@
         <v>1059</v>
       </c>
       <c r="G667" s="1" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="H667" s="1" t="s">
         <v>17</v>
@@ -25381,10 +25387,10 @@
         <v>1269</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>3920</v>
+        <v>3918</v>
       </c>
       <c r="D668" s="2" t="s">
         <v>155</v>
@@ -25396,7 +25402,7 @@
         <v>1059</v>
       </c>
       <c r="G668" s="1" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="H668" s="1" t="s">
         <v>17</v>
@@ -25410,28 +25416,28 @@
         <v>1269</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>3922</v>
+        <v>3920</v>
       </c>
       <c r="D669" s="2" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="E669" s="1" t="n">
         <v>100</v>
       </c>
       <c r="F669" s="3" t="s">
-        <v>217</v>
+        <v>1059</v>
       </c>
       <c r="G669" s="1" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="H669" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I669" s="1" t="s">
-        <v>176</v>
+        <v>348</v>
       </c>
     </row>
     <row r="670" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25439,10 +25445,28 @@
         <v>1269</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>117</v>
+        <v>784</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>3923</v>
+        <v>3922</v>
+      </c>
+      <c r="D670" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E670" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G670" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="H670" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I670" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="671" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25450,28 +25474,10 @@
         <v>1269</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>749</v>
+        <v>117</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>3924</v>
-      </c>
-      <c r="D671" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E671" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F671" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="G671" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="H671" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I671" s="1" t="s">
-        <v>31</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="672" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25479,10 +25485,10 @@
         <v>1269</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>3926</v>
+        <v>3924</v>
       </c>
       <c r="D672" s="29" t="s">
         <v>136</v>
@@ -25494,7 +25500,7 @@
         <v>140</v>
       </c>
       <c r="G672" s="1" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="H672" s="1" t="s">
         <v>17</v>
@@ -25508,10 +25514,10 @@
         <v>1269</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>3928</v>
+        <v>3926</v>
       </c>
       <c r="D673" s="29" t="s">
         <v>136</v>
@@ -25523,7 +25529,7 @@
         <v>140</v>
       </c>
       <c r="G673" s="1" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="H673" s="1" t="s">
         <v>17</v>
@@ -25537,25 +25543,28 @@
         <v>1269</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="C674" s="22" t="n">
-        <v>3930</v>
-      </c>
-      <c r="D674" s="2" t="s">
-        <v>59</v>
+        <v>767</v>
+      </c>
+      <c r="C674" s="1" t="n">
+        <v>3928</v>
+      </c>
+      <c r="D674" s="29" t="s">
+        <v>136</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F674" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="G674" s="22" t="s">
-        <v>921</v>
+        <v>1</v>
+      </c>
+      <c r="F674" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="G674" s="1" t="s">
+        <v>768</v>
       </c>
       <c r="H674" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="I674" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="675" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25563,10 +25572,10 @@
         <v>1269</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C675" s="22" t="n">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="D675" s="2" t="s">
         <v>59</v>
@@ -25578,7 +25587,7 @@
         <v>920</v>
       </c>
       <c r="G675" s="22" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="H675" s="1" t="s">
         <v>17</v>
@@ -25589,10 +25598,10 @@
         <v>1269</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C676" s="22" t="n">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="D676" s="2" t="s">
         <v>59</v>
@@ -25604,7 +25613,7 @@
         <v>920</v>
       </c>
       <c r="G676" s="22" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H676" s="1" t="s">
         <v>17</v>
@@ -25615,10 +25624,10 @@
         <v>1269</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C677" s="22" t="n">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="D677" s="2" t="s">
         <v>59</v>
@@ -25630,39 +25639,36 @@
         <v>920</v>
       </c>
       <c r="G677" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="H677" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="678" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A678" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="C678" s="22" t="n">
+        <v>3933</v>
+      </c>
+      <c r="D678" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E678" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="G678" s="22" t="s">
         <v>927</v>
       </c>
-      <c r="H677" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="678" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A678" s="22" t="s">
-        <v>1272</v>
-      </c>
-      <c r="B678" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C678" s="22" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D678" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E678" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="F678" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G678" s="22" t="s">
-        <v>218</v>
-      </c>
       <c r="H678" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I678" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="679" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25670,28 +25676,28 @@
         <v>1272</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C679" s="22" t="n">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="D679" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E679" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F679" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G679" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H679" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I679" s="1" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
     </row>
     <row r="680" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25699,28 +25705,28 @@
         <v>1272</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1273</v>
+        <v>219</v>
       </c>
       <c r="C680" s="22" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D680" s="29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E680" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F680" s="3" t="s">
-        <v>217</v>
+        <v>94</v>
       </c>
       <c r="G680" s="22" t="s">
-        <v>495</v>
+        <v>220</v>
       </c>
       <c r="H680" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I680" s="1" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
     </row>
     <row r="681" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25728,28 +25734,28 @@
         <v>1272</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1155</v>
+        <v>1273</v>
       </c>
       <c r="C681" s="22" t="n">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="D681" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E681" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F681" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G681" s="22" t="s">
-        <v>307</v>
+        <v>495</v>
       </c>
       <c r="H681" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I681" s="1" t="s">
-        <v>308</v>
+        <v>91</v>
       </c>
     </row>
     <row r="682" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25757,28 +25763,28 @@
         <v>1272</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1274</v>
+        <v>1155</v>
       </c>
       <c r="C682" s="22" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="D682" s="29" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="E682" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F682" s="3" t="s">
-        <v>1059</v>
+        <v>94</v>
       </c>
       <c r="G682" s="22" t="s">
-        <v>1275</v>
+        <v>307</v>
       </c>
       <c r="H682" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I682" s="1" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
     </row>
     <row r="683" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25786,28 +25792,28 @@
         <v>1272</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>511</v>
+        <v>1274</v>
       </c>
       <c r="C683" s="22" t="n">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="D683" s="29" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="E683" s="22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F683" s="3" t="s">
-        <v>264</v>
+        <v>1059</v>
       </c>
       <c r="G683" s="22" t="s">
-        <v>512</v>
+        <v>1275</v>
       </c>
       <c r="H683" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I683" s="1" t="s">
-        <v>241</v>
+        <v>348</v>
       </c>
     </row>
     <row r="684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25815,10 +25821,10 @@
         <v>1272</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C684" s="22" t="n">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="D684" s="29" t="s">
         <v>20</v>
@@ -25830,7 +25836,7 @@
         <v>264</v>
       </c>
       <c r="G684" s="22" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H684" s="1" t="s">
         <v>17</v>
@@ -25844,10 +25850,10 @@
         <v>1272</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>1276</v>
+        <v>513</v>
       </c>
       <c r="C685" s="22" t="n">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="D685" s="29" t="s">
         <v>20</v>
@@ -25859,7 +25865,7 @@
         <v>264</v>
       </c>
       <c r="G685" s="22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H685" s="1" t="s">
         <v>17</v>
@@ -25873,10 +25879,10 @@
         <v>1272</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C686" s="22" t="n">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="D686" s="29" t="s">
         <v>20</v>
@@ -25888,7 +25894,7 @@
         <v>264</v>
       </c>
       <c r="G686" s="22" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H686" s="1" t="s">
         <v>17</v>
@@ -25902,10 +25908,10 @@
         <v>1272</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>521</v>
+        <v>1277</v>
       </c>
       <c r="C687" s="22" t="n">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="D687" s="29" t="s">
         <v>20</v>
@@ -25917,7 +25923,7 @@
         <v>264</v>
       </c>
       <c r="G687" s="22" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H687" s="1" t="s">
         <v>17</v>
@@ -25931,10 +25937,10 @@
         <v>1272</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C688" s="22" t="n">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="D688" s="29" t="s">
         <v>20</v>
@@ -25946,7 +25952,7 @@
         <v>264</v>
       </c>
       <c r="G688" s="22" t="s">
-        <v>240</v>
+        <v>522</v>
       </c>
       <c r="H688" s="1" t="s">
         <v>17</v>
@@ -25957,31 +25963,31 @@
     </row>
     <row r="689" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A689" s="22" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>216</v>
+        <v>523</v>
       </c>
       <c r="C689" s="22" t="n">
-        <v>4100</v>
+        <v>4011</v>
       </c>
       <c r="D689" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E689" s="22" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F689" s="3" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="G689" s="22" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="H689" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I689" s="1" t="s">
-        <v>91</v>
+        <v>241</v>
       </c>
     </row>
     <row r="690" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25989,28 +25995,28 @@
         <v>1278</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C690" s="22" t="n">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="D690" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E690" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F690" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G690" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H690" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I690" s="1" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
     </row>
     <row r="691" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26018,28 +26024,28 @@
         <v>1278</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>1273</v>
+        <v>219</v>
       </c>
       <c r="C691" s="22" t="n">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="D691" s="29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E691" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F691" s="3" t="s">
-        <v>217</v>
+        <v>94</v>
       </c>
       <c r="G691" s="22" t="s">
-        <v>495</v>
+        <v>220</v>
       </c>
       <c r="H691" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I691" s="1" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
     </row>
     <row r="692" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26047,28 +26053,28 @@
         <v>1278</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>1155</v>
+        <v>1273</v>
       </c>
       <c r="C692" s="22" t="n">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="D692" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E692" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F692" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G692" s="22" t="s">
-        <v>307</v>
+        <v>495</v>
       </c>
       <c r="H692" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I692" s="1" t="s">
-        <v>308</v>
+        <v>91</v>
       </c>
     </row>
     <row r="693" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26076,28 +26082,28 @@
         <v>1278</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>1274</v>
+        <v>1155</v>
       </c>
       <c r="C693" s="22" t="n">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="D693" s="29" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="E693" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F693" s="3" t="s">
-        <v>1059</v>
+        <v>94</v>
       </c>
       <c r="G693" s="22" t="s">
-        <v>1275</v>
+        <v>307</v>
       </c>
       <c r="H693" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I693" s="1" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
     </row>
     <row r="694" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26105,28 +26111,28 @@
         <v>1278</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>511</v>
+        <v>1274</v>
       </c>
       <c r="C694" s="22" t="n">
-        <v>4106</v>
+        <v>4104</v>
       </c>
       <c r="D694" s="29" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="E694" s="22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F694" s="3" t="s">
-        <v>264</v>
+        <v>1059</v>
       </c>
       <c r="G694" s="22" t="s">
-        <v>512</v>
+        <v>1275</v>
       </c>
       <c r="H694" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I694" s="1" t="s">
-        <v>241</v>
+        <v>348</v>
       </c>
     </row>
     <row r="695" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26134,10 +26140,10 @@
         <v>1278</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C695" s="22" t="n">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="D695" s="29" t="s">
         <v>20</v>
@@ -26149,7 +26155,7 @@
         <v>264</v>
       </c>
       <c r="G695" s="22" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H695" s="1" t="s">
         <v>17</v>
@@ -26163,10 +26169,10 @@
         <v>1278</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>1276</v>
+        <v>513</v>
       </c>
       <c r="C696" s="22" t="n">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="D696" s="29" t="s">
         <v>20</v>
@@ -26178,7 +26184,7 @@
         <v>264</v>
       </c>
       <c r="G696" s="22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H696" s="1" t="s">
         <v>17</v>
@@ -26192,10 +26198,10 @@
         <v>1278</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C697" s="22" t="n">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="D697" s="29" t="s">
         <v>20</v>
@@ -26207,7 +26213,7 @@
         <v>264</v>
       </c>
       <c r="G697" s="22" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H697" s="1" t="s">
         <v>17</v>
@@ -26221,10 +26227,10 @@
         <v>1278</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>521</v>
+        <v>1277</v>
       </c>
       <c r="C698" s="22" t="n">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="D698" s="29" t="s">
         <v>20</v>
@@ -26236,7 +26242,7 @@
         <v>264</v>
       </c>
       <c r="G698" s="22" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H698" s="1" t="s">
         <v>17</v>
@@ -26250,10 +26256,10 @@
         <v>1278</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C699" s="22" t="n">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="D699" s="29" t="s">
         <v>20</v>
@@ -26265,7 +26271,7 @@
         <v>264</v>
       </c>
       <c r="G699" s="22" t="s">
-        <v>240</v>
+        <v>522</v>
       </c>
       <c r="H699" s="1" t="s">
         <v>17</v>
@@ -26279,10 +26285,10 @@
         <v>1278</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>1279</v>
+        <v>523</v>
       </c>
       <c r="C700" s="22" t="n">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="D700" s="29" t="s">
         <v>20</v>
@@ -26294,13 +26300,13 @@
         <v>264</v>
       </c>
       <c r="G700" s="22" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="H700" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I700" s="1" t="s">
-        <v>1280</v>
+        <v>241</v>
       </c>
     </row>
     <row r="701" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26308,10 +26314,10 @@
         <v>1278</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C701" s="22" t="n">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="D701" s="29" t="s">
         <v>20</v>
@@ -26323,13 +26329,13 @@
         <v>264</v>
       </c>
       <c r="G701" s="22" t="s">
-        <v>664</v>
+        <v>231</v>
       </c>
       <c r="H701" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I701" s="1" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="702" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26337,10 +26343,10 @@
         <v>1278</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>1107</v>
+        <v>1281</v>
       </c>
       <c r="C702" s="22" t="n">
-        <v>4114</v>
+        <v>4113</v>
       </c>
       <c r="D702" s="29" t="s">
         <v>20</v>
@@ -26352,13 +26358,13 @@
         <v>264</v>
       </c>
       <c r="G702" s="22" t="s">
-        <v>1108</v>
+        <v>664</v>
       </c>
       <c r="H702" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I702" s="1" t="s">
-        <v>864</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="703" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26366,10 +26372,10 @@
         <v>1278</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>1283</v>
+        <v>1107</v>
       </c>
       <c r="C703" s="22" t="n">
-        <v>4115</v>
+        <v>4114</v>
       </c>
       <c r="D703" s="29" t="s">
         <v>20</v>
@@ -26381,7 +26387,7 @@
         <v>264</v>
       </c>
       <c r="G703" s="22" t="s">
-        <v>997</v>
+        <v>1108</v>
       </c>
       <c r="H703" s="1" t="s">
         <v>17</v>
@@ -26395,10 +26401,10 @@
         <v>1278</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C704" s="22" t="n">
-        <v>4116</v>
+        <v>4115</v>
       </c>
       <c r="D704" s="29" t="s">
         <v>20</v>
@@ -26410,13 +26416,13 @@
         <v>264</v>
       </c>
       <c r="G704" s="22" t="s">
-        <v>1285</v>
+        <v>997</v>
       </c>
       <c r="H704" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I704" s="1" t="s">
-        <v>103</v>
+        <v>864</v>
       </c>
     </row>
     <row r="705" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26424,28 +26430,28 @@
         <v>1278</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C705" s="22" t="n">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="D705" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E705" s="22" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F705" s="3" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="G705" s="22" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="H705" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I705" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="706" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26453,28 +26459,28 @@
         <v>1278</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C706" s="22" t="n">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="D706" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E706" s="22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F706" s="3" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="G706" s="22" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="H706" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I706" s="1" t="s">
-        <v>888</v>
+        <v>91</v>
       </c>
     </row>
     <row r="707" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26482,10 +26488,10 @@
         <v>1278</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>844</v>
+        <v>1288</v>
       </c>
       <c r="C707" s="22" t="n">
-        <v>4119</v>
+        <v>4118</v>
       </c>
       <c r="D707" s="29" t="s">
         <v>20</v>
@@ -26497,13 +26503,13 @@
         <v>264</v>
       </c>
       <c r="G707" s="22" t="s">
-        <v>237</v>
+        <v>1289</v>
       </c>
       <c r="H707" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I707" s="1" t="s">
-        <v>637</v>
+        <v>888</v>
       </c>
     </row>
     <row r="708" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26511,57 +26517,57 @@
         <v>1278</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1290</v>
+        <v>844</v>
       </c>
       <c r="C708" s="22" t="n">
-        <v>4120</v>
+        <v>4119</v>
       </c>
       <c r="D708" s="29" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="E708" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F708" s="3" t="s">
-        <v>1291</v>
+        <v>264</v>
       </c>
       <c r="G708" s="22" t="s">
-        <v>1292</v>
+        <v>237</v>
       </c>
       <c r="H708" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I708" s="1" t="s">
-        <v>111</v>
+        <v>637</v>
       </c>
     </row>
     <row r="709" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A709" s="22" t="s">
-        <v>1293</v>
+        <v>1278</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>216</v>
+        <v>1290</v>
       </c>
       <c r="C709" s="22" t="n">
-        <v>4200</v>
+        <v>4120</v>
       </c>
       <c r="D709" s="29" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="E709" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F709" s="3" t="s">
-        <v>217</v>
+        <v>1291</v>
       </c>
       <c r="G709" s="22" t="s">
-        <v>218</v>
+        <v>1292</v>
       </c>
       <c r="H709" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I709" s="1" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="710" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26569,28 +26575,28 @@
         <v>1293</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C710" s="22" t="n">
-        <v>4201</v>
+        <v>4200</v>
       </c>
       <c r="D710" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E710" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F710" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G710" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H710" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I710" s="1" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
     </row>
     <row r="711" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26598,28 +26604,28 @@
         <v>1293</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>1273</v>
+        <v>219</v>
       </c>
       <c r="C711" s="22" t="n">
-        <v>4202</v>
+        <v>4201</v>
       </c>
       <c r="D711" s="29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E711" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F711" s="3" t="s">
-        <v>217</v>
+        <v>94</v>
       </c>
       <c r="G711" s="22" t="s">
-        <v>495</v>
+        <v>220</v>
       </c>
       <c r="H711" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I711" s="1" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
     </row>
     <row r="712" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26627,28 +26633,28 @@
         <v>1293</v>
       </c>
       <c r="B712" s="1" t="s">
-        <v>1155</v>
+        <v>1273</v>
       </c>
       <c r="C712" s="22" t="n">
-        <v>4203</v>
+        <v>4202</v>
       </c>
       <c r="D712" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E712" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F712" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G712" s="22" t="s">
-        <v>307</v>
+        <v>495</v>
       </c>
       <c r="H712" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I712" s="1" t="s">
-        <v>308</v>
+        <v>91</v>
       </c>
     </row>
     <row r="713" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26656,28 +26662,28 @@
         <v>1293</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>1274</v>
+        <v>1155</v>
       </c>
       <c r="C713" s="22" t="n">
-        <v>4204</v>
+        <v>4203</v>
       </c>
       <c r="D713" s="29" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="E713" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F713" s="3" t="s">
-        <v>1059</v>
+        <v>94</v>
       </c>
       <c r="G713" s="22" t="s">
-        <v>1275</v>
+        <v>307</v>
       </c>
       <c r="H713" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I713" s="1" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
     </row>
     <row r="714" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26685,28 +26691,28 @@
         <v>1293</v>
       </c>
       <c r="B714" s="1" t="s">
-        <v>511</v>
+        <v>1274</v>
       </c>
       <c r="C714" s="22" t="n">
-        <v>4206</v>
+        <v>4204</v>
       </c>
       <c r="D714" s="29" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="E714" s="22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F714" s="3" t="s">
-        <v>264</v>
+        <v>1059</v>
       </c>
       <c r="G714" s="22" t="s">
-        <v>512</v>
+        <v>1275</v>
       </c>
       <c r="H714" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I714" s="1" t="s">
-        <v>241</v>
+        <v>348</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26714,10 +26720,10 @@
         <v>1293</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C715" s="22" t="n">
-        <v>4207</v>
+        <v>4206</v>
       </c>
       <c r="D715" s="29" t="s">
         <v>20</v>
@@ -26729,7 +26735,7 @@
         <v>264</v>
       </c>
       <c r="G715" s="22" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H715" s="1" t="s">
         <v>17</v>
@@ -26743,10 +26749,10 @@
         <v>1293</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>1276</v>
+        <v>513</v>
       </c>
       <c r="C716" s="22" t="n">
-        <v>4208</v>
+        <v>4207</v>
       </c>
       <c r="D716" s="29" t="s">
         <v>20</v>
@@ -26758,7 +26764,7 @@
         <v>264</v>
       </c>
       <c r="G716" s="22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H716" s="1" t="s">
         <v>17</v>
@@ -26772,10 +26778,10 @@
         <v>1293</v>
       </c>
       <c r="B717" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C717" s="22" t="n">
-        <v>4209</v>
+        <v>4208</v>
       </c>
       <c r="D717" s="29" t="s">
         <v>20</v>
@@ -26787,7 +26793,7 @@
         <v>264</v>
       </c>
       <c r="G717" s="22" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H717" s="1" t="s">
         <v>17</v>
@@ -26801,10 +26807,10 @@
         <v>1293</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>521</v>
+        <v>1277</v>
       </c>
       <c r="C718" s="22" t="n">
-        <v>4210</v>
+        <v>4209</v>
       </c>
       <c r="D718" s="29" t="s">
         <v>20</v>
@@ -26816,7 +26822,7 @@
         <v>264</v>
       </c>
       <c r="G718" s="22" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H718" s="1" t="s">
         <v>17</v>
@@ -26830,10 +26836,10 @@
         <v>1293</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C719" s="22" t="n">
-        <v>4211</v>
+        <v>4210</v>
       </c>
       <c r="D719" s="29" t="s">
         <v>20</v>
@@ -26845,7 +26851,7 @@
         <v>264</v>
       </c>
       <c r="G719" s="22" t="s">
-        <v>240</v>
+        <v>522</v>
       </c>
       <c r="H719" s="1" t="s">
         <v>17</v>
@@ -26856,31 +26862,31 @@
     </row>
     <row r="720" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A720" s="22" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B720" s="1" t="s">
-        <v>216</v>
+        <v>523</v>
       </c>
       <c r="C720" s="22" t="n">
-        <v>4300</v>
+        <v>4211</v>
       </c>
       <c r="D720" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E720" s="22" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F720" s="3" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="G720" s="22" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="H720" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I720" s="1" t="s">
-        <v>91</v>
+        <v>241</v>
       </c>
     </row>
     <row r="721" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26888,28 +26894,28 @@
         <v>1294</v>
       </c>
       <c r="B721" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C721" s="22" t="n">
-        <v>4301</v>
+        <v>4300</v>
       </c>
       <c r="D721" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E721" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F721" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G721" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H721" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I721" s="1" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
     </row>
     <row r="722" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26917,28 +26923,28 @@
         <v>1294</v>
       </c>
       <c r="B722" s="1" t="s">
-        <v>1273</v>
+        <v>219</v>
       </c>
       <c r="C722" s="22" t="n">
-        <v>4302</v>
+        <v>4301</v>
       </c>
       <c r="D722" s="29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E722" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F722" s="3" t="s">
-        <v>217</v>
+        <v>94</v>
       </c>
       <c r="G722" s="22" t="s">
-        <v>495</v>
+        <v>220</v>
       </c>
       <c r="H722" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I722" s="1" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
     </row>
     <row r="723" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26946,28 +26952,28 @@
         <v>1294</v>
       </c>
       <c r="B723" s="1" t="s">
-        <v>1155</v>
+        <v>1273</v>
       </c>
       <c r="C723" s="22" t="n">
-        <v>4303</v>
+        <v>4302</v>
       </c>
       <c r="D723" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E723" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F723" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G723" s="22" t="s">
-        <v>307</v>
+        <v>495</v>
       </c>
       <c r="H723" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I723" s="1" t="s">
-        <v>308</v>
+        <v>91</v>
       </c>
     </row>
     <row r="724" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26975,28 +26981,28 @@
         <v>1294</v>
       </c>
       <c r="B724" s="1" t="s">
-        <v>1295</v>
+        <v>1155</v>
       </c>
       <c r="C724" s="22" t="n">
-        <v>4304</v>
+        <v>4303</v>
       </c>
       <c r="D724" s="29" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="E724" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F724" s="3" t="s">
-        <v>1059</v>
+        <v>94</v>
       </c>
       <c r="G724" s="22" t="s">
-        <v>1296</v>
+        <v>307</v>
       </c>
       <c r="H724" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I724" s="1" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
     </row>
     <row r="725" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27004,28 +27010,28 @@
         <v>1294</v>
       </c>
       <c r="B725" s="1" t="s">
-        <v>511</v>
+        <v>1295</v>
       </c>
       <c r="C725" s="22" t="n">
-        <v>4306</v>
+        <v>4304</v>
       </c>
       <c r="D725" s="29" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="E725" s="22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F725" s="3" t="s">
-        <v>264</v>
+        <v>1059</v>
       </c>
       <c r="G725" s="22" t="s">
-        <v>512</v>
+        <v>1296</v>
       </c>
       <c r="H725" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I725" s="1" t="s">
-        <v>241</v>
+        <v>348</v>
       </c>
     </row>
     <row r="726" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27033,10 +27039,10 @@
         <v>1294</v>
       </c>
       <c r="B726" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C726" s="22" t="n">
-        <v>4307</v>
+        <v>4306</v>
       </c>
       <c r="D726" s="29" t="s">
         <v>20</v>
@@ -27048,7 +27054,7 @@
         <v>264</v>
       </c>
       <c r="G726" s="22" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H726" s="1" t="s">
         <v>17</v>
@@ -27062,10 +27068,10 @@
         <v>1294</v>
       </c>
       <c r="B727" s="1" t="s">
-        <v>1276</v>
+        <v>513</v>
       </c>
       <c r="C727" s="22" t="n">
-        <v>4308</v>
+        <v>4307</v>
       </c>
       <c r="D727" s="29" t="s">
         <v>20</v>
@@ -27077,7 +27083,7 @@
         <v>264</v>
       </c>
       <c r="G727" s="22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H727" s="1" t="s">
         <v>17</v>
@@ -27091,10 +27097,10 @@
         <v>1294</v>
       </c>
       <c r="B728" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C728" s="22" t="n">
-        <v>4309</v>
+        <v>4308</v>
       </c>
       <c r="D728" s="29" t="s">
         <v>20</v>
@@ -27106,7 +27112,7 @@
         <v>264</v>
       </c>
       <c r="G728" s="22" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H728" s="1" t="s">
         <v>17</v>
@@ -27120,10 +27126,10 @@
         <v>1294</v>
       </c>
       <c r="B729" s="1" t="s">
-        <v>521</v>
+        <v>1277</v>
       </c>
       <c r="C729" s="22" t="n">
-        <v>4310</v>
+        <v>4309</v>
       </c>
       <c r="D729" s="29" t="s">
         <v>20</v>
@@ -27135,7 +27141,7 @@
         <v>264</v>
       </c>
       <c r="G729" s="22" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H729" s="1" t="s">
         <v>17</v>
@@ -27149,10 +27155,10 @@
         <v>1294</v>
       </c>
       <c r="B730" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C730" s="22" t="n">
-        <v>4311</v>
+        <v>4310</v>
       </c>
       <c r="D730" s="29" t="s">
         <v>20</v>
@@ -27164,7 +27170,7 @@
         <v>264</v>
       </c>
       <c r="G730" s="22" t="s">
-        <v>240</v>
+        <v>522</v>
       </c>
       <c r="H730" s="1" t="s">
         <v>17</v>
@@ -27175,31 +27181,31 @@
     </row>
     <row r="731" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A731" s="22" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="B731" s="1" t="s">
-        <v>216</v>
+        <v>523</v>
       </c>
       <c r="C731" s="22" t="n">
-        <v>4400</v>
+        <v>4311</v>
       </c>
       <c r="D731" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E731" s="22" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F731" s="3" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="G731" s="22" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="H731" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I731" s="1" t="s">
-        <v>91</v>
+        <v>241</v>
       </c>
     </row>
     <row r="732" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27207,28 +27213,28 @@
         <v>1297</v>
       </c>
       <c r="B732" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C732" s="22" t="n">
-        <v>4401</v>
+        <v>4400</v>
       </c>
       <c r="D732" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E732" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F732" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G732" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H732" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I732" s="1" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
     </row>
     <row r="733" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27236,28 +27242,28 @@
         <v>1297</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>1273</v>
+        <v>219</v>
       </c>
       <c r="C733" s="22" t="n">
-        <v>4402</v>
+        <v>4401</v>
       </c>
       <c r="D733" s="29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E733" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F733" s="3" t="s">
-        <v>217</v>
+        <v>94</v>
       </c>
       <c r="G733" s="22" t="s">
-        <v>495</v>
+        <v>220</v>
       </c>
       <c r="H733" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I733" s="1" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
     </row>
     <row r="734" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27265,28 +27271,28 @@
         <v>1297</v>
       </c>
       <c r="B734" s="1" t="s">
-        <v>1155</v>
+        <v>1273</v>
       </c>
       <c r="C734" s="22" t="n">
-        <v>4403</v>
+        <v>4402</v>
       </c>
       <c r="D734" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E734" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F734" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G734" s="22" t="s">
-        <v>307</v>
+        <v>495</v>
       </c>
       <c r="H734" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I734" s="1" t="s">
-        <v>308</v>
+        <v>91</v>
       </c>
     </row>
     <row r="735" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27294,28 +27300,28 @@
         <v>1297</v>
       </c>
       <c r="B735" s="1" t="s">
-        <v>1274</v>
+        <v>1155</v>
       </c>
       <c r="C735" s="22" t="n">
-        <v>4404</v>
+        <v>4403</v>
       </c>
       <c r="D735" s="29" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="E735" s="22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F735" s="3" t="s">
-        <v>1059</v>
+        <v>94</v>
       </c>
       <c r="G735" s="22" t="s">
-        <v>1275</v>
+        <v>307</v>
       </c>
       <c r="H735" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I735" s="1" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
     </row>
     <row r="736" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27323,10 +27329,10 @@
         <v>1297</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>1295</v>
+        <v>1274</v>
       </c>
       <c r="C736" s="22" t="n">
-        <v>4406</v>
+        <v>4404</v>
       </c>
       <c r="D736" s="29" t="s">
         <v>155</v>
@@ -27338,7 +27344,7 @@
         <v>1059</v>
       </c>
       <c r="G736" s="22" t="s">
-        <v>1296</v>
+        <v>1275</v>
       </c>
       <c r="H736" s="1" t="s">
         <v>17</v>
@@ -27352,28 +27358,28 @@
         <v>1297</v>
       </c>
       <c r="B737" s="1" t="s">
-        <v>511</v>
+        <v>1295</v>
       </c>
       <c r="C737" s="22" t="n">
-        <v>4408</v>
+        <v>4406</v>
       </c>
       <c r="D737" s="29" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="E737" s="22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F737" s="3" t="s">
-        <v>264</v>
+        <v>1059</v>
       </c>
       <c r="G737" s="22" t="s">
-        <v>512</v>
+        <v>1296</v>
       </c>
       <c r="H737" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I737" s="22" t="s">
-        <v>1298</v>
+      <c r="I737" s="1" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="738" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27381,10 +27387,10 @@
         <v>1297</v>
       </c>
       <c r="B738" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C738" s="22" t="n">
-        <v>4409</v>
+        <v>4408</v>
       </c>
       <c r="D738" s="29" t="s">
         <v>20</v>
@@ -27396,7 +27402,7 @@
         <v>264</v>
       </c>
       <c r="G738" s="22" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H738" s="1" t="s">
         <v>17</v>
@@ -27410,10 +27416,10 @@
         <v>1297</v>
       </c>
       <c r="B739" s="1" t="s">
-        <v>1276</v>
+        <v>513</v>
       </c>
       <c r="C739" s="22" t="n">
-        <v>4410</v>
+        <v>4409</v>
       </c>
       <c r="D739" s="29" t="s">
         <v>20</v>
@@ -27425,13 +27431,13 @@
         <v>264</v>
       </c>
       <c r="G739" s="22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H739" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I739" s="1" t="s">
-        <v>241</v>
+      <c r="I739" s="22" t="s">
+        <v>1298</v>
       </c>
     </row>
     <row r="740" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27439,10 +27445,10 @@
         <v>1297</v>
       </c>
       <c r="B740" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C740" s="22" t="n">
-        <v>4411</v>
+        <v>4410</v>
       </c>
       <c r="D740" s="29" t="s">
         <v>20</v>
@@ -27454,7 +27460,7 @@
         <v>264</v>
       </c>
       <c r="G740" s="22" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H740" s="1" t="s">
         <v>17</v>
@@ -27468,10 +27474,10 @@
         <v>1297</v>
       </c>
       <c r="B741" s="1" t="s">
-        <v>521</v>
+        <v>1277</v>
       </c>
       <c r="C741" s="22" t="n">
-        <v>4412</v>
+        <v>4411</v>
       </c>
       <c r="D741" s="29" t="s">
         <v>20</v>
@@ -27483,7 +27489,7 @@
         <v>264</v>
       </c>
       <c r="G741" s="22" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H741" s="1" t="s">
         <v>17</v>
@@ -27497,10 +27503,10 @@
         <v>1297</v>
       </c>
       <c r="B742" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C742" s="22" t="n">
-        <v>4413</v>
+        <v>4412</v>
       </c>
       <c r="D742" s="29" t="s">
         <v>20</v>
@@ -27512,7 +27518,7 @@
         <v>264</v>
       </c>
       <c r="G742" s="22" t="s">
-        <v>240</v>
+        <v>522</v>
       </c>
       <c r="H742" s="1" t="s">
         <v>17</v>
@@ -27523,31 +27529,31 @@
     </row>
     <row r="743" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A743" s="22" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B743" s="1" t="s">
-        <v>158</v>
+        <v>523</v>
       </c>
       <c r="C743" s="22" t="n">
-        <v>4500</v>
+        <v>4413</v>
       </c>
       <c r="D743" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E743" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F743" s="3" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="G743" s="22" t="s">
-        <v>1300</v>
-      </c>
-      <c r="H743" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I743" s="22" t="s">
-        <v>160</v>
+        <v>240</v>
+      </c>
+      <c r="H743" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I743" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="744" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27555,10 +27561,10 @@
         <v>1299</v>
       </c>
       <c r="B744" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C744" s="22" t="n">
-        <v>4501</v>
+        <v>4500</v>
       </c>
       <c r="D744" s="29" t="s">
         <v>20</v>
@@ -27570,7 +27576,7 @@
         <v>89</v>
       </c>
       <c r="G744" s="22" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H744" s="22" t="s">
         <v>17</v>
@@ -27584,10 +27590,10 @@
         <v>1299</v>
       </c>
       <c r="B745" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C745" s="22" t="n">
-        <v>4502</v>
+        <v>4501</v>
       </c>
       <c r="D745" s="29" t="s">
         <v>20</v>
@@ -27599,7 +27605,7 @@
         <v>89</v>
       </c>
       <c r="G745" s="22" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H745" s="22" t="s">
         <v>17</v>
@@ -27613,13 +27619,13 @@
         <v>1299</v>
       </c>
       <c r="B746" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C746" s="22" t="n">
-        <v>4503</v>
+        <v>4502</v>
       </c>
       <c r="D746" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E746" s="22" t="n">
         <v>10</v>
@@ -27628,13 +27634,13 @@
         <v>89</v>
       </c>
       <c r="G746" s="22" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H746" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I746" s="22" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="747" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27642,10 +27648,10 @@
         <v>1299</v>
       </c>
       <c r="B747" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C747" s="22" t="n">
-        <v>4504</v>
+        <v>4503</v>
       </c>
       <c r="D747" s="29" t="s">
         <v>59</v>
@@ -27657,7 +27663,7 @@
         <v>89</v>
       </c>
       <c r="G747" s="22" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H747" s="22" t="s">
         <v>17</v>
@@ -27671,10 +27677,10 @@
         <v>1299</v>
       </c>
       <c r="B748" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C748" s="22" t="n">
-        <v>4505</v>
+        <v>4504</v>
       </c>
       <c r="D748" s="29" t="s">
         <v>59</v>
@@ -27686,7 +27692,7 @@
         <v>89</v>
       </c>
       <c r="G748" s="22" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H748" s="22" t="s">
         <v>17</v>
@@ -27700,28 +27706,28 @@
         <v>1299</v>
       </c>
       <c r="B749" s="1" t="s">
-        <v>1306</v>
+        <v>171</v>
       </c>
       <c r="C749" s="22" t="n">
-        <v>4506</v>
+        <v>4505</v>
       </c>
       <c r="D749" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="E749" s="22" t="s">
-        <v>1307</v>
+      <c r="E749" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="F749" s="3" t="s">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="G749" s="22" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="H749" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I749" s="22" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
     </row>
     <row r="750" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27729,10 +27735,10 @@
         <v>1299</v>
       </c>
       <c r="B750" s="1" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="C750" s="22" t="n">
-        <v>4507</v>
+        <v>4506</v>
       </c>
       <c r="D750" s="29" t="s">
         <v>59</v>
@@ -27744,7 +27750,7 @@
         <v>182</v>
       </c>
       <c r="G750" s="22" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="H750" s="22" t="s">
         <v>17</v>
@@ -27758,10 +27764,10 @@
         <v>1299</v>
       </c>
       <c r="B751" s="1" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="C751" s="22" t="n">
-        <v>4508</v>
+        <v>4507</v>
       </c>
       <c r="D751" s="29" t="s">
         <v>59</v>
@@ -27773,7 +27779,7 @@
         <v>182</v>
       </c>
       <c r="G751" s="22" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="H751" s="22" t="s">
         <v>17</v>
@@ -27787,25 +27793,28 @@
         <v>1299</v>
       </c>
       <c r="B752" s="1" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C752" s="22" t="n">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="D752" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E752" s="22" t="n">
-        <v>100</v>
+        <v>59</v>
+      </c>
+      <c r="E752" s="22" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="G752" s="22" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="H752" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I752" s="22" t="s">
-        <v>176</v>
+        <v>31</v>
       </c>
     </row>
     <row r="753" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27813,28 +27822,25 @@
         <v>1299</v>
       </c>
       <c r="B753" s="1" t="s">
-        <v>190</v>
+        <v>1313</v>
       </c>
       <c r="C753" s="22" t="n">
-        <v>4510</v>
+        <v>4509</v>
       </c>
       <c r="D753" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E753" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="F753" s="3" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G753" s="22" t="s">
-        <v>191</v>
+        <v>1314</v>
       </c>
       <c r="H753" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I753" s="22" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="754" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27842,10 +27848,10 @@
         <v>1299</v>
       </c>
       <c r="B754" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C754" s="22" t="n">
-        <v>4511</v>
+        <v>4510</v>
       </c>
       <c r="D754" s="29" t="s">
         <v>20</v>
@@ -27857,7 +27863,7 @@
         <v>89</v>
       </c>
       <c r="G754" s="22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H754" s="22" t="s">
         <v>17</v>
@@ -27871,10 +27877,10 @@
         <v>1299</v>
       </c>
       <c r="B755" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C755" s="22" t="n">
-        <v>4512</v>
+        <v>4511</v>
       </c>
       <c r="D755" s="29" t="s">
         <v>20</v>
@@ -27886,7 +27892,7 @@
         <v>89</v>
       </c>
       <c r="G755" s="22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H755" s="22" t="s">
         <v>17</v>
@@ -27900,13 +27906,13 @@
         <v>1299</v>
       </c>
       <c r="B756" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C756" s="22" t="n">
-        <v>4513</v>
+        <v>4512</v>
       </c>
       <c r="D756" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E756" s="22" t="n">
         <v>10</v>
@@ -27915,13 +27921,13 @@
         <v>89</v>
       </c>
       <c r="G756" s="22" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H756" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I756" s="22" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="757" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27929,10 +27935,10 @@
         <v>1299</v>
       </c>
       <c r="B757" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C757" s="22" t="n">
-        <v>4514</v>
+        <v>4513</v>
       </c>
       <c r="D757" s="29" t="s">
         <v>59</v>
@@ -27944,7 +27950,7 @@
         <v>89</v>
       </c>
       <c r="G757" s="22" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H757" s="22" t="s">
         <v>17</v>
@@ -27958,10 +27964,10 @@
         <v>1299</v>
       </c>
       <c r="B758" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C758" s="22" t="n">
-        <v>4515</v>
+        <v>4514</v>
       </c>
       <c r="D758" s="29" t="s">
         <v>59</v>
@@ -27973,7 +27979,7 @@
         <v>89</v>
       </c>
       <c r="G758" s="22" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H758" s="22" t="s">
         <v>17</v>
@@ -27987,28 +27993,28 @@
         <v>1299</v>
       </c>
       <c r="B759" s="1" t="s">
-        <v>1315</v>
+        <v>201</v>
       </c>
       <c r="C759" s="22" t="n">
-        <v>4516</v>
+        <v>4515</v>
       </c>
       <c r="D759" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="E759" s="22" t="s">
-        <v>1307</v>
+      <c r="E759" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="F759" s="3" t="s">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="G759" s="22" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="H759" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I759" s="22" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
     </row>
     <row r="760" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28016,10 +28022,10 @@
         <v>1299</v>
       </c>
       <c r="B760" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C760" s="22" t="n">
-        <v>4517</v>
+        <v>4516</v>
       </c>
       <c r="D760" s="29" t="s">
         <v>59</v>
@@ -28031,7 +28037,7 @@
         <v>182</v>
       </c>
       <c r="G760" s="22" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H760" s="22" t="s">
         <v>17</v>
@@ -28045,10 +28051,10 @@
         <v>1299</v>
       </c>
       <c r="B761" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C761" s="22" t="n">
-        <v>4518</v>
+        <v>4517</v>
       </c>
       <c r="D761" s="29" t="s">
         <v>59</v>
@@ -28060,7 +28066,7 @@
         <v>182</v>
       </c>
       <c r="G761" s="22" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H761" s="22" t="s">
         <v>17</v>
@@ -28074,28 +28080,28 @@
         <v>1299</v>
       </c>
       <c r="B762" s="1" t="s">
-        <v>203</v>
+        <v>1317</v>
       </c>
       <c r="C762" s="22" t="n">
-        <v>4519</v>
+        <v>4518</v>
       </c>
       <c r="D762" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E762" s="22" t="n">
-        <v>100</v>
+        <v>59</v>
+      </c>
+      <c r="E762" s="22" t="s">
+        <v>1307</v>
       </c>
       <c r="F762" s="3" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="G762" s="22" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="H762" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I762" s="22" t="s">
-        <v>176</v>
+        <v>31</v>
       </c>
     </row>
     <row r="763" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28103,28 +28109,28 @@
         <v>1299</v>
       </c>
       <c r="B763" s="1" t="s">
-        <v>1318</v>
+        <v>203</v>
       </c>
       <c r="C763" s="22" t="n">
-        <v>4520</v>
+        <v>4519</v>
       </c>
       <c r="D763" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E763" s="22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F763" s="3" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="G763" s="22" t="s">
-        <v>1319</v>
+        <v>204</v>
       </c>
       <c r="H763" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I763" s="22" t="s">
-        <v>967</v>
+        <v>176</v>
       </c>
     </row>
     <row r="764" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28132,10 +28138,10 @@
         <v>1299</v>
       </c>
       <c r="B764" s="1" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C764" s="22" t="n">
-        <v>4521</v>
+        <v>4520</v>
       </c>
       <c r="D764" s="29" t="s">
         <v>20</v>
@@ -28147,7 +28153,7 @@
         <v>264</v>
       </c>
       <c r="G764" s="22" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="H764" s="22" t="s">
         <v>17</v>
@@ -28161,28 +28167,28 @@
         <v>1299</v>
       </c>
       <c r="B765" s="1" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C765" s="22" t="n">
-        <v>4522</v>
+        <v>4521</v>
       </c>
       <c r="D765" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E765" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F765" s="3" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="G765" s="22" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="H765" s="22" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I765" s="22" t="s">
-        <v>207</v>
+        <v>967</v>
       </c>
     </row>
     <row r="766" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28190,10 +28196,10 @@
         <v>1299</v>
       </c>
       <c r="B766" s="1" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C766" s="22" t="n">
-        <v>4523</v>
+        <v>4522</v>
       </c>
       <c r="D766" s="29" t="s">
         <v>20</v>
@@ -28205,7 +28211,7 @@
         <v>89</v>
       </c>
       <c r="G766" s="22" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="H766" s="22" t="s">
         <v>23</v>
@@ -28219,28 +28225,28 @@
         <v>1299</v>
       </c>
       <c r="B767" s="1" t="s">
-        <v>222</v>
+        <v>1324</v>
       </c>
       <c r="C767" s="22" t="n">
-        <v>4524</v>
+        <v>4523</v>
       </c>
       <c r="D767" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E767" s="22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F767" s="3" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="G767" s="22" t="s">
-        <v>223</v>
+        <v>1325</v>
       </c>
       <c r="H767" s="22" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I767" s="22" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="768" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28248,10 +28254,10 @@
         <v>1299</v>
       </c>
       <c r="B768" s="1" t="s">
-        <v>1326</v>
+        <v>222</v>
       </c>
       <c r="C768" s="22" t="n">
-        <v>4525</v>
+        <v>4524</v>
       </c>
       <c r="D768" s="29" t="s">
         <v>20</v>
@@ -28263,13 +28269,13 @@
         <v>264</v>
       </c>
       <c r="G768" s="22" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H768" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I768" s="22" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="769" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28277,28 +28283,28 @@
         <v>1299</v>
       </c>
       <c r="B769" s="1" t="s">
-        <v>216</v>
+        <v>1326</v>
       </c>
       <c r="C769" s="22" t="n">
-        <v>4526</v>
+        <v>4525</v>
       </c>
       <c r="D769" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E769" s="22" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F769" s="3" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="G769" s="22" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H769" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I769" s="22" t="s">
-        <v>91</v>
+        <v>227</v>
       </c>
     </row>
     <row r="770" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28306,28 +28312,28 @@
         <v>1299</v>
       </c>
       <c r="B770" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C770" s="22" t="n">
-        <v>4527</v>
+        <v>4526</v>
       </c>
       <c r="D770" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E770" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F770" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G770" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H770" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I770" s="22" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="771" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28335,10 +28341,10 @@
         <v>1299</v>
       </c>
       <c r="B771" s="1" t="s">
-        <v>306</v>
+        <v>219</v>
       </c>
       <c r="C771" s="22" t="n">
-        <v>4528</v>
+        <v>4527</v>
       </c>
       <c r="D771" s="29" t="s">
         <v>59</v>
@@ -28350,13 +28356,13 @@
         <v>94</v>
       </c>
       <c r="G771" s="22" t="s">
-        <v>307</v>
+        <v>220</v>
       </c>
       <c r="H771" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I771" s="22" t="s">
-        <v>308</v>
+        <v>96</v>
       </c>
     </row>
     <row r="772" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28364,28 +28370,28 @@
         <v>1299</v>
       </c>
       <c r="B772" s="1" t="s">
-        <v>1327</v>
+        <v>306</v>
       </c>
       <c r="C772" s="22" t="n">
-        <v>4529</v>
+        <v>4528</v>
       </c>
       <c r="D772" s="29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E772" s="22" t="n">
         <v>10</v>
       </c>
       <c r="F772" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G772" s="22" t="s">
-        <v>229</v>
+        <v>307</v>
       </c>
       <c r="H772" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I772" s="22" t="s">
-        <v>103</v>
+        <v>308</v>
       </c>
     </row>
     <row r="773" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28393,28 +28399,28 @@
         <v>1299</v>
       </c>
       <c r="B773" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C773" s="22" t="n">
-        <v>4530</v>
+        <v>4529</v>
       </c>
       <c r="D773" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E773" s="22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F773" s="3" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="G773" s="22" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H773" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I773" s="22" t="s">
-        <v>1329</v>
+        <v>103</v>
       </c>
     </row>
     <row r="774" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28422,10 +28428,10 @@
         <v>1299</v>
       </c>
       <c r="B774" s="1" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="C774" s="22" t="n">
-        <v>4531</v>
+        <v>4530</v>
       </c>
       <c r="D774" s="29" t="s">
         <v>20</v>
@@ -28437,13 +28443,13 @@
         <v>264</v>
       </c>
       <c r="G774" s="22" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="H774" s="22" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I774" s="22" t="s">
-        <v>238</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="775" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28451,10 +28457,10 @@
         <v>1299</v>
       </c>
       <c r="B775" s="1" t="s">
-        <v>239</v>
+        <v>1330</v>
       </c>
       <c r="C775" s="22" t="n">
-        <v>4532</v>
+        <v>4531</v>
       </c>
       <c r="D775" s="29" t="s">
         <v>20</v>
@@ -28466,13 +28472,13 @@
         <v>264</v>
       </c>
       <c r="G775" s="22" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H775" s="22" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I775" s="22" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="776" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28480,10 +28486,10 @@
         <v>1299</v>
       </c>
       <c r="B776" s="1" t="s">
-        <v>513</v>
+        <v>239</v>
       </c>
       <c r="C776" s="22" t="n">
-        <v>4533</v>
+        <v>4532</v>
       </c>
       <c r="D776" s="29" t="s">
         <v>20</v>
@@ -28495,7 +28501,7 @@
         <v>264</v>
       </c>
       <c r="G776" s="22" t="s">
-        <v>514</v>
+        <v>240</v>
       </c>
       <c r="H776" s="22" t="s">
         <v>17</v>
@@ -28509,10 +28515,10 @@
         <v>1299</v>
       </c>
       <c r="B777" s="1" t="s">
-        <v>1045</v>
+        <v>513</v>
       </c>
       <c r="C777" s="22" t="n">
-        <v>4534</v>
+        <v>4533</v>
       </c>
       <c r="D777" s="29" t="s">
         <v>20</v>
@@ -28524,7 +28530,7 @@
         <v>264</v>
       </c>
       <c r="G777" s="22" t="s">
-        <v>1046</v>
+        <v>514</v>
       </c>
       <c r="H777" s="22" t="s">
         <v>17</v>
@@ -28537,11 +28543,11 @@
       <c r="A778" s="22" t="s">
         <v>1299</v>
       </c>
-      <c r="B778" s="22" t="s">
-        <v>1331</v>
+      <c r="B778" s="1" t="s">
+        <v>1045</v>
       </c>
       <c r="C778" s="22" t="n">
-        <v>4535</v>
+        <v>4534</v>
       </c>
       <c r="D778" s="29" t="s">
         <v>20</v>
@@ -28553,7 +28559,7 @@
         <v>264</v>
       </c>
       <c r="G778" s="22" t="s">
-        <v>522</v>
+        <v>1046</v>
       </c>
       <c r="H778" s="22" t="s">
         <v>17</v>
@@ -28566,11 +28572,11 @@
       <c r="A779" s="22" t="s">
         <v>1299</v>
       </c>
-      <c r="B779" s="1" t="s">
-        <v>511</v>
+      <c r="B779" s="22" t="s">
+        <v>1331</v>
       </c>
       <c r="C779" s="22" t="n">
-        <v>4536</v>
+        <v>4535</v>
       </c>
       <c r="D779" s="29" t="s">
         <v>20</v>
@@ -28582,7 +28588,7 @@
         <v>264</v>
       </c>
       <c r="G779" s="22" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="H779" s="22" t="s">
         <v>17</v>
@@ -28596,10 +28602,10 @@
         <v>1299</v>
       </c>
       <c r="B780" s="1" t="s">
-        <v>1048</v>
+        <v>511</v>
       </c>
       <c r="C780" s="22" t="n">
-        <v>4537</v>
+        <v>4536</v>
       </c>
       <c r="D780" s="29" t="s">
         <v>20</v>
@@ -28611,7 +28617,7 @@
         <v>264</v>
       </c>
       <c r="G780" s="22" t="s">
-        <v>1049</v>
+        <v>512</v>
       </c>
       <c r="H780" s="22" t="s">
         <v>17</v>
@@ -28624,11 +28630,11 @@
       <c r="A781" s="22" t="s">
         <v>1299</v>
       </c>
-      <c r="B781" s="22" t="s">
-        <v>244</v>
+      <c r="B781" s="1" t="s">
+        <v>1048</v>
       </c>
       <c r="C781" s="22" t="n">
-        <v>4538</v>
+        <v>4537</v>
       </c>
       <c r="D781" s="29" t="s">
         <v>20</v>
@@ -28640,7 +28646,7 @@
         <v>264</v>
       </c>
       <c r="G781" s="22" t="s">
-        <v>245</v>
+        <v>1049</v>
       </c>
       <c r="H781" s="22" t="s">
         <v>17</v>
@@ -28653,11 +28659,11 @@
       <c r="A782" s="22" t="s">
         <v>1299</v>
       </c>
-      <c r="B782" s="1" t="s">
-        <v>1332</v>
+      <c r="B782" s="22" t="s">
+        <v>244</v>
       </c>
       <c r="C782" s="22" t="n">
-        <v>4539</v>
+        <v>4538</v>
       </c>
       <c r="D782" s="29" t="s">
         <v>20</v>
@@ -28669,7 +28675,7 @@
         <v>264</v>
       </c>
       <c r="G782" s="22" t="s">
-        <v>1051</v>
+        <v>245</v>
       </c>
       <c r="H782" s="22" t="s">
         <v>17</v>
@@ -28683,10 +28689,10 @@
         <v>1299</v>
       </c>
       <c r="B783" s="1" t="s">
-        <v>666</v>
+        <v>1332</v>
       </c>
       <c r="C783" s="22" t="n">
-        <v>4540</v>
+        <v>4539</v>
       </c>
       <c r="D783" s="29" t="s">
         <v>20</v>
@@ -28698,13 +28704,13 @@
         <v>264</v>
       </c>
       <c r="G783" s="22" t="s">
-        <v>667</v>
+        <v>1051</v>
       </c>
       <c r="H783" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I783" s="22" t="s">
-        <v>31</v>
+        <v>241</v>
       </c>
     </row>
     <row r="784" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28712,28 +28718,28 @@
         <v>1299</v>
       </c>
       <c r="B784" s="1" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C784" s="22" t="n">
-        <v>4541</v>
+        <v>4540</v>
       </c>
       <c r="D784" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E784" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F784" s="3" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="G784" s="22" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H784" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I784" s="22" t="s">
-        <v>348</v>
+        <v>31</v>
       </c>
     </row>
     <row r="785" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28741,28 +28747,28 @@
         <v>1299</v>
       </c>
       <c r="B785" s="1" t="s">
-        <v>1333</v>
+        <v>669</v>
       </c>
       <c r="C785" s="22" t="n">
-        <v>4542</v>
+        <v>4541</v>
       </c>
       <c r="D785" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E785" s="22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F785" s="3" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="G785" s="22" t="s">
-        <v>22</v>
+        <v>670</v>
       </c>
       <c r="H785" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I785" s="22" t="s">
-        <v>24</v>
+        <v>348</v>
       </c>
     </row>
     <row r="786" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28770,10 +28776,10 @@
         <v>1299</v>
       </c>
       <c r="B786" s="1" t="s">
-        <v>672</v>
+        <v>1333</v>
       </c>
       <c r="C786" s="22" t="n">
-        <v>4543</v>
+        <v>4542</v>
       </c>
       <c r="D786" s="29" t="s">
         <v>20</v>
@@ -28785,13 +28791,13 @@
         <v>264</v>
       </c>
       <c r="G786" s="22" t="s">
-        <v>673</v>
+        <v>22</v>
       </c>
       <c r="H786" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I786" s="22" t="s">
-        <v>674</v>
+        <v>24</v>
       </c>
     </row>
     <row r="787" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28799,28 +28805,28 @@
         <v>1299</v>
       </c>
       <c r="B787" s="1" t="s">
-        <v>639</v>
+        <v>672</v>
       </c>
       <c r="C787" s="22" t="n">
-        <v>4544</v>
+        <v>4543</v>
       </c>
       <c r="D787" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E787" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F787" s="3" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="G787" s="22" t="s">
-        <v>640</v>
+        <v>673</v>
       </c>
       <c r="H787" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I787" s="22" t="s">
-        <v>91</v>
+        <v>674</v>
       </c>
     </row>
     <row r="788" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28828,28 +28834,28 @@
         <v>1299</v>
       </c>
       <c r="B788" s="1" t="s">
-        <v>663</v>
+        <v>639</v>
       </c>
       <c r="C788" s="22" t="n">
-        <v>4545</v>
+        <v>4544</v>
       </c>
       <c r="D788" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E788" s="22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F788" s="3" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="G788" s="22" t="s">
-        <v>664</v>
+        <v>640</v>
       </c>
       <c r="H788" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I788" s="22" t="s">
-        <v>665</v>
+        <v>91</v>
       </c>
     </row>
     <row r="789" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28857,28 +28863,28 @@
         <v>1299</v>
       </c>
       <c r="B789" s="1" t="s">
-        <v>1334</v>
+        <v>663</v>
       </c>
       <c r="C789" s="22" t="n">
-        <v>4546</v>
+        <v>4545</v>
       </c>
       <c r="D789" s="29" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="E789" s="22" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F789" s="3" t="s">
-        <v>346</v>
+        <v>264</v>
       </c>
       <c r="G789" s="22" t="s">
-        <v>347</v>
+        <v>664</v>
       </c>
       <c r="H789" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I789" s="22" t="s">
-        <v>348</v>
+        <v>665</v>
       </c>
     </row>
     <row r="790" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28886,10 +28892,10 @@
         <v>1299</v>
       </c>
       <c r="B790" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C790" s="22" t="n">
-        <v>4548</v>
+        <v>4546</v>
       </c>
       <c r="D790" s="29" t="s">
         <v>155</v>
@@ -28901,7 +28907,7 @@
         <v>346</v>
       </c>
       <c r="G790" s="22" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="H790" s="22" t="s">
         <v>17</v>
@@ -28915,10 +28921,10 @@
         <v>1299</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C791" s="22" t="n">
-        <v>4550</v>
+        <v>4548</v>
       </c>
       <c r="D791" s="29" t="s">
         <v>155</v>
@@ -28930,7 +28936,7 @@
         <v>346</v>
       </c>
       <c r="G791" s="22" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H791" s="22" t="s">
         <v>17</v>
@@ -28944,10 +28950,10 @@
         <v>1299</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C792" s="22" t="n">
-        <v>4552</v>
+        <v>4550</v>
       </c>
       <c r="D792" s="29" t="s">
         <v>155</v>
@@ -28959,7 +28965,7 @@
         <v>346</v>
       </c>
       <c r="G792" s="22" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H792" s="22" t="s">
         <v>17</v>
@@ -28973,10 +28979,10 @@
         <v>1299</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C793" s="22" t="n">
-        <v>4554</v>
+        <v>4552</v>
       </c>
       <c r="D793" s="29" t="s">
         <v>155</v>
@@ -28988,7 +28994,7 @@
         <v>346</v>
       </c>
       <c r="G793" s="22" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H793" s="22" t="s">
         <v>17</v>
@@ -29002,10 +29008,10 @@
         <v>1299</v>
       </c>
       <c r="B794" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C794" s="22" t="n">
-        <v>4556</v>
+        <v>4554</v>
       </c>
       <c r="D794" s="29" t="s">
         <v>155</v>
@@ -29017,7 +29023,7 @@
         <v>346</v>
       </c>
       <c r="G794" s="22" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H794" s="22" t="s">
         <v>17</v>
@@ -29031,10 +29037,10 @@
         <v>1299</v>
       </c>
       <c r="B795" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C795" s="22" t="n">
-        <v>4558</v>
+        <v>4556</v>
       </c>
       <c r="D795" s="29" t="s">
         <v>155</v>
@@ -29046,7 +29052,7 @@
         <v>346</v>
       </c>
       <c r="G795" s="22" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H795" s="22" t="s">
         <v>17</v>
@@ -29060,10 +29066,10 @@
         <v>1299</v>
       </c>
       <c r="B796" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C796" s="22" t="n">
-        <v>4560</v>
+        <v>4558</v>
       </c>
       <c r="D796" s="29" t="s">
         <v>155</v>
@@ -29075,7 +29081,7 @@
         <v>346</v>
       </c>
       <c r="G796" s="22" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H796" s="22" t="s">
         <v>17</v>
@@ -29089,10 +29095,10 @@
         <v>1299</v>
       </c>
       <c r="B797" s="1" t="s">
-        <v>367</v>
+        <v>1341</v>
       </c>
       <c r="C797" s="22" t="n">
-        <v>4562</v>
+        <v>4560</v>
       </c>
       <c r="D797" s="29" t="s">
         <v>155</v>
@@ -29104,7 +29110,7 @@
         <v>346</v>
       </c>
       <c r="G797" s="22" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H797" s="22" t="s">
         <v>17</v>
@@ -29118,10 +29124,10 @@
         <v>1299</v>
       </c>
       <c r="B798" s="1" t="s">
-        <v>1060</v>
+        <v>367</v>
       </c>
       <c r="C798" s="22" t="n">
-        <v>4564</v>
+        <v>4562</v>
       </c>
       <c r="D798" s="29" t="s">
         <v>155</v>
@@ -29133,7 +29139,7 @@
         <v>346</v>
       </c>
       <c r="G798" s="22" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H798" s="22" t="s">
         <v>17</v>
@@ -29147,10 +29153,10 @@
         <v>1299</v>
       </c>
       <c r="B799" s="1" t="s">
-        <v>1342</v>
+        <v>1060</v>
       </c>
       <c r="C799" s="22" t="n">
-        <v>4566</v>
+        <v>4564</v>
       </c>
       <c r="D799" s="29" t="s">
         <v>155</v>
@@ -29162,7 +29168,7 @@
         <v>346</v>
       </c>
       <c r="G799" s="22" t="s">
-        <v>1343</v>
+        <v>370</v>
       </c>
       <c r="H799" s="22" t="s">
         <v>17</v>
@@ -29176,10 +29182,10 @@
         <v>1299</v>
       </c>
       <c r="B800" s="1" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C800" s="22" t="n">
-        <v>4568</v>
+        <v>4566</v>
       </c>
       <c r="D800" s="29" t="s">
         <v>155</v>
@@ -29191,7 +29197,7 @@
         <v>346</v>
       </c>
       <c r="G800" s="22" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="H800" s="22" t="s">
         <v>17</v>
@@ -29205,10 +29211,10 @@
         <v>1299</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>1061</v>
+        <v>1344</v>
       </c>
       <c r="C801" s="22" t="n">
-        <v>4570</v>
+        <v>4568</v>
       </c>
       <c r="D801" s="29" t="s">
         <v>155</v>
@@ -29220,7 +29226,7 @@
         <v>346</v>
       </c>
       <c r="G801" s="22" t="s">
-        <v>1062</v>
+        <v>1345</v>
       </c>
       <c r="H801" s="22" t="s">
         <v>17</v>
@@ -29234,10 +29240,10 @@
         <v>1299</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C802" s="22" t="n">
-        <v>4572</v>
+        <v>4570</v>
       </c>
       <c r="D802" s="29" t="s">
         <v>155</v>
@@ -29249,7 +29255,7 @@
         <v>346</v>
       </c>
       <c r="G802" s="22" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="H802" s="22" t="s">
         <v>17</v>
@@ -29263,22 +29269,22 @@
         <v>1299</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>651</v>
+        <v>1063</v>
       </c>
       <c r="C803" s="22" t="n">
-        <v>4574</v>
+        <v>4572</v>
       </c>
       <c r="D803" s="29" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="E803" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F803" s="3" t="s">
-        <v>89</v>
+        <v>346</v>
       </c>
       <c r="G803" s="22" t="s">
-        <v>652</v>
+        <v>1064</v>
       </c>
       <c r="H803" s="22" t="s">
         <v>17</v>
@@ -29292,28 +29298,28 @@
         <v>1299</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C804" s="22" t="n">
-        <v>4575</v>
+        <v>4574</v>
       </c>
       <c r="D804" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E804" s="22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F804" s="3" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="G804" s="22" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H804" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I804" s="22" t="s">
-        <v>31</v>
+        <v>348</v>
       </c>
     </row>
     <row r="805" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29321,28 +29327,28 @@
         <v>1299</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C805" s="22" t="n">
-        <v>4576</v>
+        <v>4575</v>
       </c>
       <c r="D805" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E805" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F805" s="3" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="G805" s="22" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="H805" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I805" s="22" t="s">
-        <v>348</v>
+        <v>31</v>
       </c>
     </row>
     <row r="806" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29350,28 +29356,28 @@
         <v>1299</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C806" s="22" t="n">
-        <v>4577</v>
+        <v>4576</v>
       </c>
       <c r="D806" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E806" s="1" t="n">
-        <v>1</v>
+      <c r="E806" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="F806" s="3" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="G806" s="22" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="H806" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="I806" s="1" t="s">
-        <v>31</v>
+      <c r="I806" s="22" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="807" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29379,43 +29385,39 @@
         <v>1299</v>
       </c>
       <c r="B807" s="1" t="s">
-        <v>683</v>
+        <v>660</v>
       </c>
       <c r="C807" s="22" t="n">
-        <v>4578</v>
+        <v>4577</v>
       </c>
       <c r="D807" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E807" s="22" t="n">
-        <v>10</v>
+      <c r="E807" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="F807" s="3" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="G807" s="22" t="s">
-        <v>684</v>
+        <v>661</v>
       </c>
       <c r="H807" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="I807" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="J807" s="22"/>
-      <c r="K807" s="22"/>
-      <c r="L807" s="22"/>
-      <c r="M807" s="22"/>
+      <c r="I807" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="808" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A808" s="22" t="s">
         <v>1299</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C808" s="22" t="n">
-        <v>4579</v>
+        <v>4578</v>
       </c>
       <c r="D808" s="29" t="s">
         <v>20</v>
@@ -29427,7 +29429,7 @@
         <v>89</v>
       </c>
       <c r="G808" s="22" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H808" s="22" t="s">
         <v>17</v>
@@ -29445,10 +29447,10 @@
         <v>1299</v>
       </c>
       <c r="B809" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C809" s="22" t="n">
-        <v>4580</v>
+        <v>4579</v>
       </c>
       <c r="D809" s="29" t="s">
         <v>20</v>
@@ -29460,7 +29462,7 @@
         <v>89</v>
       </c>
       <c r="G809" s="22" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H809" s="22" t="s">
         <v>17</v>
@@ -29478,10 +29480,10 @@
         <v>1299</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C810" s="22" t="n">
-        <v>4581</v>
+        <v>4580</v>
       </c>
       <c r="D810" s="29" t="s">
         <v>20</v>
@@ -29493,7 +29495,7 @@
         <v>89</v>
       </c>
       <c r="G810" s="22" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="H810" s="22" t="s">
         <v>17</v>
@@ -29511,10 +29513,10 @@
         <v>1299</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C811" s="22" t="n">
-        <v>4582</v>
+        <v>4581</v>
       </c>
       <c r="D811" s="29" t="s">
         <v>20</v>
@@ -29526,7 +29528,7 @@
         <v>89</v>
       </c>
       <c r="G811" s="22" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H811" s="22" t="s">
         <v>17</v>
@@ -29544,10 +29546,10 @@
         <v>1299</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C812" s="22" t="n">
-        <v>4583</v>
+        <v>4582</v>
       </c>
       <c r="D812" s="29" t="s">
         <v>20</v>
@@ -29559,7 +29561,7 @@
         <v>89</v>
       </c>
       <c r="G812" s="22" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H812" s="22" t="s">
         <v>17</v>
@@ -29577,10 +29579,10 @@
         <v>1299</v>
       </c>
       <c r="B813" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C813" s="22" t="n">
-        <v>4584</v>
+        <v>4583</v>
       </c>
       <c r="D813" s="29" t="s">
         <v>20</v>
@@ -29592,7 +29594,7 @@
         <v>89</v>
       </c>
       <c r="G813" s="22" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H813" s="22" t="s">
         <v>17</v>
@@ -29610,10 +29612,10 @@
         <v>1299</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C814" s="22" t="n">
-        <v>4585</v>
+        <v>4584</v>
       </c>
       <c r="D814" s="29" t="s">
         <v>20</v>
@@ -29625,7 +29627,7 @@
         <v>89</v>
       </c>
       <c r="G814" s="22" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H814" s="22" t="s">
         <v>17</v>
@@ -29643,28 +29645,28 @@
         <v>1299</v>
       </c>
       <c r="B815" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C815" s="22" t="n">
-        <v>4586</v>
+        <v>4585</v>
       </c>
       <c r="D815" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E815" s="22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F815" s="3" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="G815" s="22" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H815" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I815" s="22" t="s">
-        <v>31</v>
+        <v>348</v>
       </c>
       <c r="J815" s="22"/>
       <c r="K815" s="22"/>
@@ -29676,10 +29678,10 @@
         <v>1299</v>
       </c>
       <c r="B816" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C816" s="22" t="n">
-        <v>4587</v>
+        <v>4586</v>
       </c>
       <c r="D816" s="29" t="s">
         <v>20</v>
@@ -29691,7 +29693,7 @@
         <v>264</v>
       </c>
       <c r="G816" s="22" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H816" s="22" t="s">
         <v>17</v>
@@ -29709,10 +29711,10 @@
         <v>1299</v>
       </c>
       <c r="B817" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C817" s="22" t="n">
-        <v>4588</v>
+        <v>4587</v>
       </c>
       <c r="D817" s="29" t="s">
         <v>20</v>
@@ -29724,7 +29726,7 @@
         <v>264</v>
       </c>
       <c r="G817" s="22" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H817" s="22" t="s">
         <v>17</v>
@@ -29742,10 +29744,10 @@
         <v>1299</v>
       </c>
       <c r="B818" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C818" s="22" t="n">
-        <v>4589</v>
+        <v>4588</v>
       </c>
       <c r="D818" s="29" t="s">
         <v>20</v>
@@ -29757,7 +29759,7 @@
         <v>264</v>
       </c>
       <c r="G818" s="22" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H818" s="22" t="s">
         <v>17</v>
@@ -29775,10 +29777,10 @@
         <v>1299</v>
       </c>
       <c r="B819" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C819" s="22" t="n">
-        <v>4590</v>
+        <v>4589</v>
       </c>
       <c r="D819" s="29" t="s">
         <v>20</v>
@@ -29790,7 +29792,7 @@
         <v>264</v>
       </c>
       <c r="G819" s="22" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H819" s="22" t="s">
         <v>17</v>
@@ -29808,10 +29810,10 @@
         <v>1299</v>
       </c>
       <c r="B820" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C820" s="22" t="n">
-        <v>4591</v>
+        <v>4590</v>
       </c>
       <c r="D820" s="29" t="s">
         <v>20</v>
@@ -29823,7 +29825,7 @@
         <v>264</v>
       </c>
       <c r="G820" s="22" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H820" s="22" t="s">
         <v>17</v>
@@ -29841,10 +29843,10 @@
         <v>1299</v>
       </c>
       <c r="B821" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C821" s="22" t="n">
-        <v>4592</v>
+        <v>4591</v>
       </c>
       <c r="D821" s="29" t="s">
         <v>20</v>
@@ -29856,7 +29858,7 @@
         <v>264</v>
       </c>
       <c r="G821" s="22" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H821" s="22" t="s">
         <v>17</v>
@@ -29874,10 +29876,10 @@
         <v>1299</v>
       </c>
       <c r="B822" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C822" s="22" t="n">
-        <v>4593</v>
+        <v>4592</v>
       </c>
       <c r="D822" s="29" t="s">
         <v>20</v>
@@ -29889,7 +29891,7 @@
         <v>264</v>
       </c>
       <c r="G822" s="22" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H822" s="22" t="s">
         <v>17</v>
@@ -29907,39 +29909,43 @@
         <v>1299</v>
       </c>
       <c r="B823" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="C823" s="1" t="n">
-        <v>4594</v>
+        <v>713</v>
+      </c>
+      <c r="C823" s="22" t="n">
+        <v>4593</v>
       </c>
       <c r="D823" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E823" s="1" t="n">
-        <v>10</v>
+      <c r="E823" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="F823" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G823" s="1" t="s">
-        <v>676</v>
+        <v>264</v>
+      </c>
+      <c r="G823" s="22" t="s">
+        <v>714</v>
       </c>
       <c r="H823" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="I823" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="I823" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J823" s="22"/>
+      <c r="K823" s="22"/>
+      <c r="L823" s="22"/>
+      <c r="M823" s="22"/>
     </row>
     <row r="824" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A824" s="22" t="s">
         <v>1299</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>4595</v>
+        <v>4594</v>
       </c>
       <c r="D824" s="29" t="s">
         <v>20</v>
@@ -29951,7 +29957,7 @@
         <v>89</v>
       </c>
       <c r="G824" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H824" s="22" t="s">
         <v>17</v>
@@ -29965,10 +29971,10 @@
         <v>1299</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>4596</v>
+        <v>4595</v>
       </c>
       <c r="D825" s="29" t="s">
         <v>20</v>
@@ -29980,7 +29986,7 @@
         <v>89</v>
       </c>
       <c r="G825" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H825" s="22" t="s">
         <v>17</v>
@@ -29994,10 +30000,10 @@
         <v>1299</v>
       </c>
       <c r="B826" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>4597</v>
+        <v>4596</v>
       </c>
       <c r="D826" s="29" t="s">
         <v>20</v>
@@ -30009,7 +30015,7 @@
         <v>89</v>
       </c>
       <c r="G826" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H826" s="22" t="s">
         <v>17</v>
@@ -30023,28 +30029,28 @@
         <v>1299</v>
       </c>
       <c r="B827" s="1" t="s">
-        <v>715</v>
+        <v>681</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>4598</v>
+        <v>4597</v>
       </c>
       <c r="D827" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F827" s="3" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="G827" s="1" t="s">
-        <v>716</v>
+        <v>682</v>
       </c>
       <c r="H827" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I827" s="1" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
     </row>
     <row r="828" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30052,10 +30058,10 @@
         <v>1299</v>
       </c>
       <c r="B828" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>4599</v>
+        <v>4598</v>
       </c>
       <c r="D828" s="29" t="s">
         <v>20</v>
@@ -30067,7 +30073,7 @@
         <v>264</v>
       </c>
       <c r="G828" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H828" s="22" t="s">
         <v>17</v>
@@ -30081,10 +30087,10 @@
         <v>1299</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>4600</v>
+        <v>4599</v>
       </c>
       <c r="D829" s="29" t="s">
         <v>20</v>
@@ -30096,7 +30102,7 @@
         <v>264</v>
       </c>
       <c r="G829" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="H829" s="22" t="s">
         <v>17</v>
@@ -30110,10 +30116,10 @@
         <v>1299</v>
       </c>
       <c r="B830" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>4601</v>
+        <v>4600</v>
       </c>
       <c r="D830" s="29" t="s">
         <v>20</v>
@@ -30125,7 +30131,7 @@
         <v>264</v>
       </c>
       <c r="G830" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="H830" s="22" t="s">
         <v>17</v>
@@ -30135,14 +30141,14 @@
       </c>
     </row>
     <row r="831" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A831" s="1" t="s">
+      <c r="A831" s="22" t="s">
         <v>1299</v>
       </c>
       <c r="B831" s="1" t="s">
-        <v>1082</v>
+        <v>721</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>4602</v>
+        <v>4601</v>
       </c>
       <c r="D831" s="29" t="s">
         <v>20</v>
@@ -30154,13 +30160,13 @@
         <v>264</v>
       </c>
       <c r="G831" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="H831" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="H831" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I831" s="1" t="s">
-        <v>626</v>
+        <v>31</v>
       </c>
     </row>
     <row r="832" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30168,60 +30174,60 @@
         <v>1299</v>
       </c>
       <c r="B832" s="1" t="s">
-        <v>669</v>
+        <v>1082</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>4603</v>
-      </c>
-      <c r="D832" s="2" t="s">
-        <v>155</v>
+        <v>4602</v>
+      </c>
+      <c r="D832" s="29" t="s">
+        <v>20</v>
       </c>
       <c r="E832" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F832" s="3" t="s">
-        <v>723</v>
+        <v>264</v>
       </c>
       <c r="G832" s="1" t="s">
-        <v>670</v>
+        <v>520</v>
       </c>
       <c r="H832" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I832" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="J832" s="1" t="s">
-        <v>671</v>
+        <v>626</v>
       </c>
     </row>
     <row r="833" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A833" s="1" t="s">
         <v>1299</v>
       </c>
-      <c r="B833" s="21" t="s">
-        <v>724</v>
+      <c r="B833" s="1" t="s">
+        <v>669</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>4605</v>
-      </c>
-      <c r="D833" s="29" t="s">
-        <v>20</v>
+        <v>4603</v>
+      </c>
+      <c r="D833" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="E833" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F833" s="3" t="s">
-        <v>264</v>
+        <v>723</v>
       </c>
       <c r="G833" s="1" t="s">
-        <v>725</v>
+        <v>670</v>
       </c>
       <c r="H833" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I833" s="22" t="s">
-        <v>674</v>
+      <c r="I833" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J833" s="1" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="834" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30229,10 +30235,10 @@
         <v>1299</v>
       </c>
       <c r="B834" s="21" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>4606</v>
+        <v>4605</v>
       </c>
       <c r="D834" s="29" t="s">
         <v>20</v>
@@ -30244,7 +30250,7 @@
         <v>264</v>
       </c>
       <c r="G834" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="H834" s="1" t="s">
         <v>17</v>
@@ -30258,10 +30264,10 @@
         <v>1299</v>
       </c>
       <c r="B835" s="21" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>4607</v>
+        <v>4606</v>
       </c>
       <c r="D835" s="29" t="s">
         <v>20</v>
@@ -30273,7 +30279,7 @@
         <v>264</v>
       </c>
       <c r="G835" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="H835" s="1" t="s">
         <v>17</v>
@@ -30287,10 +30293,10 @@
         <v>1299</v>
       </c>
       <c r="B836" s="21" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>4608</v>
+        <v>4607</v>
       </c>
       <c r="D836" s="29" t="s">
         <v>20</v>
@@ -30302,7 +30308,7 @@
         <v>264</v>
       </c>
       <c r="G836" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="H836" s="1" t="s">
         <v>17</v>
@@ -30316,10 +30322,10 @@
         <v>1299</v>
       </c>
       <c r="B837" s="21" t="s">
-        <v>1346</v>
+        <v>730</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>4609</v>
+        <v>4608</v>
       </c>
       <c r="D837" s="29" t="s">
         <v>20</v>
@@ -30331,42 +30337,42 @@
         <v>264</v>
       </c>
       <c r="G837" s="1" t="s">
-        <v>1347</v>
+        <v>731</v>
       </c>
       <c r="H837" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I837" s="22" t="s">
-        <v>1348</v>
+        <v>674</v>
       </c>
     </row>
     <row r="838" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A838" s="1" t="s">
         <v>1299</v>
       </c>
-      <c r="B838" s="22" t="s">
-        <v>1349</v>
+      <c r="B838" s="21" t="s">
+        <v>1346</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>4610</v>
+        <v>4609</v>
       </c>
       <c r="D838" s="29" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="E838" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F838" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G838" s="21" t="s">
-        <v>1350</v>
+        <v>264</v>
+      </c>
+      <c r="G838" s="1" t="s">
+        <v>1347</v>
       </c>
       <c r="H838" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I838" s="22" t="s">
-        <v>31</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="839" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30374,28 +30380,28 @@
         <v>1299</v>
       </c>
       <c r="B839" s="22" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>4612</v>
+        <v>4610</v>
       </c>
       <c r="D839" s="29" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="E839" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F839" s="3" t="s">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="G839" s="21" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="H839" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I839" s="22" t="s">
-        <v>1353</v>
+        <v>31</v>
       </c>
     </row>
     <row r="840" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30403,10 +30409,10 @@
         <v>1299</v>
       </c>
       <c r="B840" s="22" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>4613</v>
+        <v>4612</v>
       </c>
       <c r="D840" s="29" t="s">
         <v>20</v>
@@ -30418,13 +30424,13 @@
         <v>264</v>
       </c>
       <c r="G840" s="21" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="H840" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I840" s="22" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="841" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30432,10 +30438,10 @@
         <v>1299</v>
       </c>
       <c r="B841" s="22" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="D841" s="29" t="s">
         <v>20</v>
@@ -30447,24 +30453,24 @@
         <v>264</v>
       </c>
       <c r="G841" s="21" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="H841" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I841" s="22" t="s">
-        <v>103</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="842" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A842" s="1" t="s">
         <v>1299</v>
       </c>
-      <c r="B842" s="1" t="s">
-        <v>342</v>
+      <c r="B842" s="22" t="s">
+        <v>1357</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>4615</v>
+        <v>4614</v>
       </c>
       <c r="D842" s="29" t="s">
         <v>20</v>
@@ -30475,14 +30481,14 @@
       <c r="F842" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G842" s="1" t="s">
-        <v>1359</v>
+      <c r="G842" s="21" t="s">
+        <v>1358</v>
       </c>
       <c r="H842" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I842" s="1" t="s">
-        <v>344</v>
+        <v>23</v>
+      </c>
+      <c r="I842" s="22" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="843" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30490,12 +30496,29 @@
         <v>1299</v>
       </c>
       <c r="B843" s="1" t="s">
-        <v>117</v>
+        <v>342</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>4616</v>
-      </c>
-      <c r="D843" s="29"/>
+        <v>4615</v>
+      </c>
+      <c r="D843" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E843" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F843" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G843" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H843" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I843" s="1" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="844" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A844" s="1" t="s">
@@ -30505,7 +30528,7 @@
         <v>117</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>4617</v>
+        <v>4616</v>
       </c>
       <c r="D844" s="29"/>
     </row>
@@ -30517,7 +30540,7 @@
         <v>117</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>4618</v>
+        <v>4617</v>
       </c>
       <c r="D845" s="29"/>
     </row>
@@ -30529,7 +30552,7 @@
         <v>117</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>4619</v>
+        <v>4618</v>
       </c>
       <c r="D846" s="29"/>
     </row>
@@ -30538,45 +30561,41 @@
         <v>1299</v>
       </c>
       <c r="B847" s="1" t="s">
-        <v>1360</v>
+        <v>117</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>4620</v>
-      </c>
-      <c r="D847" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E847" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F847" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G847" s="22" t="s">
-        <v>1361</v>
-      </c>
-      <c r="H847" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I847" s="22" t="s">
-        <v>241</v>
-      </c>
+        <v>4619</v>
+      </c>
+      <c r="D847" s="29"/>
     </row>
     <row r="848" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A848" s="1" t="s">
         <v>1299</v>
       </c>
       <c r="B848" s="1" t="s">
-        <v>117</v>
+        <v>1360</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>4621</v>
-      </c>
-      <c r="D848" s="29"/>
-      <c r="E848" s="22"/>
-      <c r="G848" s="22"/>
-      <c r="H848" s="22"/>
-      <c r="I848" s="22"/>
+        <v>4620</v>
+      </c>
+      <c r="D848" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E848" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F848" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G848" s="22" t="s">
+        <v>1361</v>
+      </c>
+      <c r="H848" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I848" s="22" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="849" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A849" s="1" t="s">
@@ -30586,7 +30605,7 @@
         <v>117</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>4622</v>
+        <v>4621</v>
       </c>
       <c r="D849" s="29"/>
       <c r="E849" s="22"/>
@@ -30602,7 +30621,7 @@
         <v>117</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>4623</v>
+        <v>4622</v>
       </c>
       <c r="D850" s="29"/>
       <c r="E850" s="22"/>
@@ -30618,7 +30637,7 @@
         <v>117</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>4624</v>
+        <v>4623</v>
       </c>
       <c r="D851" s="29"/>
       <c r="E851" s="22"/>
@@ -30634,7 +30653,7 @@
         <v>117</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>4625</v>
+        <v>4624</v>
       </c>
       <c r="D852" s="29"/>
       <c r="E852" s="22"/>
@@ -30650,7 +30669,7 @@
         <v>117</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>4626</v>
+        <v>4625</v>
       </c>
       <c r="D853" s="29"/>
       <c r="E853" s="22"/>
@@ -30666,7 +30685,7 @@
         <v>117</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>4627</v>
+        <v>4626</v>
       </c>
       <c r="D854" s="29"/>
       <c r="E854" s="22"/>
@@ -30682,7 +30701,7 @@
         <v>117</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>4628</v>
+        <v>4627</v>
       </c>
       <c r="D855" s="29"/>
       <c r="E855" s="22"/>
@@ -30698,7 +30717,7 @@
         <v>117</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>4629</v>
+        <v>4628</v>
       </c>
       <c r="D856" s="29"/>
       <c r="E856" s="22"/>
@@ -30710,40 +30729,27 @@
       <c r="A857" s="1" t="s">
         <v>1299</v>
       </c>
-      <c r="B857" s="21" t="s">
-        <v>732</v>
+      <c r="B857" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>4630</v>
-      </c>
-      <c r="D857" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E857" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F857" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G857" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="H857" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I857" s="22" t="s">
-        <v>398</v>
-      </c>
+        <v>4629</v>
+      </c>
+      <c r="D857" s="29"/>
+      <c r="E857" s="22"/>
+      <c r="G857" s="22"/>
+      <c r="H857" s="22"/>
+      <c r="I857" s="22"/>
     </row>
     <row r="858" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A858" s="1" t="s">
         <v>1299</v>
       </c>
       <c r="B858" s="21" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>4631</v>
+        <v>4630</v>
       </c>
       <c r="D858" s="2" t="s">
         <v>20</v>
@@ -30755,7 +30761,7 @@
         <v>264</v>
       </c>
       <c r="G858" s="1" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="H858" s="1" t="s">
         <v>17</v>
@@ -30769,10 +30775,10 @@
         <v>1299</v>
       </c>
       <c r="B859" s="21" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>4632</v>
+        <v>4631</v>
       </c>
       <c r="D859" s="2" t="s">
         <v>20</v>
@@ -30784,7 +30790,7 @@
         <v>264</v>
       </c>
       <c r="G859" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H859" s="1" t="s">
         <v>17</v>
@@ -30798,10 +30804,10 @@
         <v>1299</v>
       </c>
       <c r="B860" s="21" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>4633</v>
+        <v>4632</v>
       </c>
       <c r="D860" s="2" t="s">
         <v>20</v>
@@ -30813,7 +30819,7 @@
         <v>264</v>
       </c>
       <c r="G860" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="H860" s="1" t="s">
         <v>17</v>
@@ -30824,15 +30830,15 @@
     </row>
     <row r="861" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A861" s="1" t="s">
-        <v>1362</v>
-      </c>
-      <c r="B861" s="1" t="s">
-        <v>1363</v>
+        <v>1299</v>
+      </c>
+      <c r="B861" s="21" t="s">
+        <v>739</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>4700</v>
-      </c>
-      <c r="D861" s="29" t="s">
+        <v>4633</v>
+      </c>
+      <c r="D861" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E861" s="1" t="n">
@@ -30842,24 +30848,24 @@
         <v>264</v>
       </c>
       <c r="G861" s="1" t="s">
-        <v>231</v>
+        <v>740</v>
       </c>
       <c r="H861" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I861" s="1" t="s">
-        <v>1364</v>
+      <c r="I861" s="22" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="862" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A862" s="1" t="s">
-        <v>928</v>
+        <v>1362</v>
       </c>
       <c r="B862" s="1" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>4701</v>
+        <v>4700</v>
       </c>
       <c r="D862" s="29" t="s">
         <v>20</v>
@@ -30871,13 +30877,13 @@
         <v>264</v>
       </c>
       <c r="G862" s="1" t="s">
-        <v>1366</v>
+        <v>231</v>
       </c>
       <c r="H862" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I862" s="1" t="s">
-        <v>398</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="863" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30885,10 +30891,10 @@
         <v>928</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>844</v>
+        <v>1365</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>4702</v>
+        <v>4701</v>
       </c>
       <c r="D863" s="29" t="s">
         <v>20</v>
@@ -30899,14 +30905,14 @@
       <c r="F863" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G863" s="21" t="s">
-        <v>1367</v>
+      <c r="G863" s="1" t="s">
+        <v>1366</v>
       </c>
       <c r="H863" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I863" s="1" t="s">
-        <v>1368</v>
+        <v>398</v>
       </c>
     </row>
     <row r="864" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30914,10 +30920,10 @@
         <v>928</v>
       </c>
       <c r="B864" s="1" t="s">
-        <v>1369</v>
+        <v>844</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>4703</v>
+        <v>4702</v>
       </c>
       <c r="D864" s="29" t="s">
         <v>20</v>
@@ -30926,16 +30932,16 @@
         <v>1</v>
       </c>
       <c r="F864" s="3" t="s">
-        <v>101</v>
+        <v>264</v>
       </c>
       <c r="G864" s="21" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="H864" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I864" s="1" t="s">
-        <v>103</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="865" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30943,10 +30949,10 @@
         <v>928</v>
       </c>
       <c r="B865" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>4704</v>
+        <v>4703</v>
       </c>
       <c r="D865" s="29" t="s">
         <v>20</v>
@@ -30958,7 +30964,7 @@
         <v>101</v>
       </c>
       <c r="G865" s="21" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="H865" s="1" t="s">
         <v>23</v>
@@ -30969,28 +30975,31 @@
     </row>
     <row r="866" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A866" s="1" t="s">
-        <v>1373</v>
-      </c>
-      <c r="B866" s="22" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C866" s="22" t="n">
-        <v>4800</v>
+        <v>928</v>
+      </c>
+      <c r="B866" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C866" s="1" t="n">
+        <v>4704</v>
       </c>
       <c r="D866" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E866" s="22" t="n">
+      <c r="E866" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F866" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G866" s="22" t="s">
-        <v>1023</v>
+        <v>101</v>
+      </c>
+      <c r="G866" s="21" t="s">
+        <v>1372</v>
       </c>
       <c r="H866" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="I866" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="867" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30998,22 +31007,22 @@
         <v>1373</v>
       </c>
       <c r="B867" s="22" t="s">
-        <v>1052</v>
+        <v>1022</v>
       </c>
       <c r="C867" s="22" t="n">
-        <v>4801</v>
+        <v>4800</v>
       </c>
       <c r="D867" s="29" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="E867" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F867" s="3" t="s">
-        <v>723</v>
+        <v>264</v>
       </c>
       <c r="G867" s="22" t="s">
-        <v>1053</v>
+        <v>1023</v>
       </c>
       <c r="H867" s="1" t="s">
         <v>17</v>
@@ -31024,28 +31033,25 @@
         <v>1373</v>
       </c>
       <c r="B868" s="22" t="s">
-        <v>663</v>
+        <v>1052</v>
       </c>
       <c r="C868" s="22" t="n">
-        <v>4803</v>
+        <v>4801</v>
       </c>
       <c r="D868" s="29" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="E868" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F868" s="3" t="s">
-        <v>264</v>
+        <v>723</v>
       </c>
       <c r="G868" s="22" t="s">
-        <v>664</v>
+        <v>1053</v>
       </c>
       <c r="H868" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I868" s="22" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="869" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31053,28 +31059,28 @@
         <v>1373</v>
       </c>
       <c r="B869" s="22" t="s">
-        <v>216</v>
+        <v>663</v>
       </c>
       <c r="C869" s="22" t="n">
-        <v>4804</v>
+        <v>4803</v>
       </c>
       <c r="D869" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E869" s="22" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F869" s="3" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="G869" s="22" t="s">
-        <v>218</v>
+        <v>664</v>
       </c>
       <c r="H869" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I869" s="22" t="s">
-        <v>91</v>
+        <v>665</v>
       </c>
     </row>
     <row r="870" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31082,28 +31088,28 @@
         <v>1373</v>
       </c>
       <c r="B870" s="22" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C870" s="22" t="n">
-        <v>4805</v>
+        <v>4804</v>
       </c>
       <c r="D870" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E870" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F870" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G870" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H870" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I870" s="22" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="871" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31111,10 +31117,10 @@
         <v>1373</v>
       </c>
       <c r="B871" s="22" t="s">
-        <v>306</v>
+        <v>219</v>
       </c>
       <c r="C871" s="22" t="n">
-        <v>4806</v>
+        <v>4805</v>
       </c>
       <c r="D871" s="29" t="s">
         <v>59</v>
@@ -31126,13 +31132,13 @@
         <v>94</v>
       </c>
       <c r="G871" s="22" t="s">
-        <v>307</v>
+        <v>220</v>
       </c>
       <c r="H871" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I871" s="22" t="s">
-        <v>308</v>
+        <v>96</v>
       </c>
     </row>
     <row r="872" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31140,28 +31146,28 @@
         <v>1373</v>
       </c>
       <c r="B872" s="22" t="s">
-        <v>1330</v>
+        <v>306</v>
       </c>
       <c r="C872" s="22" t="n">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="D872" s="29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E872" s="22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F872" s="3" t="s">
-        <v>264</v>
+        <v>94</v>
       </c>
       <c r="G872" s="22" t="s">
-        <v>237</v>
+        <v>307</v>
       </c>
       <c r="H872" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I872" s="22" t="s">
-        <v>637</v>
+        <v>308</v>
       </c>
     </row>
     <row r="873" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31169,10 +31175,10 @@
         <v>1373</v>
       </c>
       <c r="B873" s="22" t="s">
-        <v>374</v>
+        <v>1330</v>
       </c>
       <c r="C873" s="22" t="n">
-        <v>4808</v>
+        <v>4807</v>
       </c>
       <c r="D873" s="29" t="s">
         <v>20</v>
@@ -31184,13 +31190,13 @@
         <v>264</v>
       </c>
       <c r="G873" s="22" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="H873" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I873" s="22" t="s">
-        <v>1374</v>
+        <v>637</v>
       </c>
     </row>
     <row r="874" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31198,28 +31204,28 @@
         <v>1373</v>
       </c>
       <c r="B874" s="22" t="s">
-        <v>1286</v>
+        <v>374</v>
       </c>
       <c r="C874" s="22" t="n">
-        <v>4809</v>
+        <v>4808</v>
       </c>
       <c r="D874" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E874" s="22" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F874" s="3" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="G874" s="22" t="s">
-        <v>1287</v>
+        <v>231</v>
       </c>
       <c r="H874" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I874" s="22" t="s">
-        <v>91</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="875" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31227,28 +31233,28 @@
         <v>1373</v>
       </c>
       <c r="B875" s="22" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C875" s="22" t="n">
-        <v>4810</v>
+        <v>4809</v>
       </c>
       <c r="D875" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E875" s="22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F875" s="3" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="G875" s="22" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="H875" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I875" s="22" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
     </row>
     <row r="876" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31256,86 +31262,86 @@
         <v>1373</v>
       </c>
       <c r="B876" s="22" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C876" s="22" t="n">
+        <v>4810</v>
+      </c>
+      <c r="D876" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E876" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F876" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G876" s="22" t="s">
+        <v>1289</v>
+      </c>
+      <c r="H876" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I876" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="877" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A877" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B877" s="22" t="s">
         <v>1375</v>
       </c>
-      <c r="C876" s="22" t="n">
+      <c r="C877" s="22" t="n">
         <v>4811</v>
       </c>
-      <c r="D876" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E876" s="22" t="n">
+      <c r="D877" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E877" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="F876" s="3" t="s">
+      <c r="F877" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G876" s="22" t="s">
+      <c r="G877" s="22" t="s">
         <v>1292</v>
       </c>
-      <c r="H876" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I876" s="22" t="s">
+      <c r="H877" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I877" s="22" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="877" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A877" s="22" t="s">
-        <v>1376</v>
-      </c>
-      <c r="B877" s="22" t="s">
-        <v>1377</v>
-      </c>
-      <c r="C877" s="22" t="n">
-        <v>4900</v>
-      </c>
-      <c r="D877" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E877" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F877" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G877" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="H877" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I877" s="22" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="878" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A878" s="22" t="s">
         <v>1376</v>
       </c>
-      <c r="B878" s="1" t="s">
-        <v>158</v>
+      <c r="B878" s="22" t="s">
+        <v>1377</v>
       </c>
       <c r="C878" s="22" t="n">
-        <v>4901</v>
+        <v>4900</v>
       </c>
       <c r="D878" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E878" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F878" s="3" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="G878" s="22" t="s">
-        <v>1300</v>
+        <v>231</v>
       </c>
       <c r="H878" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I878" s="22" t="s">
-        <v>160</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="879" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31343,10 +31349,10 @@
         <v>1376</v>
       </c>
       <c r="B879" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C879" s="22" t="n">
-        <v>4902</v>
+        <v>4901</v>
       </c>
       <c r="D879" s="29" t="s">
         <v>20</v>
@@ -31358,7 +31364,7 @@
         <v>89</v>
       </c>
       <c r="G879" s="22" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H879" s="22" t="s">
         <v>17</v>
@@ -31372,10 +31378,10 @@
         <v>1376</v>
       </c>
       <c r="B880" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C880" s="22" t="n">
-        <v>4903</v>
+        <v>4902</v>
       </c>
       <c r="D880" s="29" t="s">
         <v>20</v>
@@ -31387,7 +31393,7 @@
         <v>89</v>
       </c>
       <c r="G880" s="22" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H880" s="22" t="s">
         <v>17</v>
@@ -31401,13 +31407,13 @@
         <v>1376</v>
       </c>
       <c r="B881" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C881" s="22" t="n">
-        <v>4904</v>
+        <v>4903</v>
       </c>
       <c r="D881" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E881" s="22" t="n">
         <v>10</v>
@@ -31416,13 +31422,13 @@
         <v>89</v>
       </c>
       <c r="G881" s="22" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H881" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I881" s="22" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="882" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31430,10 +31436,10 @@
         <v>1376</v>
       </c>
       <c r="B882" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C882" s="22" t="n">
-        <v>4905</v>
+        <v>4904</v>
       </c>
       <c r="D882" s="29" t="s">
         <v>59</v>
@@ -31445,7 +31451,7 @@
         <v>89</v>
       </c>
       <c r="G882" s="22" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H882" s="22" t="s">
         <v>17</v>
@@ -31459,10 +31465,10 @@
         <v>1376</v>
       </c>
       <c r="B883" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C883" s="22" t="n">
-        <v>4906</v>
+        <v>4905</v>
       </c>
       <c r="D883" s="29" t="s">
         <v>59</v>
@@ -31474,7 +31480,7 @@
         <v>89</v>
       </c>
       <c r="G883" s="22" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H883" s="22" t="s">
         <v>17</v>
@@ -31488,28 +31494,28 @@
         <v>1376</v>
       </c>
       <c r="B884" s="1" t="s">
-        <v>1306</v>
+        <v>171</v>
       </c>
       <c r="C884" s="22" t="n">
-        <v>4907</v>
+        <v>4906</v>
       </c>
       <c r="D884" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="E884" s="22" t="s">
-        <v>1307</v>
+      <c r="E884" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="F884" s="3" t="s">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="G884" s="22" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="H884" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I884" s="22" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
     </row>
     <row r="885" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31517,10 +31523,10 @@
         <v>1376</v>
       </c>
       <c r="B885" s="1" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="C885" s="22" t="n">
-        <v>4908</v>
+        <v>4907</v>
       </c>
       <c r="D885" s="29" t="s">
         <v>59</v>
@@ -31532,7 +31538,7 @@
         <v>182</v>
       </c>
       <c r="G885" s="22" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="H885" s="22" t="s">
         <v>17</v>
@@ -31546,10 +31552,10 @@
         <v>1376</v>
       </c>
       <c r="B886" s="1" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="C886" s="22" t="n">
-        <v>4909</v>
+        <v>4908</v>
       </c>
       <c r="D886" s="29" t="s">
         <v>59</v>
@@ -31561,7 +31567,7 @@
         <v>182</v>
       </c>
       <c r="G886" s="22" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="H886" s="22" t="s">
         <v>17</v>
@@ -31575,28 +31581,28 @@
         <v>1376</v>
       </c>
       <c r="B887" s="1" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C887" s="22" t="n">
-        <v>4910</v>
+        <v>4909</v>
       </c>
       <c r="D887" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E887" s="22" t="n">
-        <v>100</v>
+        <v>59</v>
+      </c>
+      <c r="E887" s="22" t="s">
+        <v>1307</v>
       </c>
       <c r="F887" s="3" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="G887" s="22" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="H887" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I887" s="22" t="s">
-        <v>176</v>
+        <v>31</v>
       </c>
     </row>
     <row r="888" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31604,28 +31610,28 @@
         <v>1376</v>
       </c>
       <c r="B888" s="1" t="s">
-        <v>190</v>
+        <v>1313</v>
       </c>
       <c r="C888" s="22" t="n">
-        <v>4911</v>
+        <v>4910</v>
       </c>
       <c r="D888" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E888" s="22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F888" s="3" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="G888" s="22" t="s">
-        <v>191</v>
+        <v>1314</v>
       </c>
       <c r="H888" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I888" s="22" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="889" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31633,10 +31639,10 @@
         <v>1376</v>
       </c>
       <c r="B889" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C889" s="22" t="n">
-        <v>4912</v>
+        <v>4911</v>
       </c>
       <c r="D889" s="29" t="s">
         <v>20</v>
@@ -31648,7 +31654,7 @@
         <v>89</v>
       </c>
       <c r="G889" s="22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H889" s="22" t="s">
         <v>17</v>
@@ -31662,10 +31668,10 @@
         <v>1376</v>
       </c>
       <c r="B890" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C890" s="22" t="n">
-        <v>4913</v>
+        <v>4912</v>
       </c>
       <c r="D890" s="29" t="s">
         <v>20</v>
@@ -31677,7 +31683,7 @@
         <v>89</v>
       </c>
       <c r="G890" s="22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H890" s="22" t="s">
         <v>17</v>
@@ -31691,28 +31697,28 @@
         <v>1376</v>
       </c>
       <c r="B891" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C891" s="22" t="n">
-        <v>4914</v>
+        <v>4913</v>
       </c>
       <c r="D891" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E891" s="22" t="n">
         <v>10</v>
       </c>
       <c r="F891" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G891" s="22" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H891" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I891" s="22" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="892" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31720,10 +31726,10 @@
         <v>1376</v>
       </c>
       <c r="B892" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C892" s="22" t="n">
-        <v>4915</v>
+        <v>4914</v>
       </c>
       <c r="D892" s="29" t="s">
         <v>59</v>
@@ -31735,7 +31741,7 @@
         <v>94</v>
       </c>
       <c r="G892" s="22" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H892" s="22" t="s">
         <v>17</v>
@@ -31749,10 +31755,10 @@
         <v>1376</v>
       </c>
       <c r="B893" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C893" s="22" t="n">
-        <v>4916</v>
+        <v>4915</v>
       </c>
       <c r="D893" s="29" t="s">
         <v>59</v>
@@ -31764,7 +31770,7 @@
         <v>94</v>
       </c>
       <c r="G893" s="22" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H893" s="22" t="s">
         <v>17</v>
@@ -31778,28 +31784,28 @@
         <v>1376</v>
       </c>
       <c r="B894" s="1" t="s">
-        <v>1315</v>
+        <v>201</v>
       </c>
       <c r="C894" s="22" t="n">
-        <v>4917</v>
+        <v>4916</v>
       </c>
       <c r="D894" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="E894" s="22" t="s">
-        <v>1307</v>
+      <c r="E894" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="F894" s="3" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="G894" s="22" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="H894" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I894" s="22" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
     </row>
     <row r="895" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31807,10 +31813,10 @@
         <v>1376</v>
       </c>
       <c r="B895" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C895" s="22" t="n">
-        <v>4918</v>
+        <v>4917</v>
       </c>
       <c r="D895" s="29" t="s">
         <v>59</v>
@@ -31822,7 +31828,7 @@
         <v>182</v>
       </c>
       <c r="G895" s="22" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H895" s="22" t="s">
         <v>17</v>
@@ -31836,10 +31842,10 @@
         <v>1376</v>
       </c>
       <c r="B896" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C896" s="22" t="n">
-        <v>4919</v>
+        <v>4918</v>
       </c>
       <c r="D896" s="29" t="s">
         <v>59</v>
@@ -31851,7 +31857,7 @@
         <v>182</v>
       </c>
       <c r="G896" s="22" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H896" s="22" t="s">
         <v>17</v>
@@ -31865,57 +31871,57 @@
         <v>1376</v>
       </c>
       <c r="B897" s="1" t="s">
-        <v>203</v>
+        <v>1317</v>
       </c>
       <c r="C897" s="22" t="n">
-        <v>4920</v>
+        <v>4919</v>
       </c>
       <c r="D897" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E897" s="22" t="n">
-        <v>100</v>
+        <v>59</v>
+      </c>
+      <c r="E897" s="22" t="s">
+        <v>1307</v>
       </c>
       <c r="F897" s="3" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="G897" s="22" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="H897" s="22" t="s">
         <v>17</v>
       </c>
       <c r="I897" s="22" t="s">
-        <v>176</v>
+        <v>31</v>
       </c>
     </row>
     <row r="898" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A898" s="22" t="s">
         <v>1376</v>
       </c>
-      <c r="B898" s="22" t="s">
-        <v>1346</v>
+      <c r="B898" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="C898" s="22" t="n">
-        <v>4921</v>
+        <v>4920</v>
       </c>
       <c r="D898" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E898" s="22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F898" s="3" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="G898" s="22" t="s">
-        <v>1347</v>
+        <v>204</v>
       </c>
       <c r="H898" s="22" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I898" s="22" t="s">
-        <v>1017</v>
+        <v>176</v>
       </c>
     </row>
     <row r="899" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31923,28 +31929,28 @@
         <v>1376</v>
       </c>
       <c r="B899" s="22" t="s">
-        <v>1378</v>
+        <v>1346</v>
       </c>
       <c r="C899" s="22" t="n">
-        <v>4922</v>
+        <v>4921</v>
       </c>
       <c r="D899" s="29" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="E899" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F899" s="3" t="s">
-        <v>140</v>
+        <v>264</v>
       </c>
       <c r="G899" s="22" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="H899" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="I899" s="1" t="s">
-        <v>31</v>
+      <c r="I899" s="22" t="s">
+        <v>1017</v>
       </c>
     </row>
     <row r="900" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31952,57 +31958,57 @@
         <v>1376</v>
       </c>
       <c r="B900" s="22" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C900" s="22" t="n">
-        <v>4924</v>
+        <v>4922</v>
       </c>
       <c r="D900" s="29" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="E900" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F900" s="3" t="s">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="G900" s="22" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="H900" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="I900" s="22" t="s">
-        <v>1353</v>
+      <c r="I900" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="901" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A901" s="22" t="s">
         <v>1376</v>
       </c>
-      <c r="B901" s="1" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C901" s="1" t="n">
-        <v>4925</v>
+      <c r="B901" s="22" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C901" s="22" t="n">
+        <v>4924</v>
       </c>
       <c r="D901" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E901" s="1" t="n">
+      <c r="E901" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F901" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G901" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="H901" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I901" s="1" t="s">
-        <v>103</v>
+      <c r="G901" s="22" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H901" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="I901" s="22" t="s">
+        <v>1353</v>
       </c>
     </row>
     <row r="902" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32010,10 +32016,28 @@
         <v>1376</v>
       </c>
       <c r="B902" s="1" t="s">
-        <v>117</v>
+        <v>1380</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>4926</v>
+        <v>4925</v>
+      </c>
+      <c r="D902" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E902" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F902" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G902" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="H902" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I902" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="903" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32024,7 +32048,7 @@
         <v>117</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>4927</v>
+        <v>4926</v>
       </c>
     </row>
     <row r="904" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32035,7 +32059,7 @@
         <v>117</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>4928</v>
+        <v>4927</v>
       </c>
     </row>
     <row r="905" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32046,7 +32070,7 @@
         <v>117</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>4929</v>
+        <v>4928</v>
       </c>
     </row>
     <row r="906" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32054,28 +32078,10 @@
         <v>1376</v>
       </c>
       <c r="B906" s="1" t="s">
-        <v>1382</v>
+        <v>117</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>4930</v>
-      </c>
-      <c r="D906" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E906" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F906" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G906" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="H906" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I906" s="22" t="s">
-        <v>241</v>
+        <v>4929</v>
       </c>
     </row>
     <row r="907" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32083,10 +32089,10 @@
         <v>1376</v>
       </c>
       <c r="B907" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>4931</v>
+        <v>4930</v>
       </c>
       <c r="D907" s="2" t="s">
         <v>20</v>
@@ -32098,7 +32104,7 @@
         <v>264</v>
       </c>
       <c r="G907" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H907" s="1" t="s">
         <v>17</v>
@@ -32112,12 +32118,29 @@
         <v>1376</v>
       </c>
       <c r="B908" s="1" t="s">
-        <v>117</v>
+        <v>1383</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>4932</v>
-      </c>
-      <c r="I908" s="22"/>
+        <v>4931</v>
+      </c>
+      <c r="D908" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E908" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F908" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G908" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="H908" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I908" s="22" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="909" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A909" s="22" t="s">
@@ -32127,7 +32150,7 @@
         <v>117</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>4933</v>
+        <v>4932</v>
       </c>
       <c r="I909" s="22"/>
     </row>
@@ -32139,7 +32162,7 @@
         <v>117</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>4934</v>
+        <v>4933</v>
       </c>
       <c r="I910" s="22"/>
     </row>
@@ -32151,7 +32174,7 @@
         <v>117</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>4935</v>
+        <v>4934</v>
       </c>
       <c r="I911" s="22"/>
     </row>
@@ -32163,7 +32186,7 @@
         <v>117</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>4936</v>
+        <v>4935</v>
       </c>
       <c r="I912" s="22"/>
     </row>
@@ -32175,7 +32198,7 @@
         <v>117</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>4937</v>
+        <v>4936</v>
       </c>
       <c r="I913" s="22"/>
     </row>
@@ -32187,7 +32210,7 @@
         <v>117</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>4938</v>
+        <v>4937</v>
       </c>
       <c r="I914" s="22"/>
     </row>
@@ -32199,7 +32222,7 @@
         <v>117</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>4939</v>
+        <v>4938</v>
       </c>
       <c r="I915" s="22"/>
     </row>
@@ -32208,39 +32231,22 @@
         <v>1376</v>
       </c>
       <c r="B916" s="1" t="s">
-        <v>1322</v>
+        <v>117</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>4940</v>
-      </c>
-      <c r="D916" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E916" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F916" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G916" s="1" t="s">
-        <v>1323</v>
-      </c>
-      <c r="H916" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I916" s="22" t="s">
-        <v>207</v>
-      </c>
+        <v>4939</v>
+      </c>
+      <c r="I916" s="22"/>
     </row>
     <row r="917" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A917" s="22" t="s">
         <v>1376</v>
       </c>
       <c r="B917" s="1" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>4941</v>
+        <v>4940</v>
       </c>
       <c r="D917" s="2" t="s">
         <v>20</v>
@@ -32252,7 +32258,7 @@
         <v>1384</v>
       </c>
       <c r="G917" s="1" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="H917" s="1" t="s">
         <v>23</v>
@@ -32266,10 +32272,10 @@
         <v>1376</v>
       </c>
       <c r="B918" s="1" t="s">
-        <v>1385</v>
+        <v>1324</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>4942</v>
+        <v>4941</v>
       </c>
       <c r="D918" s="2" t="s">
         <v>20</v>
@@ -32281,7 +32287,7 @@
         <v>1384</v>
       </c>
       <c r="G918" s="1" t="s">
-        <v>1386</v>
+        <v>1325</v>
       </c>
       <c r="H918" s="1" t="s">
         <v>23</v>
@@ -32292,28 +32298,31 @@
     </row>
     <row r="919" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A919" s="22" t="s">
-        <v>1387</v>
+        <v>1376</v>
       </c>
       <c r="B919" s="1" t="s">
-        <v>1388</v>
-      </c>
-      <c r="C919" s="30" t="n">
-        <v>5200</v>
-      </c>
-      <c r="D919" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E919" s="30" t="n">
-        <v>1</v>
+        <v>1385</v>
+      </c>
+      <c r="C919" s="1" t="n">
+        <v>4942</v>
+      </c>
+      <c r="D919" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E919" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="F919" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G919" s="30" t="s">
-        <v>1023</v>
+        <v>1384</v>
+      </c>
+      <c r="G919" s="1" t="s">
+        <v>1386</v>
       </c>
       <c r="H919" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="I919" s="22" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="920" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32321,10 +32330,10 @@
         <v>1387</v>
       </c>
       <c r="B920" s="1" t="s">
-        <v>1099</v>
+        <v>1388</v>
       </c>
       <c r="C920" s="30" t="n">
-        <v>5201</v>
+        <v>5200</v>
       </c>
       <c r="D920" s="29" t="s">
         <v>20</v>
@@ -32336,7 +32345,7 @@
         <v>264</v>
       </c>
       <c r="G920" s="30" t="s">
-        <v>1100</v>
+        <v>1023</v>
       </c>
       <c r="H920" s="1" t="s">
         <v>17</v>
@@ -32347,10 +32356,10 @@
         <v>1387</v>
       </c>
       <c r="B921" s="1" t="s">
-        <v>788</v>
+        <v>1099</v>
       </c>
       <c r="C921" s="30" t="n">
-        <v>5202</v>
+        <v>5201</v>
       </c>
       <c r="D921" s="29" t="s">
         <v>20</v>
@@ -32362,7 +32371,7 @@
         <v>264</v>
       </c>
       <c r="G921" s="30" t="s">
-        <v>664</v>
+        <v>1100</v>
       </c>
       <c r="H921" s="1" t="s">
         <v>17</v>
@@ -32373,10 +32382,10 @@
         <v>1387</v>
       </c>
       <c r="B922" s="1" t="s">
-        <v>1365</v>
+        <v>788</v>
       </c>
       <c r="C922" s="30" t="n">
-        <v>5203</v>
+        <v>5202</v>
       </c>
       <c r="D922" s="29" t="s">
         <v>20</v>
@@ -32388,7 +32397,7 @@
         <v>264</v>
       </c>
       <c r="G922" s="30" t="s">
-        <v>1104</v>
+        <v>664</v>
       </c>
       <c r="H922" s="1" t="s">
         <v>17</v>
@@ -32399,10 +32408,10 @@
         <v>1387</v>
       </c>
       <c r="B923" s="1" t="s">
-        <v>1119</v>
+        <v>1365</v>
       </c>
       <c r="C923" s="30" t="n">
-        <v>5204</v>
+        <v>5203</v>
       </c>
       <c r="D923" s="29" t="s">
         <v>20</v>
@@ -32414,13 +32423,10 @@
         <v>264</v>
       </c>
       <c r="G923" s="30" t="s">
-        <v>1120</v>
+        <v>1104</v>
       </c>
       <c r="H923" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I923" s="1" t="s">
-        <v>1204</v>
+        <v>17</v>
       </c>
     </row>
     <row r="924" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32428,28 +32434,28 @@
         <v>1387</v>
       </c>
       <c r="B924" s="1" t="s">
-        <v>1389</v>
+        <v>1119</v>
       </c>
       <c r="C924" s="30" t="n">
-        <v>5205</v>
+        <v>5204</v>
       </c>
       <c r="D924" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E924" s="30" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F924" s="3" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="G924" s="30" t="s">
-        <v>218</v>
+        <v>1120</v>
       </c>
       <c r="H924" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I924" s="1" t="s">
-        <v>1390</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="925" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32457,68 +32463,68 @@
         <v>1387</v>
       </c>
       <c r="B925" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="C925" s="30" t="n">
-        <v>5206</v>
+        <v>5205</v>
       </c>
       <c r="D925" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E925" s="30" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F925" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="G925" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H925" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I925" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="926" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A926" s="22" t="s">
         <v>1387</v>
       </c>
-      <c r="B926" s="30" t="s">
-        <v>1105</v>
+      <c r="B926" s="1" t="s">
+        <v>1391</v>
       </c>
       <c r="C926" s="30" t="n">
-        <v>5207</v>
+        <v>5206</v>
       </c>
       <c r="D926" s="29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E926" s="30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F926" s="3" t="s">
-        <v>264</v>
+        <v>94</v>
       </c>
       <c r="G926" s="30" t="s">
-        <v>1106</v>
+        <v>220</v>
       </c>
       <c r="H926" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I926" s="1" t="s">
-        <v>103</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="927" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A927" s="22" t="s">
         <v>1387</v>
       </c>
-      <c r="B927" s="1" t="s">
-        <v>1393</v>
+      <c r="B927" s="30" t="s">
+        <v>1105</v>
       </c>
       <c r="C927" s="30" t="n">
-        <v>5208</v>
+        <v>5207</v>
       </c>
       <c r="D927" s="29" t="s">
         <v>20</v>
@@ -32530,13 +32536,13 @@
         <v>264</v>
       </c>
       <c r="G927" s="30" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H927" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I927" s="1" t="s">
-        <v>864</v>
+        <v>103</v>
       </c>
     </row>
     <row r="928" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32544,57 +32550,57 @@
         <v>1387</v>
       </c>
       <c r="B928" s="1" t="s">
-        <v>1126</v>
+        <v>1393</v>
       </c>
       <c r="C928" s="30" t="n">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="D928" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E928" s="30" t="s">
-        <v>1394</v>
+      <c r="E928" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="F928" s="3" t="s">
-        <v>323</v>
+        <v>264</v>
       </c>
       <c r="G928" s="30" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="H928" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I928" s="1" t="s">
-        <v>1395</v>
+        <v>864</v>
       </c>
     </row>
     <row r="929" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A929" s="22" t="s">
         <v>1387</v>
       </c>
-      <c r="B929" s="30" t="s">
-        <v>1111</v>
+      <c r="B929" s="1" t="s">
+        <v>1126</v>
       </c>
       <c r="C929" s="30" t="n">
-        <v>5210</v>
+        <v>5209</v>
       </c>
       <c r="D929" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="E929" s="30" t="n">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="E929" s="30" t="s">
+        <v>1394</v>
       </c>
       <c r="F929" s="3" t="s">
-        <v>94</v>
+        <v>323</v>
       </c>
       <c r="G929" s="30" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="H929" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I929" s="1" t="s">
-        <v>308</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="930" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32602,10 +32608,10 @@
         <v>1387</v>
       </c>
       <c r="B930" s="30" t="s">
-        <v>1396</v>
+        <v>1111</v>
       </c>
       <c r="C930" s="30" t="n">
-        <v>5211</v>
+        <v>5210</v>
       </c>
       <c r="D930" s="29" t="s">
         <v>59</v>
@@ -32617,7 +32623,7 @@
         <v>94</v>
       </c>
       <c r="G930" s="30" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="H930" s="1" t="s">
         <v>17</v>
@@ -32631,10 +32637,10 @@
         <v>1387</v>
       </c>
       <c r="B931" s="30" t="s">
-        <v>1115</v>
+        <v>1396</v>
       </c>
       <c r="C931" s="30" t="n">
-        <v>5212</v>
+        <v>5211</v>
       </c>
       <c r="D931" s="29" t="s">
         <v>59</v>
@@ -32646,7 +32652,7 @@
         <v>94</v>
       </c>
       <c r="G931" s="30" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H931" s="1" t="s">
         <v>17</v>
@@ -32660,109 +32666,109 @@
         <v>1387</v>
       </c>
       <c r="B932" s="30" t="s">
-        <v>494</v>
+        <v>1115</v>
       </c>
       <c r="C932" s="30" t="n">
-        <v>5213</v>
+        <v>5212</v>
       </c>
       <c r="D932" s="29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E932" s="30" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F932" s="3" t="s">
-        <v>217</v>
+        <v>94</v>
       </c>
       <c r="G932" s="30" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="H932" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I932" s="1" t="s">
-        <v>1390</v>
+        <v>308</v>
       </c>
     </row>
     <row r="933" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A933" s="22" t="s">
         <v>1387</v>
       </c>
-      <c r="B933" s="1" t="s">
-        <v>1123</v>
+      <c r="B933" s="30" t="s">
+        <v>494</v>
       </c>
       <c r="C933" s="30" t="n">
-        <v>5214</v>
+        <v>5213</v>
       </c>
       <c r="D933" s="29" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E933" s="30" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F933" s="3" t="s">
-        <v>60</v>
+        <v>217</v>
       </c>
       <c r="G933" s="30" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="H933" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I933" s="1" t="s">
-        <v>1125</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="934" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A934" s="22" t="s">
         <v>1387</v>
       </c>
-      <c r="B934" s="30" t="s">
-        <v>1393</v>
+      <c r="B934" s="1" t="s">
+        <v>1123</v>
       </c>
       <c r="C934" s="30" t="n">
-        <v>5215</v>
+        <v>5214</v>
       </c>
       <c r="D934" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E934" s="30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F934" s="3" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="G934" s="30" t="s">
-        <v>1397</v>
+        <v>1124</v>
       </c>
       <c r="H934" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I934" s="1" t="s">
-        <v>308</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="935" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A935" s="22" t="s">
         <v>1387</v>
       </c>
-      <c r="B935" s="1" t="s">
-        <v>1126</v>
+      <c r="B935" s="30" t="s">
+        <v>1393</v>
       </c>
       <c r="C935" s="30" t="n">
-        <v>5216</v>
+        <v>5215</v>
       </c>
       <c r="D935" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E935" s="30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F935" s="3" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="G935" s="30" t="s">
-        <v>1127</v>
+        <v>1397</v>
       </c>
       <c r="H935" s="1" t="s">
         <v>17</v>
@@ -32775,49 +32781,52 @@
       <c r="A936" s="22" t="s">
         <v>1387</v>
       </c>
-      <c r="B936" s="30" t="s">
-        <v>117</v>
+      <c r="B936" s="1" t="s">
+        <v>1126</v>
       </c>
       <c r="C936" s="30" t="n">
-        <v>5217</v>
+        <v>5216</v>
       </c>
       <c r="D936" s="29" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E936" s="30" t="n">
         <v>1</v>
       </c>
+      <c r="F936" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="G936" s="30" t="s">
-        <v>117</v>
+        <v>1127</v>
       </c>
       <c r="H936" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="937" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I936" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="937" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A937" s="22" t="s">
         <v>1387</v>
       </c>
-      <c r="B937" s="1" t="s">
-        <v>1128</v>
+      <c r="B937" s="30" t="s">
+        <v>117</v>
       </c>
       <c r="C937" s="30" t="n">
-        <v>5218</v>
+        <v>5217</v>
       </c>
       <c r="D937" s="29" t="s">
-        <v>1129</v>
+        <v>20</v>
       </c>
       <c r="E937" s="30" t="n">
         <v>1</v>
       </c>
       <c r="G937" s="30" t="s">
-        <v>1131</v>
+        <v>117</v>
       </c>
       <c r="H937" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I937" s="1" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="938" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32825,10 +32834,10 @@
         <v>1387</v>
       </c>
       <c r="B938" s="1" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="C938" s="30" t="n">
-        <v>5234</v>
+        <v>5218</v>
       </c>
       <c r="D938" s="29" t="s">
         <v>1129</v>
@@ -32837,10 +32846,13 @@
         <v>1</v>
       </c>
       <c r="G938" s="30" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="H938" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="I938" s="1" t="s">
+        <v>1132</v>
       </c>
     </row>
     <row r="939" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32848,10 +32860,10 @@
         <v>1387</v>
       </c>
       <c r="B939" s="1" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C939" s="30" t="n">
-        <v>5250</v>
+        <v>5234</v>
       </c>
       <c r="D939" s="29" t="s">
         <v>1129</v>
@@ -32860,7 +32872,7 @@
         <v>1</v>
       </c>
       <c r="G939" s="30" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H939" s="1" t="s">
         <v>17</v>
@@ -32871,10 +32883,10 @@
         <v>1387</v>
       </c>
       <c r="B940" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="C940" s="30" t="n">
-        <v>5266</v>
+        <v>5250</v>
       </c>
       <c r="D940" s="29" t="s">
         <v>1129</v>
@@ -32883,7 +32895,7 @@
         <v>1</v>
       </c>
       <c r="G940" s="30" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="H940" s="1" t="s">
         <v>17</v>
@@ -32894,10 +32906,10 @@
         <v>1387</v>
       </c>
       <c r="B941" s="1" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C941" s="30" t="n">
-        <v>5282</v>
+        <v>5266</v>
       </c>
       <c r="D941" s="29" t="s">
         <v>1129</v>
@@ -32906,7 +32918,7 @@
         <v>1</v>
       </c>
       <c r="G941" s="30" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H941" s="1" t="s">
         <v>17</v>
@@ -32917,10 +32929,10 @@
         <v>1387</v>
       </c>
       <c r="B942" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C942" s="30" t="n">
-        <v>5298</v>
+        <v>5282</v>
       </c>
       <c r="D942" s="29" t="s">
         <v>1129</v>
@@ -32929,7 +32941,7 @@
         <v>1</v>
       </c>
       <c r="G942" s="30" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="H942" s="1" t="s">
         <v>17</v>
@@ -32940,10 +32952,10 @@
         <v>1387</v>
       </c>
       <c r="B943" s="1" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C943" s="30" t="n">
-        <v>5314</v>
+        <v>5298</v>
       </c>
       <c r="D943" s="29" t="s">
         <v>1129</v>
@@ -32952,7 +32964,7 @@
         <v>1</v>
       </c>
       <c r="G943" s="30" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="H943" s="1" t="s">
         <v>17</v>
@@ -32963,10 +32975,10 @@
         <v>1387</v>
       </c>
       <c r="B944" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C944" s="30" t="n">
-        <v>5330</v>
+        <v>5314</v>
       </c>
       <c r="D944" s="29" t="s">
         <v>1129</v>
@@ -32975,50 +32987,44 @@
         <v>1</v>
       </c>
       <c r="G944" s="30" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H944" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="945" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A945" s="22" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B945" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C945" s="30" t="n">
+        <v>5330</v>
+      </c>
+      <c r="D945" s="29" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E945" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G945" s="30" t="s">
         <v>1146</v>
       </c>
-      <c r="H944" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="945" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A945" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B945" s="30" t="s">
-        <v>1398</v>
-      </c>
-      <c r="C945" s="1" t="n">
-        <v>5400</v>
-      </c>
-      <c r="D945" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E945" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F945" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G945" s="1" t="s">
-        <v>1399</v>
-      </c>
       <c r="H945" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I945" s="22" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="946" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A946" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B946" s="1" t="s">
-        <v>1401</v>
+      <c r="B946" s="30" t="s">
+        <v>1398</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>5401</v>
+        <v>5400</v>
       </c>
       <c r="D946" s="29" t="s">
         <v>20</v>
@@ -33030,13 +33036,13 @@
         <v>264</v>
       </c>
       <c r="G946" s="1" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="H946" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I946" s="22" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="947" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33044,10 +33050,10 @@
         <v>12</v>
       </c>
       <c r="B947" s="1" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="D947" s="29" t="s">
         <v>20</v>
@@ -33059,68 +33065,68 @@
         <v>264</v>
       </c>
       <c r="G947" s="1" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="H947" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I947" s="1" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="948" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I947" s="22" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="948" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A948" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B948" s="25" t="s">
-        <v>1407</v>
+      <c r="B948" s="1" t="s">
+        <v>1404</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="D948" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F948" s="3" t="s">
-        <v>1408</v>
+        <v>264</v>
       </c>
       <c r="G948" s="1" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="H948" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="949" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I948" s="1" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="949" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A949" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B949" s="1" t="s">
-        <v>788</v>
+      <c r="B949" s="25" t="s">
+        <v>1407</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>5404</v>
+        <v>5403</v>
       </c>
       <c r="D949" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F949" s="3" t="s">
-        <v>264</v>
+        <v>1408</v>
       </c>
       <c r="G949" s="1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H949" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I949" s="1" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="950" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33128,10 +33134,10 @@
         <v>12</v>
       </c>
       <c r="B950" s="1" t="s">
-        <v>1412</v>
+        <v>788</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>5405</v>
+        <v>5404</v>
       </c>
       <c r="D950" s="29" t="s">
         <v>20</v>
@@ -33143,13 +33149,13 @@
         <v>264</v>
       </c>
       <c r="G950" s="1" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="H950" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I950" s="1" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="951" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33157,10 +33163,10 @@
         <v>12</v>
       </c>
       <c r="B951" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>5406</v>
+        <v>5405</v>
       </c>
       <c r="D951" s="29" t="s">
         <v>20</v>
@@ -33172,13 +33178,13 @@
         <v>264</v>
       </c>
       <c r="G951" s="1" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="H951" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I951" s="1" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="952" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33186,10 +33192,10 @@
         <v>12</v>
       </c>
       <c r="B952" s="1" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>5407</v>
+        <v>5406</v>
       </c>
       <c r="D952" s="29" t="s">
         <v>20</v>
@@ -33201,42 +33207,42 @@
         <v>264</v>
       </c>
       <c r="G952" s="1" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="H952" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I952" s="1" t="s">
-        <v>103</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="953" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A953" s="1" t="s">
-        <v>928</v>
+        <v>12</v>
       </c>
       <c r="B953" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>5420</v>
+        <v>5407</v>
       </c>
       <c r="D953" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F953" s="3" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="G953" s="1" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="H953" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I953" s="1" t="s">
-        <v>348</v>
+        <v>103</v>
       </c>
     </row>
     <row r="954" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33244,28 +33250,28 @@
         <v>928</v>
       </c>
       <c r="B954" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>5421</v>
+        <v>5420</v>
       </c>
       <c r="D954" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F954" s="3" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="G954" s="1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="H954" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I954" s="1" t="s">
-        <v>1424</v>
+        <v>348</v>
       </c>
     </row>
     <row r="955" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33273,10 +33279,10 @@
         <v>928</v>
       </c>
       <c r="B955" s="1" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>5422</v>
+        <v>5421</v>
       </c>
       <c r="D955" s="29" t="s">
         <v>20</v>
@@ -33288,13 +33294,13 @@
         <v>264</v>
       </c>
       <c r="G955" s="1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="H955" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I955" s="1" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="956" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33302,10 +33308,10 @@
         <v>928</v>
       </c>
       <c r="B956" s="1" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>5423</v>
+        <v>5422</v>
       </c>
       <c r="D956" s="29" t="s">
         <v>20</v>
@@ -33317,13 +33323,13 @@
         <v>264</v>
       </c>
       <c r="G956" s="1" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="H956" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I956" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="957" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33331,10 +33337,10 @@
         <v>928</v>
       </c>
       <c r="B957" s="1" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>5424</v>
+        <v>5423</v>
       </c>
       <c r="D957" s="29" t="s">
         <v>20</v>
@@ -33346,13 +33352,13 @@
         <v>264</v>
       </c>
       <c r="G957" s="1" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="H957" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I957" s="22" t="s">
-        <v>1403</v>
+      <c r="I957" s="1" t="s">
+        <v>1430</v>
       </c>
     </row>
     <row r="958" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33360,10 +33366,10 @@
         <v>928</v>
       </c>
       <c r="B958" s="1" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>5425</v>
+        <v>5424</v>
       </c>
       <c r="D958" s="29" t="s">
         <v>20</v>
@@ -33375,13 +33381,13 @@
         <v>264</v>
       </c>
       <c r="G958" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="H958" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I958" s="1" t="s">
-        <v>1395</v>
+      <c r="I958" s="22" t="s">
+        <v>1403</v>
       </c>
     </row>
     <row r="959" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33389,10 +33395,10 @@
         <v>928</v>
       </c>
       <c r="B959" s="1" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>5426</v>
+        <v>5425</v>
       </c>
       <c r="D959" s="29" t="s">
         <v>20</v>
@@ -33404,13 +33410,13 @@
         <v>264</v>
       </c>
       <c r="G959" s="1" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="H959" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I959" s="1" t="s">
-        <v>1437</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="960" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33418,10 +33424,10 @@
         <v>928</v>
       </c>
       <c r="B960" s="1" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>5427</v>
+        <v>5426</v>
       </c>
       <c r="D960" s="29" t="s">
         <v>20</v>
@@ -33433,13 +33439,13 @@
         <v>264</v>
       </c>
       <c r="G960" s="1" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="H960" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I960" s="1" t="s">
-        <v>103</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="961" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33447,25 +33453,28 @@
         <v>928</v>
       </c>
       <c r="B961" s="1" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>5428</v>
-      </c>
-      <c r="D961" s="2" t="s">
-        <v>136</v>
+        <v>5427</v>
+      </c>
+      <c r="D961" s="29" t="s">
+        <v>20</v>
       </c>
       <c r="E961" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F961" s="3" t="s">
-        <v>140</v>
+        <v>264</v>
       </c>
       <c r="G961" s="1" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="H961" s="1" t="s">
         <v>23</v>
+      </c>
+      <c r="I961" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="962" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33473,41 +33482,38 @@
         <v>928</v>
       </c>
       <c r="B962" s="1" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>5430</v>
-      </c>
-      <c r="D962" s="29" t="s">
-        <v>20</v>
+        <v>5428</v>
+      </c>
+      <c r="D962" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="E962" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F962" s="3" t="s">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="G962" s="1" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H962" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I962" s="1" t="s">
-        <v>1417</v>
-      </c>
     </row>
     <row r="963" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A963" s="1" t="s">
-        <v>1444</v>
+        <v>928</v>
       </c>
       <c r="B963" s="1" t="s">
-        <v>1022</v>
+        <v>1442</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D963" s="2" t="s">
+        <v>5430</v>
+      </c>
+      <c r="D963" s="29" t="s">
         <v>20</v>
       </c>
       <c r="E963" s="1" t="n">
@@ -33517,10 +33523,13 @@
         <v>264</v>
       </c>
       <c r="G963" s="1" t="s">
-        <v>1023</v>
+        <v>1443</v>
       </c>
       <c r="H963" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="I963" s="1" t="s">
+        <v>1417</v>
       </c>
     </row>
     <row r="964" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33528,10 +33537,10 @@
         <v>1444</v>
       </c>
       <c r="B964" s="1" t="s">
-        <v>1445</v>
+        <v>1022</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>5501</v>
+        <v>5500</v>
       </c>
       <c r="D964" s="2" t="s">
         <v>20</v>
@@ -33543,13 +33552,10 @@
         <v>264</v>
       </c>
       <c r="G964" s="1" t="s">
-        <v>231</v>
+        <v>1023</v>
       </c>
       <c r="H964" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I964" s="1" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="965" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33557,28 +33563,28 @@
         <v>1444</v>
       </c>
       <c r="B965" s="1" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>5502</v>
+        <v>5501</v>
       </c>
       <c r="D965" s="2" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="E965" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F965" s="3" t="s">
-        <v>632</v>
+        <v>264</v>
       </c>
       <c r="G965" s="1" t="s">
-        <v>778</v>
+        <v>231</v>
       </c>
       <c r="H965" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I965" s="1" t="s">
-        <v>31</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="966" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33586,28 +33592,28 @@
         <v>1444</v>
       </c>
       <c r="B966" s="1" t="s">
-        <v>1295</v>
+        <v>1447</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>5504</v>
+        <v>5502</v>
       </c>
       <c r="D966" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F966" s="3" t="s">
-        <v>346</v>
+        <v>632</v>
       </c>
       <c r="G966" s="1" t="s">
-        <v>915</v>
+        <v>778</v>
       </c>
       <c r="H966" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I966" s="1" t="s">
-        <v>348</v>
+        <v>31</v>
       </c>
     </row>
     <row r="967" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33615,28 +33621,28 @@
         <v>1444</v>
       </c>
       <c r="B967" s="1" t="s">
-        <v>1448</v>
+        <v>1295</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>5506</v>
+        <v>5504</v>
       </c>
       <c r="D967" s="2" t="s">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F967" s="3" t="s">
-        <v>94</v>
+        <v>346</v>
       </c>
       <c r="G967" s="1" t="s">
-        <v>1156</v>
+        <v>915</v>
       </c>
       <c r="H967" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I967" s="1" t="s">
-        <v>308</v>
+        <v>348</v>
       </c>
     </row>
     <row r="968" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33644,10 +33650,10 @@
         <v>1444</v>
       </c>
       <c r="B968" s="1" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>5507</v>
+        <v>5506</v>
       </c>
       <c r="D968" s="2" t="s">
         <v>59</v>
@@ -33659,7 +33665,7 @@
         <v>94</v>
       </c>
       <c r="G968" s="1" t="s">
-        <v>1450</v>
+        <v>1156</v>
       </c>
       <c r="H968" s="1" t="s">
         <v>17</v>
@@ -33670,42 +33676,42 @@
     </row>
     <row r="969" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A969" s="1" t="s">
-        <v>1451</v>
-      </c>
-      <c r="B969" s="30" t="s">
-        <v>1452</v>
+        <v>1444</v>
+      </c>
+      <c r="B969" s="1" t="s">
+        <v>1449</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>5800</v>
+        <v>5507</v>
       </c>
       <c r="D969" s="2" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F969" s="3" t="s">
-        <v>264</v>
+        <v>94</v>
       </c>
       <c r="G969" s="1" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="H969" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I969" s="1" t="s">
-        <v>1454</v>
+        <v>308</v>
       </c>
     </row>
     <row r="970" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A970" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="B970" s="1" t="s">
-        <v>1455</v>
+      <c r="B970" s="30" t="s">
+        <v>1452</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>5801</v>
+        <v>5800</v>
       </c>
       <c r="D970" s="2" t="s">
         <v>20</v>
@@ -33717,13 +33723,13 @@
         <v>264</v>
       </c>
       <c r="G970" s="1" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="H970" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I970" s="1" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="971" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33731,10 +33737,10 @@
         <v>1451</v>
       </c>
       <c r="B971" s="1" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>5802</v>
+        <v>5801</v>
       </c>
       <c r="D971" s="2" t="s">
         <v>20</v>
@@ -33746,24 +33752,42 @@
         <v>264</v>
       </c>
       <c r="G971" s="1" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="H971" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I971" s="1" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="972" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A972" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="B972" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="C972" s="23" t="s">
-        <v>1461</v>
+      <c r="B972" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C972" s="1" t="n">
+        <v>5802</v>
+      </c>
+      <c r="D972" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E972" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F972" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G972" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H972" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I972" s="1" t="s">
+        <v>1460</v>
       </c>
     </row>
     <row r="973" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33771,39 +33795,21 @@
         <v>1451</v>
       </c>
       <c r="B973" s="30" t="s">
-        <v>1452</v>
-      </c>
-      <c r="C973" s="1" t="n">
-        <v>5810</v>
-      </c>
-      <c r="D973" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E973" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F973" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G973" s="1" t="s">
-        <v>1462</v>
-      </c>
-      <c r="H973" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I973" s="1" t="s">
-        <v>1454</v>
+        <v>117</v>
+      </c>
+      <c r="C973" s="23" t="s">
+        <v>1461</v>
       </c>
     </row>
     <row r="974" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A974" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="B974" s="1" t="s">
-        <v>1455</v>
+      <c r="B974" s="30" t="s">
+        <v>1452</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>5811</v>
+        <v>5810</v>
       </c>
       <c r="D974" s="2" t="s">
         <v>20</v>
@@ -33815,13 +33821,13 @@
         <v>264</v>
       </c>
       <c r="G974" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H974" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I974" s="1" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="975" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33829,10 +33835,10 @@
         <v>1451</v>
       </c>
       <c r="B975" s="1" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>5812</v>
+        <v>5811</v>
       </c>
       <c r="D975" s="2" t="s">
         <v>20</v>
@@ -33844,23 +33850,52 @@
         <v>264</v>
       </c>
       <c r="G975" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H975" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I975" s="1" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="976" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A976" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="B976" s="30" t="s">
+      <c r="B976" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C976" s="1" t="n">
+        <v>5812</v>
+      </c>
+      <c r="D976" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E976" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F976" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G976" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="H976" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I976" s="1" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="977" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A977" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B977" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="C976" s="23" t="s">
+      <c r="C977" s="23" t="s">
         <v>1465</v>
       </c>
     </row>
@@ -33871,7 +33906,7 @@
   <hyperlinks>
     <hyperlink ref="J492" r:id="rId1" location="UUID-af4a7478-4b75-68ac-cf3c-16c381335d1e" display="This value is maintained by BatteryLife. The Active SOC limit is the lower of this value, and register 2901. Also see https://www.victronenergy.com/media/pg/Energy_Storage_System/en/controlling-depth-of-discharge.html#UUID-af4a7478-4b75-68ac-cf3c-16c381335d1e"/>
     <hyperlink ref="I591" r:id="rId2" location="error-codes" display="See https://github.com/victronenergy/venus/wiki/dbus#error-codes"/>
-    <hyperlink ref="I937" r:id="rId3" location="error-codes" display="See https://github.com/victronenergy/venus/wiki/dbus#error-codes"/>
+    <hyperlink ref="I938" r:id="rId3" location="error-codes" display="See https://github.com/victronenergy/venus/wiki/dbus#error-codes"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -34398,7 +34433,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C173"/>
+  <dimension ref="A1:C175"/>
   <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="8.57"/>
@@ -35431,6 +35466,16 @@
         <v>1719</v>
       </c>
     </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B174" s="22" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B175" s="22" t="s">
+        <v>1721</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/CCGX-Modbus-TCP-register-list.xlsx
+++ b/CCGX-Modbus-TCP-register-list.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="1760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7065" uniqueCount="1761">
   <si>
     <t xml:space="preserve">NOTE: Use unit-id 100 for the com.victronenergy.system data, for more information see FAQ.</t>
   </si>
@@ -1416,6 +1416,9 @@
     <t xml:space="preserve">/MicroGrid/DirectDrivePQ/Fmin</t>
   </si>
   <si>
+    <t xml:space="preserve">Unsupported</t>
+  </si>
+  <si>
     <t xml:space="preserve">Grid-following (P-Q) range maximum frequency Fmax</t>
   </si>
   <si>
@@ -1450,9 +1453,6 @@
   </si>
   <si>
     <t xml:space="preserve">/MicroGrid/DirectDrivePQ/Activate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will time out after 2 seconds</t>
   </si>
   <si>
     <t xml:space="preserve">Grid-forming (V-f) frequency setpoint f</t>
@@ -5553,6 +5553,9 @@
     <t xml:space="preserve">Make Register 3816 reflect session enery as in the past</t>
   </si>
   <si>
+    <t xml:space="preserve">Mark registers 213-222 as unsupported</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rev 53</t>
   </si>
   <si>
@@ -5587,7 +5590,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5621,6 +5624,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -5763,7 +5773,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5860,11 +5870,19 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5872,11 +5890,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5888,11 +5906,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12012,13 +12026,16 @@
       <c r="I202" s="22" t="s">
         <v>176</v>
       </c>
+      <c r="J202" s="24" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
         <v>157</v>
       </c>
       <c r="B203" s="22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C203" s="22" t="n">
         <v>214</v>
@@ -12033,10 +12050,13 @@
         <v>217</v>
       </c>
       <c r="G203" s="22" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I203" s="22" t="s">
         <v>176</v>
+      </c>
+      <c r="J203" s="24" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12044,7 +12064,7 @@
         <v>157</v>
       </c>
       <c r="B204" s="22" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C204" s="22" t="n">
         <v>215</v>
@@ -12059,10 +12079,13 @@
         <v>174</v>
       </c>
       <c r="G204" s="22" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I204" s="22" t="s">
         <v>103</v>
+      </c>
+      <c r="J204" s="24" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12070,7 +12093,7 @@
         <v>157</v>
       </c>
       <c r="B205" s="22" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C205" s="22" t="n">
         <v>216</v>
@@ -12085,10 +12108,13 @@
         <v>174</v>
       </c>
       <c r="G205" s="22" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I205" s="22" t="s">
         <v>103</v>
+      </c>
+      <c r="J205" s="24" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12096,7 +12122,7 @@
         <v>157</v>
       </c>
       <c r="B206" s="22" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C206" s="22" t="n">
         <v>217</v>
@@ -12111,10 +12137,13 @@
         <v>217</v>
       </c>
       <c r="G206" s="22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I206" s="22" t="s">
         <v>458</v>
+      </c>
+      <c r="J206" s="24" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12122,7 +12151,7 @@
         <v>157</v>
       </c>
       <c r="B207" s="22" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C207" s="22" t="n">
         <v>218</v>
@@ -12137,10 +12166,13 @@
         <v>217</v>
       </c>
       <c r="G207" s="22" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I207" s="22" t="s">
         <v>458</v>
+      </c>
+      <c r="J207" s="24" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12148,7 +12180,7 @@
         <v>157</v>
       </c>
       <c r="B208" s="22" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C208" s="22" t="n">
         <v>219</v>
@@ -12163,13 +12195,13 @@
         <v>264</v>
       </c>
       <c r="G208" s="22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I208" s="22" t="s">
         <v>461</v>
       </c>
-      <c r="J208" s="1" t="s">
-        <v>476</v>
+      <c r="J208" s="24" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12197,6 +12229,9 @@
       <c r="I209" s="22" t="s">
         <v>176</v>
       </c>
+      <c r="J209" s="24" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
@@ -12223,6 +12258,9 @@
       <c r="I210" s="22" t="s">
         <v>458</v>
       </c>
+      <c r="J210" s="24" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
@@ -12249,8 +12287,8 @@
       <c r="I211" s="22" t="s">
         <v>461</v>
       </c>
-      <c r="J211" s="1" t="s">
-        <v>476</v>
+      <c r="J211" s="24" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12260,7 +12298,7 @@
       <c r="B212" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C212" s="24" t="s">
+      <c r="C212" s="25" t="s">
         <v>483</v>
       </c>
       <c r="D212" s="2" t="s">
@@ -12340,15 +12378,15 @@
       <c r="B215" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C215" s="24" t="s">
+      <c r="C215" s="25" t="s">
         <v>491</v>
       </c>
-      <c r="D215" s="0"/>
+      <c r="D215" s="26"/>
       <c r="E215" s="22"/>
-      <c r="G215" s="0" t="s">
+      <c r="G215" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="H215" s="0"/>
+      <c r="H215" s="26"/>
       <c r="I215" s="22"/>
     </row>
     <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18735,7 +18773,7 @@
       <c r="C430" s="23" t="s">
         <v>900</v>
       </c>
-      <c r="D430" s="0"/>
+      <c r="D430" s="26"/>
       <c r="G430" s="1" t="s">
         <v>117</v>
       </c>
@@ -20695,7 +20733,7 @@
       <c r="H498" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I498" s="25"/>
+      <c r="I498" s="27"/>
     </row>
     <row r="499" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
@@ -23464,7 +23502,7 @@
       <c r="B597" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C597" s="24" t="s">
+      <c r="C597" s="25" t="s">
         <v>1142</v>
       </c>
       <c r="G597" s="22" t="s">
@@ -23943,7 +23981,7 @@
       <c r="A616" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="B616" s="26" t="s">
+      <c r="B616" s="28" t="s">
         <v>1184</v>
       </c>
       <c r="C616" s="1" t="n">
@@ -23975,7 +24013,7 @@
       <c r="A617" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="B617" s="26" t="s">
+      <c r="B617" s="28" t="s">
         <v>1189</v>
       </c>
       <c r="C617" s="1" t="n">
@@ -23990,7 +24028,7 @@
       <c r="F617" s="3" t="s">
         <v>1191</v>
       </c>
-      <c r="G617" s="27" t="s">
+      <c r="G617" s="29" t="s">
         <v>1192</v>
       </c>
       <c r="H617" s="1" t="s">
@@ -24007,7 +24045,7 @@
       <c r="A618" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="B618" s="26" t="s">
+      <c r="B618" s="28" t="s">
         <v>1194</v>
       </c>
       <c r="C618" s="1" t="n">
@@ -24036,7 +24074,7 @@
       <c r="A619" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="B619" s="26" t="s">
+      <c r="B619" s="28" t="s">
         <v>1197</v>
       </c>
       <c r="C619" s="1" t="n">
@@ -24057,7 +24095,7 @@
       <c r="H619" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I619" s="26" t="s">
+      <c r="I619" s="28" t="s">
         <v>1200</v>
       </c>
       <c r="J619" s="1" t="s">
@@ -24068,7 +24106,7 @@
       <c r="A620" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="B620" s="26" t="s">
+      <c r="B620" s="28" t="s">
         <v>1201</v>
       </c>
       <c r="C620" s="1" t="n">
@@ -24097,7 +24135,7 @@
       <c r="A621" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="B621" s="26" t="s">
+      <c r="B621" s="28" t="s">
         <v>117</v>
       </c>
       <c r="C621" s="23" t="s">
@@ -24111,7 +24149,7 @@
       <c r="A622" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="B622" s="26" t="s">
+      <c r="B622" s="28" t="s">
         <v>492</v>
       </c>
       <c r="C622" s="1" t="n">
@@ -25358,7 +25396,7 @@
       <c r="E668" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F668" s="28" t="s">
+      <c r="F668" s="30" t="s">
         <v>729</v>
       </c>
       <c r="G668" s="1" t="s">
@@ -25416,7 +25454,7 @@
       <c r="E670" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F670" s="29" t="s">
+      <c r="F670" s="31" t="s">
         <v>1283</v>
       </c>
       <c r="G670" s="1" t="s">
@@ -25442,7 +25480,7 @@
       <c r="E671" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F671" s="29" t="s">
+      <c r="F671" s="31" t="s">
         <v>1283</v>
       </c>
       <c r="G671" s="1" t="s">
@@ -25933,13 +25971,13 @@
       <c r="C690" s="1" t="n">
         <v>3924</v>
       </c>
-      <c r="D690" s="30" t="s">
+      <c r="D690" s="32" t="s">
         <v>136</v>
       </c>
       <c r="E690" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F690" s="29" t="s">
+      <c r="F690" s="31" t="s">
         <v>140</v>
       </c>
       <c r="G690" s="1" t="s">
@@ -25962,13 +26000,13 @@
       <c r="C691" s="1" t="n">
         <v>3926</v>
       </c>
-      <c r="D691" s="30" t="s">
+      <c r="D691" s="32" t="s">
         <v>136</v>
       </c>
       <c r="E691" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F691" s="29" t="s">
+      <c r="F691" s="31" t="s">
         <v>140</v>
       </c>
       <c r="G691" s="1" t="s">
@@ -25991,13 +26029,13 @@
       <c r="C692" s="1" t="n">
         <v>3928</v>
       </c>
-      <c r="D692" s="30" t="s">
+      <c r="D692" s="32" t="s">
         <v>136</v>
       </c>
       <c r="E692" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F692" s="29" t="s">
+      <c r="F692" s="31" t="s">
         <v>140</v>
       </c>
       <c r="G692" s="1" t="s">
@@ -26121,7 +26159,7 @@
       <c r="B697" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C697" s="24" t="s">
+      <c r="C697" s="25" t="s">
         <v>1292</v>
       </c>
       <c r="G697" s="22" t="s">
@@ -26158,7 +26196,7 @@
       <c r="C699" s="22" t="n">
         <v>4000</v>
       </c>
-      <c r="D699" s="30" t="s">
+      <c r="D699" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E699" s="22" t="n">
@@ -26187,7 +26225,7 @@
       <c r="C700" s="22" t="n">
         <v>4001</v>
       </c>
-      <c r="D700" s="30" t="s">
+      <c r="D700" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E700" s="22" t="n">
@@ -26216,7 +26254,7 @@
       <c r="C701" s="22" t="n">
         <v>4002</v>
       </c>
-      <c r="D701" s="30" t="s">
+      <c r="D701" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E701" s="22" t="n">
@@ -26245,7 +26283,7 @@
       <c r="C702" s="22" t="n">
         <v>4003</v>
       </c>
-      <c r="D702" s="30" t="s">
+      <c r="D702" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E702" s="22" t="n">
@@ -26274,7 +26312,7 @@
       <c r="C703" s="22" t="n">
         <v>4004</v>
       </c>
-      <c r="D703" s="30" t="s">
+      <c r="D703" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E703" s="22" t="n">
@@ -26303,7 +26341,7 @@
       <c r="C704" s="22" t="n">
         <v>4006</v>
       </c>
-      <c r="D704" s="30" t="s">
+      <c r="D704" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E704" s="22" t="n">
@@ -26332,7 +26370,7 @@
       <c r="C705" s="22" t="n">
         <v>4007</v>
       </c>
-      <c r="D705" s="30" t="s">
+      <c r="D705" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E705" s="22" t="n">
@@ -26361,7 +26399,7 @@
       <c r="C706" s="22" t="n">
         <v>4008</v>
       </c>
-      <c r="D706" s="30" t="s">
+      <c r="D706" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E706" s="22" t="n">
@@ -26390,7 +26428,7 @@
       <c r="C707" s="22" t="n">
         <v>4009</v>
       </c>
-      <c r="D707" s="30" t="s">
+      <c r="D707" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E707" s="22" t="n">
@@ -26419,7 +26457,7 @@
       <c r="C708" s="22" t="n">
         <v>4010</v>
       </c>
-      <c r="D708" s="30" t="s">
+      <c r="D708" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E708" s="22" t="n">
@@ -26448,7 +26486,7 @@
       <c r="C709" s="22" t="n">
         <v>4011</v>
       </c>
-      <c r="D709" s="30" t="s">
+      <c r="D709" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E709" s="22" t="n">
@@ -26477,7 +26515,7 @@
       <c r="C710" s="22" t="n">
         <v>4100</v>
       </c>
-      <c r="D710" s="30" t="s">
+      <c r="D710" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E710" s="22" t="n">
@@ -26506,7 +26544,7 @@
       <c r="C711" s="22" t="n">
         <v>4101</v>
       </c>
-      <c r="D711" s="30" t="s">
+      <c r="D711" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E711" s="22" t="n">
@@ -26535,7 +26573,7 @@
       <c r="C712" s="22" t="n">
         <v>4102</v>
       </c>
-      <c r="D712" s="30" t="s">
+      <c r="D712" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E712" s="22" t="n">
@@ -26564,7 +26602,7 @@
       <c r="C713" s="22" t="n">
         <v>4103</v>
       </c>
-      <c r="D713" s="30" t="s">
+      <c r="D713" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E713" s="22" t="n">
@@ -26593,7 +26631,7 @@
       <c r="C714" s="22" t="n">
         <v>4104</v>
       </c>
-      <c r="D714" s="30" t="s">
+      <c r="D714" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E714" s="22" t="n">
@@ -26622,7 +26660,7 @@
       <c r="C715" s="22" t="n">
         <v>4106</v>
       </c>
-      <c r="D715" s="30" t="s">
+      <c r="D715" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E715" s="22" t="n">
@@ -26651,7 +26689,7 @@
       <c r="C716" s="22" t="n">
         <v>4107</v>
       </c>
-      <c r="D716" s="30" t="s">
+      <c r="D716" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E716" s="22" t="n">
@@ -26680,7 +26718,7 @@
       <c r="C717" s="22" t="n">
         <v>4108</v>
       </c>
-      <c r="D717" s="30" t="s">
+      <c r="D717" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E717" s="22" t="n">
@@ -26709,7 +26747,7 @@
       <c r="C718" s="22" t="n">
         <v>4109</v>
       </c>
-      <c r="D718" s="30" t="s">
+      <c r="D718" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E718" s="22" t="n">
@@ -26738,7 +26776,7 @@
       <c r="C719" s="22" t="n">
         <v>4110</v>
       </c>
-      <c r="D719" s="30" t="s">
+      <c r="D719" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E719" s="22" t="n">
@@ -26767,7 +26805,7 @@
       <c r="C720" s="22" t="n">
         <v>4111</v>
       </c>
-      <c r="D720" s="30" t="s">
+      <c r="D720" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E720" s="22" t="n">
@@ -26796,7 +26834,7 @@
       <c r="C721" s="22" t="n">
         <v>4112</v>
       </c>
-      <c r="D721" s="30" t="s">
+      <c r="D721" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E721" s="22" t="n">
@@ -26825,7 +26863,7 @@
       <c r="C722" s="22" t="n">
         <v>4113</v>
       </c>
-      <c r="D722" s="30" t="s">
+      <c r="D722" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E722" s="22" t="n">
@@ -26854,7 +26892,7 @@
       <c r="C723" s="22" t="n">
         <v>4114</v>
       </c>
-      <c r="D723" s="30" t="s">
+      <c r="D723" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E723" s="22" t="n">
@@ -26883,7 +26921,7 @@
       <c r="C724" s="22" t="n">
         <v>4115</v>
       </c>
-      <c r="D724" s="30" t="s">
+      <c r="D724" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E724" s="22" t="n">
@@ -26912,7 +26950,7 @@
       <c r="C725" s="22" t="n">
         <v>4116</v>
       </c>
-      <c r="D725" s="30" t="s">
+      <c r="D725" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E725" s="22" t="n">
@@ -26941,7 +26979,7 @@
       <c r="C726" s="22" t="n">
         <v>4117</v>
       </c>
-      <c r="D726" s="30" t="s">
+      <c r="D726" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E726" s="22" t="n">
@@ -26970,7 +27008,7 @@
       <c r="C727" s="22" t="n">
         <v>4118</v>
       </c>
-      <c r="D727" s="30" t="s">
+      <c r="D727" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E727" s="22" t="n">
@@ -26999,7 +27037,7 @@
       <c r="C728" s="22" t="n">
         <v>4119</v>
       </c>
-      <c r="D728" s="30" t="s">
+      <c r="D728" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E728" s="22" t="n">
@@ -27028,7 +27066,7 @@
       <c r="C729" s="22" t="n">
         <v>4120</v>
       </c>
-      <c r="D729" s="30" t="s">
+      <c r="D729" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E729" s="22" t="n">
@@ -27057,7 +27095,7 @@
       <c r="C730" s="22" t="s">
         <v>1314</v>
       </c>
-      <c r="D730" s="30"/>
+      <c r="D730" s="32"/>
       <c r="E730" s="22"/>
       <c r="G730" s="22" t="s">
         <v>117</v>
@@ -27073,7 +27111,7 @@
       <c r="C731" s="22" t="n">
         <v>4220</v>
       </c>
-      <c r="D731" s="30" t="s">
+      <c r="D731" s="32" t="s">
         <v>493</v>
       </c>
       <c r="E731" s="22"/>
@@ -27094,7 +27132,7 @@
       <c r="C732" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="D732" s="30" t="s">
+      <c r="D732" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E732" s="22" t="n">
@@ -27123,7 +27161,7 @@
       <c r="C733" s="22" t="n">
         <v>4201</v>
       </c>
-      <c r="D733" s="30" t="s">
+      <c r="D733" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E733" s="22" t="n">
@@ -27152,7 +27190,7 @@
       <c r="C734" s="22" t="n">
         <v>4202</v>
       </c>
-      <c r="D734" s="30" t="s">
+      <c r="D734" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E734" s="22" t="n">
@@ -27181,7 +27219,7 @@
       <c r="C735" s="22" t="n">
         <v>4203</v>
       </c>
-      <c r="D735" s="30" t="s">
+      <c r="D735" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E735" s="22" t="n">
@@ -27210,7 +27248,7 @@
       <c r="C736" s="22" t="n">
         <v>4204</v>
       </c>
-      <c r="D736" s="30" t="s">
+      <c r="D736" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E736" s="22" t="n">
@@ -27239,7 +27277,7 @@
       <c r="C737" s="22" t="n">
         <v>4206</v>
       </c>
-      <c r="D737" s="30" t="s">
+      <c r="D737" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E737" s="22" t="n">
@@ -27268,7 +27306,7 @@
       <c r="C738" s="22" t="n">
         <v>4207</v>
       </c>
-      <c r="D738" s="30" t="s">
+      <c r="D738" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E738" s="22" t="n">
@@ -27297,7 +27335,7 @@
       <c r="C739" s="22" t="n">
         <v>4208</v>
       </c>
-      <c r="D739" s="30" t="s">
+      <c r="D739" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E739" s="22" t="n">
@@ -27326,7 +27364,7 @@
       <c r="C740" s="22" t="n">
         <v>4209</v>
       </c>
-      <c r="D740" s="30" t="s">
+      <c r="D740" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E740" s="22" t="n">
@@ -27355,7 +27393,7 @@
       <c r="C741" s="22" t="n">
         <v>4210</v>
       </c>
-      <c r="D741" s="30" t="s">
+      <c r="D741" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E741" s="22" t="n">
@@ -27384,7 +27422,7 @@
       <c r="C742" s="22" t="n">
         <v>4211</v>
       </c>
-      <c r="D742" s="30" t="s">
+      <c r="D742" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E742" s="22" t="n">
@@ -27410,10 +27448,10 @@
       <c r="B743" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C743" s="24" t="s">
+      <c r="C743" s="25" t="s">
         <v>1316</v>
       </c>
-      <c r="D743" s="30"/>
+      <c r="D743" s="32"/>
       <c r="E743" s="22"/>
       <c r="G743" s="22" t="s">
         <v>117</v>
@@ -27429,7 +27467,7 @@
       <c r="C744" s="22" t="n">
         <v>4220</v>
       </c>
-      <c r="D744" s="30" t="s">
+      <c r="D744" s="32" t="s">
         <v>493</v>
       </c>
       <c r="E744" s="22"/>
@@ -27450,7 +27488,7 @@
       <c r="C745" s="22" t="n">
         <v>4300</v>
       </c>
-      <c r="D745" s="30" t="s">
+      <c r="D745" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E745" s="22" t="n">
@@ -27479,7 +27517,7 @@
       <c r="C746" s="22" t="n">
         <v>4301</v>
       </c>
-      <c r="D746" s="30" t="s">
+      <c r="D746" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E746" s="22" t="n">
@@ -27508,7 +27546,7 @@
       <c r="C747" s="22" t="n">
         <v>4302</v>
       </c>
-      <c r="D747" s="30" t="s">
+      <c r="D747" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E747" s="22" t="n">
@@ -27537,7 +27575,7 @@
       <c r="C748" s="22" t="n">
         <v>4303</v>
       </c>
-      <c r="D748" s="30" t="s">
+      <c r="D748" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E748" s="22" t="n">
@@ -27566,7 +27604,7 @@
       <c r="C749" s="22" t="n">
         <v>4304</v>
       </c>
-      <c r="D749" s="30" t="s">
+      <c r="D749" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E749" s="22" t="n">
@@ -27595,7 +27633,7 @@
       <c r="C750" s="22" t="n">
         <v>4306</v>
       </c>
-      <c r="D750" s="30" t="s">
+      <c r="D750" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E750" s="22" t="n">
@@ -27624,7 +27662,7 @@
       <c r="C751" s="22" t="n">
         <v>4307</v>
       </c>
-      <c r="D751" s="30" t="s">
+      <c r="D751" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E751" s="22" t="n">
@@ -27653,7 +27691,7 @@
       <c r="C752" s="22" t="n">
         <v>4308</v>
       </c>
-      <c r="D752" s="30" t="s">
+      <c r="D752" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E752" s="22" t="n">
@@ -27682,7 +27720,7 @@
       <c r="C753" s="22" t="n">
         <v>4309</v>
       </c>
-      <c r="D753" s="30" t="s">
+      <c r="D753" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E753" s="22" t="n">
@@ -27711,7 +27749,7 @@
       <c r="C754" s="22" t="n">
         <v>4310</v>
       </c>
-      <c r="D754" s="30" t="s">
+      <c r="D754" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E754" s="22" t="n">
@@ -27740,7 +27778,7 @@
       <c r="C755" s="22" t="n">
         <v>4311</v>
       </c>
-      <c r="D755" s="30" t="s">
+      <c r="D755" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E755" s="22" t="n">
@@ -27766,10 +27804,10 @@
       <c r="B756" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C756" s="24" t="s">
+      <c r="C756" s="25" t="s">
         <v>1320</v>
       </c>
-      <c r="D756" s="30"/>
+      <c r="D756" s="32"/>
       <c r="E756" s="22"/>
       <c r="G756" s="22" t="s">
         <v>117</v>
@@ -27785,7 +27823,7 @@
       <c r="C757" s="22" t="n">
         <v>4320</v>
       </c>
-      <c r="D757" s="30" t="s">
+      <c r="D757" s="32" t="s">
         <v>493</v>
       </c>
       <c r="E757" s="22"/>
@@ -27806,7 +27844,7 @@
       <c r="C758" s="22" t="n">
         <v>4400</v>
       </c>
-      <c r="D758" s="30" t="s">
+      <c r="D758" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E758" s="22" t="n">
@@ -27835,7 +27873,7 @@
       <c r="C759" s="22" t="n">
         <v>4401</v>
       </c>
-      <c r="D759" s="30" t="s">
+      <c r="D759" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E759" s="22" t="n">
@@ -27864,7 +27902,7 @@
       <c r="C760" s="22" t="n">
         <v>4402</v>
       </c>
-      <c r="D760" s="30" t="s">
+      <c r="D760" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E760" s="22" t="n">
@@ -27893,7 +27931,7 @@
       <c r="C761" s="22" t="n">
         <v>4403</v>
       </c>
-      <c r="D761" s="30" t="s">
+      <c r="D761" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E761" s="22" t="n">
@@ -27922,7 +27960,7 @@
       <c r="C762" s="22" t="n">
         <v>4404</v>
       </c>
-      <c r="D762" s="30" t="s">
+      <c r="D762" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E762" s="22" t="n">
@@ -27951,7 +27989,7 @@
       <c r="C763" s="22" t="n">
         <v>4406</v>
       </c>
-      <c r="D763" s="30" t="s">
+      <c r="D763" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E763" s="22" t="n">
@@ -27980,7 +28018,7 @@
       <c r="C764" s="22" t="n">
         <v>4408</v>
       </c>
-      <c r="D764" s="30" t="s">
+      <c r="D764" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E764" s="22" t="n">
@@ -28009,7 +28047,7 @@
       <c r="C765" s="22" t="n">
         <v>4409</v>
       </c>
-      <c r="D765" s="30" t="s">
+      <c r="D765" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E765" s="22" t="n">
@@ -28038,7 +28076,7 @@
       <c r="C766" s="22" t="n">
         <v>4410</v>
       </c>
-      <c r="D766" s="30" t="s">
+      <c r="D766" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E766" s="22" t="n">
@@ -28067,7 +28105,7 @@
       <c r="C767" s="22" t="n">
         <v>4411</v>
       </c>
-      <c r="D767" s="30" t="s">
+      <c r="D767" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E767" s="22" t="n">
@@ -28096,7 +28134,7 @@
       <c r="C768" s="22" t="n">
         <v>4412</v>
       </c>
-      <c r="D768" s="30" t="s">
+      <c r="D768" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E768" s="22" t="n">
@@ -28125,7 +28163,7 @@
       <c r="C769" s="22" t="n">
         <v>4413</v>
       </c>
-      <c r="D769" s="30" t="s">
+      <c r="D769" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E769" s="22" t="n">
@@ -28151,10 +28189,10 @@
       <c r="B770" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C770" s="24" t="s">
+      <c r="C770" s="25" t="s">
         <v>1323</v>
       </c>
-      <c r="D770" s="30"/>
+      <c r="D770" s="32"/>
       <c r="E770" s="22"/>
       <c r="G770" s="22" t="s">
         <v>117</v>
@@ -28170,7 +28208,7 @@
       <c r="C771" s="22" t="n">
         <v>4420</v>
       </c>
-      <c r="D771" s="30" t="s">
+      <c r="D771" s="32" t="s">
         <v>493</v>
       </c>
       <c r="E771" s="22"/>
@@ -28191,7 +28229,7 @@
       <c r="C772" s="22" t="n">
         <v>4500</v>
       </c>
-      <c r="D772" s="30" t="s">
+      <c r="D772" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E772" s="22" t="n">
@@ -28220,7 +28258,7 @@
       <c r="C773" s="22" t="n">
         <v>4501</v>
       </c>
-      <c r="D773" s="30" t="s">
+      <c r="D773" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E773" s="22" t="n">
@@ -28249,7 +28287,7 @@
       <c r="C774" s="22" t="n">
         <v>4502</v>
       </c>
-      <c r="D774" s="30" t="s">
+      <c r="D774" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E774" s="22" t="n">
@@ -28278,7 +28316,7 @@
       <c r="C775" s="22" t="n">
         <v>4503</v>
       </c>
-      <c r="D775" s="30" t="s">
+      <c r="D775" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E775" s="22" t="n">
@@ -28307,7 +28345,7 @@
       <c r="C776" s="22" t="n">
         <v>4504</v>
       </c>
-      <c r="D776" s="30" t="s">
+      <c r="D776" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E776" s="22" t="n">
@@ -28336,7 +28374,7 @@
       <c r="C777" s="22" t="n">
         <v>4505</v>
       </c>
-      <c r="D777" s="30" t="s">
+      <c r="D777" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E777" s="22" t="n">
@@ -28365,7 +28403,7 @@
       <c r="C778" s="22" t="n">
         <v>4506</v>
       </c>
-      <c r="D778" s="30" t="s">
+      <c r="D778" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E778" s="22" t="s">
@@ -28394,7 +28432,7 @@
       <c r="C779" s="22" t="n">
         <v>4507</v>
       </c>
-      <c r="D779" s="30" t="s">
+      <c r="D779" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E779" s="22" t="s">
@@ -28423,7 +28461,7 @@
       <c r="C780" s="22" t="n">
         <v>4508</v>
       </c>
-      <c r="D780" s="30" t="s">
+      <c r="D780" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E780" s="22" t="s">
@@ -28452,7 +28490,7 @@
       <c r="C781" s="22" t="n">
         <v>4509</v>
       </c>
-      <c r="D781" s="30" t="s">
+      <c r="D781" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E781" s="22" t="n">
@@ -28478,7 +28516,7 @@
       <c r="C782" s="22" t="n">
         <v>4510</v>
       </c>
-      <c r="D782" s="30" t="s">
+      <c r="D782" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E782" s="22" t="n">
@@ -28507,7 +28545,7 @@
       <c r="C783" s="22" t="n">
         <v>4511</v>
       </c>
-      <c r="D783" s="30" t="s">
+      <c r="D783" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E783" s="22" t="n">
@@ -28536,7 +28574,7 @@
       <c r="C784" s="22" t="n">
         <v>4512</v>
       </c>
-      <c r="D784" s="30" t="s">
+      <c r="D784" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E784" s="22" t="n">
@@ -28565,7 +28603,7 @@
       <c r="C785" s="22" t="n">
         <v>4513</v>
       </c>
-      <c r="D785" s="30" t="s">
+      <c r="D785" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E785" s="22" t="n">
@@ -28594,7 +28632,7 @@
       <c r="C786" s="22" t="n">
         <v>4514</v>
       </c>
-      <c r="D786" s="30" t="s">
+      <c r="D786" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E786" s="22" t="n">
@@ -28623,7 +28661,7 @@
       <c r="C787" s="22" t="n">
         <v>4515</v>
       </c>
-      <c r="D787" s="30" t="s">
+      <c r="D787" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E787" s="22" t="n">
@@ -28652,7 +28690,7 @@
       <c r="C788" s="22" t="n">
         <v>4516</v>
       </c>
-      <c r="D788" s="30" t="s">
+      <c r="D788" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E788" s="22" t="s">
@@ -28681,7 +28719,7 @@
       <c r="C789" s="22" t="n">
         <v>4517</v>
       </c>
-      <c r="D789" s="30" t="s">
+      <c r="D789" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E789" s="22" t="s">
@@ -28710,7 +28748,7 @@
       <c r="C790" s="22" t="n">
         <v>4518</v>
       </c>
-      <c r="D790" s="30" t="s">
+      <c r="D790" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E790" s="22" t="s">
@@ -28739,7 +28777,7 @@
       <c r="C791" s="22" t="n">
         <v>4519</v>
       </c>
-      <c r="D791" s="30" t="s">
+      <c r="D791" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E791" s="22" t="n">
@@ -28768,7 +28806,7 @@
       <c r="C792" s="22" t="n">
         <v>4520</v>
       </c>
-      <c r="D792" s="30" t="s">
+      <c r="D792" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E792" s="22" t="n">
@@ -28797,7 +28835,7 @@
       <c r="C793" s="22" t="n">
         <v>4521</v>
       </c>
-      <c r="D793" s="30" t="s">
+      <c r="D793" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E793" s="22" t="n">
@@ -28826,7 +28864,7 @@
       <c r="C794" s="22" t="n">
         <v>4522</v>
       </c>
-      <c r="D794" s="30" t="s">
+      <c r="D794" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E794" s="22" t="n">
@@ -28855,7 +28893,7 @@
       <c r="C795" s="22" t="n">
         <v>4523</v>
       </c>
-      <c r="D795" s="30" t="s">
+      <c r="D795" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E795" s="22" t="n">
@@ -28884,7 +28922,7 @@
       <c r="C796" s="22" t="n">
         <v>4524</v>
       </c>
-      <c r="D796" s="30" t="s">
+      <c r="D796" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E796" s="22" t="n">
@@ -28913,7 +28951,7 @@
       <c r="C797" s="22" t="n">
         <v>4525</v>
       </c>
-      <c r="D797" s="30" t="s">
+      <c r="D797" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E797" s="22" t="n">
@@ -28942,7 +28980,7 @@
       <c r="C798" s="22" t="n">
         <v>4526</v>
       </c>
-      <c r="D798" s="30" t="s">
+      <c r="D798" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E798" s="22" t="n">
@@ -28971,7 +29009,7 @@
       <c r="C799" s="22" t="n">
         <v>4527</v>
       </c>
-      <c r="D799" s="30" t="s">
+      <c r="D799" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E799" s="22" t="n">
@@ -29000,7 +29038,7 @@
       <c r="C800" s="22" t="n">
         <v>4528</v>
       </c>
-      <c r="D800" s="30" t="s">
+      <c r="D800" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E800" s="22" t="n">
@@ -29029,7 +29067,7 @@
       <c r="C801" s="22" t="n">
         <v>4529</v>
       </c>
-      <c r="D801" s="30" t="s">
+      <c r="D801" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E801" s="22" t="n">
@@ -29058,7 +29096,7 @@
       <c r="C802" s="22" t="n">
         <v>4530</v>
       </c>
-      <c r="D802" s="30" t="s">
+      <c r="D802" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E802" s="22" t="n">
@@ -29087,7 +29125,7 @@
       <c r="C803" s="22" t="n">
         <v>4531</v>
       </c>
-      <c r="D803" s="30" t="s">
+      <c r="D803" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E803" s="22" t="n">
@@ -29116,7 +29154,7 @@
       <c r="C804" s="22" t="n">
         <v>4532</v>
       </c>
-      <c r="D804" s="30" t="s">
+      <c r="D804" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E804" s="22" t="n">
@@ -29145,7 +29183,7 @@
       <c r="C805" s="22" t="n">
         <v>4533</v>
       </c>
-      <c r="D805" s="30" t="s">
+      <c r="D805" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E805" s="22" t="n">
@@ -29174,7 +29212,7 @@
       <c r="C806" s="22" t="n">
         <v>4534</v>
       </c>
-      <c r="D806" s="30" t="s">
+      <c r="D806" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E806" s="22" t="n">
@@ -29203,7 +29241,7 @@
       <c r="C807" s="22" t="n">
         <v>4535</v>
       </c>
-      <c r="D807" s="30" t="s">
+      <c r="D807" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E807" s="22" t="n">
@@ -29232,7 +29270,7 @@
       <c r="C808" s="22" t="n">
         <v>4536</v>
       </c>
-      <c r="D808" s="30" t="s">
+      <c r="D808" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E808" s="22" t="n">
@@ -29261,7 +29299,7 @@
       <c r="C809" s="22" t="n">
         <v>4537</v>
       </c>
-      <c r="D809" s="30" t="s">
+      <c r="D809" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E809" s="22" t="n">
@@ -29290,7 +29328,7 @@
       <c r="C810" s="22" t="n">
         <v>4538</v>
       </c>
-      <c r="D810" s="30" t="s">
+      <c r="D810" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E810" s="22" t="n">
@@ -29319,7 +29357,7 @@
       <c r="C811" s="22" t="n">
         <v>4539</v>
       </c>
-      <c r="D811" s="30" t="s">
+      <c r="D811" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E811" s="22" t="n">
@@ -29348,7 +29386,7 @@
       <c r="C812" s="22" t="n">
         <v>4540</v>
       </c>
-      <c r="D812" s="30" t="s">
+      <c r="D812" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E812" s="22" t="n">
@@ -29377,7 +29415,7 @@
       <c r="C813" s="22" t="n">
         <v>4541</v>
       </c>
-      <c r="D813" s="30" t="s">
+      <c r="D813" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E813" s="22" t="n">
@@ -29406,7 +29444,7 @@
       <c r="C814" s="22" t="n">
         <v>4542</v>
       </c>
-      <c r="D814" s="30" t="s">
+      <c r="D814" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E814" s="22" t="n">
@@ -29435,7 +29473,7 @@
       <c r="C815" s="22" t="n">
         <v>4543</v>
       </c>
-      <c r="D815" s="30" t="s">
+      <c r="D815" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E815" s="22" t="n">
@@ -29464,7 +29502,7 @@
       <c r="C816" s="22" t="n">
         <v>4544</v>
       </c>
-      <c r="D816" s="30" t="s">
+      <c r="D816" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E816" s="22" t="n">
@@ -29493,7 +29531,7 @@
       <c r="C817" s="22" t="n">
         <v>4545</v>
       </c>
-      <c r="D817" s="30" t="s">
+      <c r="D817" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E817" s="22" t="n">
@@ -29522,7 +29560,7 @@
       <c r="C818" s="22" t="n">
         <v>4546</v>
       </c>
-      <c r="D818" s="30" t="s">
+      <c r="D818" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E818" s="22" t="n">
@@ -29551,7 +29589,7 @@
       <c r="C819" s="22" t="n">
         <v>4548</v>
       </c>
-      <c r="D819" s="30" t="s">
+      <c r="D819" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E819" s="22" t="n">
@@ -29580,7 +29618,7 @@
       <c r="C820" s="22" t="n">
         <v>4550</v>
       </c>
-      <c r="D820" s="30" t="s">
+      <c r="D820" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E820" s="22" t="n">
@@ -29609,7 +29647,7 @@
       <c r="C821" s="22" t="n">
         <v>4552</v>
       </c>
-      <c r="D821" s="30" t="s">
+      <c r="D821" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E821" s="22" t="n">
@@ -29638,7 +29676,7 @@
       <c r="C822" s="22" t="n">
         <v>4554</v>
       </c>
-      <c r="D822" s="30" t="s">
+      <c r="D822" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E822" s="22" t="n">
@@ -29667,7 +29705,7 @@
       <c r="C823" s="22" t="n">
         <v>4556</v>
       </c>
-      <c r="D823" s="30" t="s">
+      <c r="D823" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E823" s="22" t="n">
@@ -29696,7 +29734,7 @@
       <c r="C824" s="22" t="n">
         <v>4558</v>
       </c>
-      <c r="D824" s="30" t="s">
+      <c r="D824" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E824" s="22" t="n">
@@ -29725,7 +29763,7 @@
       <c r="C825" s="22" t="n">
         <v>4560</v>
       </c>
-      <c r="D825" s="30" t="s">
+      <c r="D825" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E825" s="22" t="n">
@@ -29754,7 +29792,7 @@
       <c r="C826" s="22" t="n">
         <v>4562</v>
       </c>
-      <c r="D826" s="30" t="s">
+      <c r="D826" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E826" s="22" t="n">
@@ -29783,7 +29821,7 @@
       <c r="C827" s="22" t="n">
         <v>4564</v>
       </c>
-      <c r="D827" s="30" t="s">
+      <c r="D827" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E827" s="22" t="n">
@@ -29812,7 +29850,7 @@
       <c r="C828" s="22" t="n">
         <v>4566</v>
       </c>
-      <c r="D828" s="30" t="s">
+      <c r="D828" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E828" s="22" t="n">
@@ -29841,7 +29879,7 @@
       <c r="C829" s="22" t="n">
         <v>4568</v>
       </c>
-      <c r="D829" s="30" t="s">
+      <c r="D829" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E829" s="22" t="n">
@@ -29870,7 +29908,7 @@
       <c r="C830" s="22" t="n">
         <v>4570</v>
       </c>
-      <c r="D830" s="30" t="s">
+      <c r="D830" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E830" s="22" t="n">
@@ -29899,7 +29937,7 @@
       <c r="C831" s="22" t="n">
         <v>4572</v>
       </c>
-      <c r="D831" s="30" t="s">
+      <c r="D831" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E831" s="22" t="n">
@@ -29928,7 +29966,7 @@
       <c r="C832" s="22" t="n">
         <v>4574</v>
       </c>
-      <c r="D832" s="30" t="s">
+      <c r="D832" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E832" s="22" t="n">
@@ -29957,7 +29995,7 @@
       <c r="C833" s="22" t="n">
         <v>4575</v>
       </c>
-      <c r="D833" s="30" t="s">
+      <c r="D833" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E833" s="22" t="n">
@@ -29986,7 +30024,7 @@
       <c r="C834" s="22" t="n">
         <v>4576</v>
       </c>
-      <c r="D834" s="30" t="s">
+      <c r="D834" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E834" s="22" t="n">
@@ -30015,7 +30053,7 @@
       <c r="C835" s="22" t="n">
         <v>4577</v>
       </c>
-      <c r="D835" s="30" t="s">
+      <c r="D835" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E835" s="1" t="n">
@@ -30044,7 +30082,7 @@
       <c r="C836" s="22" t="n">
         <v>4578</v>
       </c>
-      <c r="D836" s="30" t="s">
+      <c r="D836" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E836" s="22" t="n">
@@ -30077,7 +30115,7 @@
       <c r="C837" s="22" t="n">
         <v>4579</v>
       </c>
-      <c r="D837" s="30" t="s">
+      <c r="D837" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E837" s="22" t="n">
@@ -30110,7 +30148,7 @@
       <c r="C838" s="22" t="n">
         <v>4580</v>
       </c>
-      <c r="D838" s="30" t="s">
+      <c r="D838" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E838" s="22" t="n">
@@ -30143,7 +30181,7 @@
       <c r="C839" s="22" t="n">
         <v>4581</v>
       </c>
-      <c r="D839" s="30" t="s">
+      <c r="D839" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E839" s="22" t="n">
@@ -30176,7 +30214,7 @@
       <c r="C840" s="22" t="n">
         <v>4582</v>
       </c>
-      <c r="D840" s="30" t="s">
+      <c r="D840" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E840" s="22" t="n">
@@ -30209,7 +30247,7 @@
       <c r="C841" s="22" t="n">
         <v>4583</v>
       </c>
-      <c r="D841" s="30" t="s">
+      <c r="D841" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E841" s="22" t="n">
@@ -30242,7 +30280,7 @@
       <c r="C842" s="22" t="n">
         <v>4584</v>
       </c>
-      <c r="D842" s="30" t="s">
+      <c r="D842" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E842" s="22" t="n">
@@ -30275,7 +30313,7 @@
       <c r="C843" s="22" t="n">
         <v>4585</v>
       </c>
-      <c r="D843" s="30" t="s">
+      <c r="D843" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E843" s="22" t="n">
@@ -30308,7 +30346,7 @@
       <c r="C844" s="22" t="n">
         <v>4586</v>
       </c>
-      <c r="D844" s="30" t="s">
+      <c r="D844" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E844" s="22" t="n">
@@ -30341,7 +30379,7 @@
       <c r="C845" s="22" t="n">
         <v>4587</v>
       </c>
-      <c r="D845" s="30" t="s">
+      <c r="D845" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E845" s="22" t="n">
@@ -30374,7 +30412,7 @@
       <c r="C846" s="22" t="n">
         <v>4588</v>
       </c>
-      <c r="D846" s="30" t="s">
+      <c r="D846" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E846" s="22" t="n">
@@ -30407,7 +30445,7 @@
       <c r="C847" s="22" t="n">
         <v>4589</v>
       </c>
-      <c r="D847" s="30" t="s">
+      <c r="D847" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E847" s="22" t="n">
@@ -30440,7 +30478,7 @@
       <c r="C848" s="22" t="n">
         <v>4590</v>
       </c>
-      <c r="D848" s="30" t="s">
+      <c r="D848" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E848" s="22" t="n">
@@ -30473,7 +30511,7 @@
       <c r="C849" s="22" t="n">
         <v>4591</v>
       </c>
-      <c r="D849" s="30" t="s">
+      <c r="D849" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E849" s="22" t="n">
@@ -30506,7 +30544,7 @@
       <c r="C850" s="22" t="n">
         <v>4592</v>
       </c>
-      <c r="D850" s="30" t="s">
+      <c r="D850" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E850" s="22" t="n">
@@ -30539,7 +30577,7 @@
       <c r="C851" s="22" t="n">
         <v>4593</v>
       </c>
-      <c r="D851" s="30" t="s">
+      <c r="D851" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E851" s="22" t="n">
@@ -30572,7 +30610,7 @@
       <c r="C852" s="1" t="n">
         <v>4594</v>
       </c>
-      <c r="D852" s="30" t="s">
+      <c r="D852" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E852" s="1" t="n">
@@ -30601,7 +30639,7 @@
       <c r="C853" s="1" t="n">
         <v>4595</v>
       </c>
-      <c r="D853" s="30" t="s">
+      <c r="D853" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E853" s="1" t="n">
@@ -30630,7 +30668,7 @@
       <c r="C854" s="1" t="n">
         <v>4596</v>
       </c>
-      <c r="D854" s="30" t="s">
+      <c r="D854" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E854" s="1" t="n">
@@ -30659,7 +30697,7 @@
       <c r="C855" s="1" t="n">
         <v>4597</v>
       </c>
-      <c r="D855" s="30" t="s">
+      <c r="D855" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E855" s="1" t="n">
@@ -30688,7 +30726,7 @@
       <c r="C856" s="1" t="n">
         <v>4598</v>
       </c>
-      <c r="D856" s="30" t="s">
+      <c r="D856" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E856" s="1" t="n">
@@ -30717,7 +30755,7 @@
       <c r="C857" s="1" t="n">
         <v>4599</v>
       </c>
-      <c r="D857" s="30" t="s">
+      <c r="D857" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E857" s="1" t="n">
@@ -30746,7 +30784,7 @@
       <c r="C858" s="1" t="n">
         <v>4600</v>
       </c>
-      <c r="D858" s="30" t="s">
+      <c r="D858" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E858" s="1" t="n">
@@ -30775,7 +30813,7 @@
       <c r="C859" s="1" t="n">
         <v>4601</v>
       </c>
-      <c r="D859" s="30" t="s">
+      <c r="D859" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E859" s="1" t="n">
@@ -30804,7 +30842,7 @@
       <c r="C860" s="1" t="n">
         <v>4602</v>
       </c>
-      <c r="D860" s="30" t="s">
+      <c r="D860" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E860" s="1" t="n">
@@ -30865,7 +30903,7 @@
       <c r="C862" s="1" t="n">
         <v>4605</v>
       </c>
-      <c r="D862" s="30" t="s">
+      <c r="D862" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E862" s="1" t="n">
@@ -30894,7 +30932,7 @@
       <c r="C863" s="1" t="n">
         <v>4606</v>
       </c>
-      <c r="D863" s="30" t="s">
+      <c r="D863" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E863" s="1" t="n">
@@ -30923,7 +30961,7 @@
       <c r="C864" s="1" t="n">
         <v>4607</v>
       </c>
-      <c r="D864" s="30" t="s">
+      <c r="D864" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E864" s="1" t="n">
@@ -30952,7 +30990,7 @@
       <c r="C865" s="1" t="n">
         <v>4608</v>
       </c>
-      <c r="D865" s="30" t="s">
+      <c r="D865" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E865" s="1" t="n">
@@ -30981,7 +31019,7 @@
       <c r="C866" s="1" t="n">
         <v>4609</v>
       </c>
-      <c r="D866" s="30" t="s">
+      <c r="D866" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E866" s="1" t="n">
@@ -31010,7 +31048,7 @@
       <c r="C867" s="1" t="n">
         <v>4610</v>
       </c>
-      <c r="D867" s="30" t="s">
+      <c r="D867" s="32" t="s">
         <v>136</v>
       </c>
       <c r="E867" s="1" t="n">
@@ -31039,7 +31077,7 @@
       <c r="C868" s="1" t="n">
         <v>4612</v>
       </c>
-      <c r="D868" s="30" t="s">
+      <c r="D868" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E868" s="1" t="n">
@@ -31068,7 +31106,7 @@
       <c r="C869" s="1" t="n">
         <v>4613</v>
       </c>
-      <c r="D869" s="30" t="s">
+      <c r="D869" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E869" s="1" t="n">
@@ -31097,7 +31135,7 @@
       <c r="C870" s="1" t="n">
         <v>4614</v>
       </c>
-      <c r="D870" s="30" t="s">
+      <c r="D870" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E870" s="1" t="n">
@@ -31126,7 +31164,7 @@
       <c r="C871" s="1" t="n">
         <v>4615</v>
       </c>
-      <c r="D871" s="30" t="s">
+      <c r="D871" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E871" s="1" t="n">
@@ -31155,7 +31193,7 @@
       <c r="C872" s="23" t="s">
         <v>1385</v>
       </c>
-      <c r="D872" s="30"/>
+      <c r="D872" s="32"/>
     </row>
     <row r="873" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A873" s="1" t="s">
@@ -31167,7 +31205,7 @@
       <c r="C873" s="1" t="n">
         <v>4620</v>
       </c>
-      <c r="D873" s="30" t="s">
+      <c r="D873" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E873" s="22" t="n">
@@ -31196,7 +31234,7 @@
       <c r="C874" s="1" t="n">
         <v>4621</v>
       </c>
-      <c r="D874" s="30"/>
+      <c r="D874" s="32"/>
       <c r="E874" s="22"/>
       <c r="G874" s="22" t="s">
         <v>117</v>
@@ -31214,7 +31252,7 @@
       <c r="C875" s="1" t="n">
         <v>4622</v>
       </c>
-      <c r="D875" s="30" t="s">
+      <c r="D875" s="32" t="s">
         <v>493</v>
       </c>
       <c r="E875" s="22"/>
@@ -31352,7 +31390,7 @@
       <c r="C880" s="1" t="n">
         <v>4700</v>
       </c>
-      <c r="D880" s="30" t="s">
+      <c r="D880" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E880" s="1" t="n">
@@ -31381,7 +31419,7 @@
       <c r="C881" s="1" t="n">
         <v>4701</v>
       </c>
-      <c r="D881" s="30" t="s">
+      <c r="D881" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E881" s="1" t="n">
@@ -31410,7 +31448,7 @@
       <c r="C882" s="1" t="n">
         <v>4702</v>
       </c>
-      <c r="D882" s="30" t="s">
+      <c r="D882" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E882" s="1" t="n">
@@ -31439,7 +31477,7 @@
       <c r="C883" s="1" t="n">
         <v>4703</v>
       </c>
-      <c r="D883" s="30" t="s">
+      <c r="D883" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E883" s="1" t="n">
@@ -31468,7 +31506,7 @@
       <c r="C884" s="1" t="n">
         <v>4704</v>
       </c>
-      <c r="D884" s="30" t="s">
+      <c r="D884" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E884" s="1" t="n">
@@ -31497,7 +31535,7 @@
       <c r="C885" s="22" t="n">
         <v>4800</v>
       </c>
-      <c r="D885" s="30" t="s">
+      <c r="D885" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E885" s="22" t="n">
@@ -31523,7 +31561,7 @@
       <c r="C886" s="22" t="n">
         <v>4801</v>
       </c>
-      <c r="D886" s="30" t="s">
+      <c r="D886" s="32" t="s">
         <v>155</v>
       </c>
       <c r="E886" s="22" t="n">
@@ -31549,7 +31587,7 @@
       <c r="C887" s="22" t="n">
         <v>4803</v>
       </c>
-      <c r="D887" s="30" t="s">
+      <c r="D887" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E887" s="22" t="n">
@@ -31578,7 +31616,7 @@
       <c r="C888" s="22" t="n">
         <v>4804</v>
       </c>
-      <c r="D888" s="30" t="s">
+      <c r="D888" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E888" s="22" t="n">
@@ -31607,7 +31645,7 @@
       <c r="C889" s="22" t="n">
         <v>4805</v>
       </c>
-      <c r="D889" s="30" t="s">
+      <c r="D889" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E889" s="22" t="n">
@@ -31636,7 +31674,7 @@
       <c r="C890" s="22" t="n">
         <v>4806</v>
       </c>
-      <c r="D890" s="30" t="s">
+      <c r="D890" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E890" s="22" t="n">
@@ -31665,7 +31703,7 @@
       <c r="C891" s="22" t="n">
         <v>4807</v>
       </c>
-      <c r="D891" s="30" t="s">
+      <c r="D891" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E891" s="22" t="n">
@@ -31694,7 +31732,7 @@
       <c r="C892" s="22" t="n">
         <v>4808</v>
       </c>
-      <c r="D892" s="30" t="s">
+      <c r="D892" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E892" s="22" t="n">
@@ -31723,7 +31761,7 @@
       <c r="C893" s="22" t="n">
         <v>4809</v>
       </c>
-      <c r="D893" s="30" t="s">
+      <c r="D893" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E893" s="22" t="n">
@@ -31752,7 +31790,7 @@
       <c r="C894" s="22" t="n">
         <v>4810</v>
       </c>
-      <c r="D894" s="30" t="s">
+      <c r="D894" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E894" s="22" t="n">
@@ -31781,7 +31819,7 @@
       <c r="C895" s="22" t="n">
         <v>4811</v>
       </c>
-      <c r="D895" s="30" t="s">
+      <c r="D895" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E895" s="22" t="n">
@@ -31807,10 +31845,10 @@
       <c r="B896" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C896" s="24" t="s">
+      <c r="C896" s="25" t="s">
         <v>1402</v>
       </c>
-      <c r="D896" s="30"/>
+      <c r="D896" s="32"/>
       <c r="E896" s="22"/>
       <c r="G896" s="22" t="s">
         <v>117</v>
@@ -31827,7 +31865,7 @@
       <c r="C897" s="22" t="n">
         <v>4820</v>
       </c>
-      <c r="D897" s="30" t="s">
+      <c r="D897" s="32" t="s">
         <v>493</v>
       </c>
       <c r="E897" s="22"/>
@@ -31849,7 +31887,7 @@
       <c r="C898" s="22" t="n">
         <v>4900</v>
       </c>
-      <c r="D898" s="30" t="s">
+      <c r="D898" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E898" s="22" t="n">
@@ -31878,7 +31916,7 @@
       <c r="C899" s="22" t="n">
         <v>4901</v>
       </c>
-      <c r="D899" s="30" t="s">
+      <c r="D899" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E899" s="22" t="n">
@@ -31907,7 +31945,7 @@
       <c r="C900" s="22" t="n">
         <v>4902</v>
       </c>
-      <c r="D900" s="30" t="s">
+      <c r="D900" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E900" s="22" t="n">
@@ -31936,7 +31974,7 @@
       <c r="C901" s="22" t="n">
         <v>4903</v>
       </c>
-      <c r="D901" s="30" t="s">
+      <c r="D901" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E901" s="22" t="n">
@@ -31965,7 +32003,7 @@
       <c r="C902" s="22" t="n">
         <v>4904</v>
       </c>
-      <c r="D902" s="30" t="s">
+      <c r="D902" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E902" s="22" t="n">
@@ -31994,7 +32032,7 @@
       <c r="C903" s="22" t="n">
         <v>4905</v>
       </c>
-      <c r="D903" s="30" t="s">
+      <c r="D903" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E903" s="22" t="n">
@@ -32023,7 +32061,7 @@
       <c r="C904" s="22" t="n">
         <v>4906</v>
       </c>
-      <c r="D904" s="30" t="s">
+      <c r="D904" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E904" s="22" t="n">
@@ -32052,7 +32090,7 @@
       <c r="C905" s="22" t="n">
         <v>4907</v>
       </c>
-      <c r="D905" s="30" t="s">
+      <c r="D905" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E905" s="22" t="s">
@@ -32081,7 +32119,7 @@
       <c r="C906" s="22" t="n">
         <v>4908</v>
       </c>
-      <c r="D906" s="30" t="s">
+      <c r="D906" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E906" s="22" t="s">
@@ -32110,7 +32148,7 @@
       <c r="C907" s="22" t="n">
         <v>4909</v>
       </c>
-      <c r="D907" s="30" t="s">
+      <c r="D907" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E907" s="22" t="s">
@@ -32139,7 +32177,7 @@
       <c r="C908" s="22" t="n">
         <v>4910</v>
       </c>
-      <c r="D908" s="30" t="s">
+      <c r="D908" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E908" s="22" t="n">
@@ -32168,7 +32206,7 @@
       <c r="C909" s="22" t="n">
         <v>4911</v>
       </c>
-      <c r="D909" s="30" t="s">
+      <c r="D909" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E909" s="22" t="n">
@@ -32197,7 +32235,7 @@
       <c r="C910" s="22" t="n">
         <v>4912</v>
       </c>
-      <c r="D910" s="30" t="s">
+      <c r="D910" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E910" s="22" t="n">
@@ -32226,7 +32264,7 @@
       <c r="C911" s="22" t="n">
         <v>4913</v>
       </c>
-      <c r="D911" s="30" t="s">
+      <c r="D911" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E911" s="22" t="n">
@@ -32255,7 +32293,7 @@
       <c r="C912" s="22" t="n">
         <v>4914</v>
       </c>
-      <c r="D912" s="30" t="s">
+      <c r="D912" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E912" s="22" t="n">
@@ -32284,7 +32322,7 @@
       <c r="C913" s="22" t="n">
         <v>4915</v>
       </c>
-      <c r="D913" s="30" t="s">
+      <c r="D913" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E913" s="22" t="n">
@@ -32313,7 +32351,7 @@
       <c r="C914" s="22" t="n">
         <v>4916</v>
       </c>
-      <c r="D914" s="30" t="s">
+      <c r="D914" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E914" s="22" t="n">
@@ -32342,7 +32380,7 @@
       <c r="C915" s="22" t="n">
         <v>4917</v>
       </c>
-      <c r="D915" s="30" t="s">
+      <c r="D915" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E915" s="22" t="s">
@@ -32371,7 +32409,7 @@
       <c r="C916" s="22" t="n">
         <v>4918</v>
       </c>
-      <c r="D916" s="30" t="s">
+      <c r="D916" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E916" s="22" t="s">
@@ -32400,7 +32438,7 @@
       <c r="C917" s="22" t="n">
         <v>4919</v>
       </c>
-      <c r="D917" s="30" t="s">
+      <c r="D917" s="32" t="s">
         <v>59</v>
       </c>
       <c r="E917" s="22" t="s">
@@ -32429,7 +32467,7 @@
       <c r="C918" s="22" t="n">
         <v>4920</v>
       </c>
-      <c r="D918" s="30" t="s">
+      <c r="D918" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E918" s="22" t="n">
@@ -32458,7 +32496,7 @@
       <c r="C919" s="22" t="n">
         <v>4921</v>
       </c>
-      <c r="D919" s="30" t="s">
+      <c r="D919" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E919" s="22" t="n">
@@ -32487,7 +32525,7 @@
       <c r="C920" s="22" t="n">
         <v>4922</v>
       </c>
-      <c r="D920" s="30" t="s">
+      <c r="D920" s="32" t="s">
         <v>136</v>
       </c>
       <c r="E920" s="22" t="n">
@@ -32516,7 +32554,7 @@
       <c r="C921" s="22" t="n">
         <v>4924</v>
       </c>
-      <c r="D921" s="30" t="s">
+      <c r="D921" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E921" s="22" t="n">
@@ -32545,7 +32583,7 @@
       <c r="C922" s="1" t="n">
         <v>4925</v>
       </c>
-      <c r="D922" s="30" t="s">
+      <c r="D922" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E922" s="1" t="n">
@@ -32778,19 +32816,19 @@
       <c r="B932" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="C932" s="31" t="n">
+      <c r="C932" s="26" t="n">
         <v>5200</v>
       </c>
-      <c r="D932" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E932" s="31" t="n">
+      <c r="D932" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E932" s="26" t="n">
         <v>1</v>
       </c>
       <c r="F932" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G932" s="31" t="s">
+      <c r="G932" s="26" t="s">
         <v>1033</v>
       </c>
       <c r="H932" s="1" t="s">
@@ -32804,19 +32842,19 @@
       <c r="B933" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="C933" s="31" t="n">
+      <c r="C933" s="26" t="n">
         <v>5201</v>
       </c>
-      <c r="D933" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E933" s="31" t="n">
+      <c r="D933" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E933" s="26" t="n">
         <v>1</v>
       </c>
       <c r="F933" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G933" s="31" t="s">
+      <c r="G933" s="26" t="s">
         <v>1113</v>
       </c>
       <c r="H933" s="1" t="s">
@@ -32830,19 +32868,19 @@
       <c r="B934" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="C934" s="31" t="n">
+      <c r="C934" s="26" t="n">
         <v>5202</v>
       </c>
-      <c r="D934" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E934" s="31" t="n">
+      <c r="D934" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E934" s="26" t="n">
         <v>1</v>
       </c>
       <c r="F934" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G934" s="31" t="s">
+      <c r="G934" s="26" t="s">
         <v>669</v>
       </c>
       <c r="H934" s="1" t="s">
@@ -32856,19 +32894,19 @@
       <c r="B935" s="1" t="s">
         <v>1391</v>
       </c>
-      <c r="C935" s="31" t="n">
+      <c r="C935" s="26" t="n">
         <v>5203</v>
       </c>
-      <c r="D935" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E935" s="31" t="n">
+      <c r="D935" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E935" s="26" t="n">
         <v>1</v>
       </c>
       <c r="F935" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G935" s="31" t="s">
+      <c r="G935" s="26" t="s">
         <v>1117</v>
       </c>
       <c r="H935" s="1" t="s">
@@ -32882,19 +32920,19 @@
       <c r="B936" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="C936" s="31" t="n">
+      <c r="C936" s="26" t="n">
         <v>5204</v>
       </c>
-      <c r="D936" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E936" s="31" t="n">
+      <c r="D936" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E936" s="26" t="n">
         <v>1</v>
       </c>
       <c r="F936" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G936" s="31" t="s">
+      <c r="G936" s="26" t="s">
         <v>1133</v>
       </c>
       <c r="H936" s="1" t="s">
@@ -32911,19 +32949,19 @@
       <c r="B937" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="C937" s="31" t="n">
+      <c r="C937" s="26" t="n">
         <v>5205</v>
       </c>
-      <c r="D937" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E937" s="31" t="n">
+      <c r="D937" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E937" s="26" t="n">
         <v>100</v>
       </c>
       <c r="F937" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G937" s="31" t="s">
+      <c r="G937" s="26" t="s">
         <v>218</v>
       </c>
       <c r="H937" s="1" t="s">
@@ -32940,19 +32978,19 @@
       <c r="B938" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="C938" s="31" t="n">
+      <c r="C938" s="26" t="n">
         <v>5206</v>
       </c>
-      <c r="D938" s="30" t="s">
+      <c r="D938" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E938" s="31" t="n">
+      <c r="E938" s="26" t="n">
         <v>10</v>
       </c>
       <c r="F938" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G938" s="31" t="s">
+      <c r="G938" s="26" t="s">
         <v>220</v>
       </c>
       <c r="H938" s="1" t="s">
@@ -32966,22 +33004,22 @@
       <c r="A939" s="22" t="s">
         <v>1417</v>
       </c>
-      <c r="B939" s="31" t="s">
+      <c r="B939" s="26" t="s">
         <v>1118</v>
       </c>
-      <c r="C939" s="31" t="n">
+      <c r="C939" s="26" t="n">
         <v>5207</v>
       </c>
-      <c r="D939" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E939" s="31" t="n">
+      <c r="D939" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E939" s="26" t="n">
         <v>1</v>
       </c>
       <c r="F939" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G939" s="31" t="s">
+      <c r="G939" s="26" t="s">
         <v>1119</v>
       </c>
       <c r="H939" s="1" t="s">
@@ -32998,19 +33036,19 @@
       <c r="B940" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="C940" s="31" t="n">
+      <c r="C940" s="26" t="n">
         <v>5208</v>
       </c>
-      <c r="D940" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E940" s="31" t="n">
+      <c r="D940" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E940" s="26" t="n">
         <v>1</v>
       </c>
       <c r="F940" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G940" s="31" t="s">
+      <c r="G940" s="26" t="s">
         <v>1121</v>
       </c>
       <c r="H940" s="1" t="s">
@@ -33027,19 +33065,19 @@
       <c r="B941" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="C941" s="31" t="n">
+      <c r="C941" s="26" t="n">
         <v>5209</v>
       </c>
-      <c r="D941" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E941" s="31" t="s">
+      <c r="D941" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E941" s="26" t="s">
         <v>1424</v>
       </c>
       <c r="F941" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G941" s="31" t="s">
+      <c r="G941" s="26" t="s">
         <v>1123</v>
       </c>
       <c r="H941" s="1" t="s">
@@ -33053,22 +33091,22 @@
       <c r="A942" s="22" t="s">
         <v>1417</v>
       </c>
-      <c r="B942" s="31" t="s">
+      <c r="B942" s="26" t="s">
         <v>1124</v>
       </c>
-      <c r="C942" s="31" t="n">
+      <c r="C942" s="26" t="n">
         <v>5210</v>
       </c>
-      <c r="D942" s="30" t="s">
+      <c r="D942" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E942" s="31" t="n">
+      <c r="E942" s="26" t="n">
         <v>10</v>
       </c>
       <c r="F942" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G942" s="31" t="s">
+      <c r="G942" s="26" t="s">
         <v>1125</v>
       </c>
       <c r="H942" s="1" t="s">
@@ -33082,22 +33120,22 @@
       <c r="A943" s="22" t="s">
         <v>1417</v>
       </c>
-      <c r="B943" s="31" t="s">
+      <c r="B943" s="26" t="s">
         <v>1426</v>
       </c>
-      <c r="C943" s="31" t="n">
+      <c r="C943" s="26" t="n">
         <v>5211</v>
       </c>
-      <c r="D943" s="30" t="s">
+      <c r="D943" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E943" s="31" t="n">
+      <c r="E943" s="26" t="n">
         <v>10</v>
       </c>
       <c r="F943" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G943" s="31" t="s">
+      <c r="G943" s="26" t="s">
         <v>1127</v>
       </c>
       <c r="H943" s="1" t="s">
@@ -33111,22 +33149,22 @@
       <c r="A944" s="22" t="s">
         <v>1417</v>
       </c>
-      <c r="B944" s="31" t="s">
+      <c r="B944" s="26" t="s">
         <v>1128</v>
       </c>
-      <c r="C944" s="31" t="n">
+      <c r="C944" s="26" t="n">
         <v>5212</v>
       </c>
-      <c r="D944" s="30" t="s">
+      <c r="D944" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E944" s="31" t="n">
+      <c r="E944" s="26" t="n">
         <v>10</v>
       </c>
       <c r="F944" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G944" s="31" t="s">
+      <c r="G944" s="26" t="s">
         <v>1129</v>
       </c>
       <c r="H944" s="1" t="s">
@@ -33140,22 +33178,22 @@
       <c r="A945" s="22" t="s">
         <v>1417</v>
       </c>
-      <c r="B945" s="31" t="s">
+      <c r="B945" s="26" t="s">
         <v>499</v>
       </c>
-      <c r="C945" s="31" t="n">
+      <c r="C945" s="26" t="n">
         <v>5213</v>
       </c>
-      <c r="D945" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E945" s="31" t="n">
+      <c r="D945" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E945" s="26" t="n">
         <v>100</v>
       </c>
       <c r="F945" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G945" s="31" t="s">
+      <c r="G945" s="26" t="s">
         <v>1131</v>
       </c>
       <c r="H945" s="1" t="s">
@@ -33172,19 +33210,19 @@
       <c r="B946" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="C946" s="31" t="n">
+      <c r="C946" s="26" t="n">
         <v>5214</v>
       </c>
-      <c r="D946" s="30" t="s">
+      <c r="D946" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E946" s="31" t="n">
+      <c r="E946" s="26" t="n">
         <v>1</v>
       </c>
       <c r="F946" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G946" s="31" t="s">
+      <c r="G946" s="26" t="s">
         <v>1137</v>
       </c>
       <c r="H946" s="1" t="s">
@@ -33198,22 +33236,22 @@
       <c r="A947" s="22" t="s">
         <v>1417</v>
       </c>
-      <c r="B947" s="31" t="s">
+      <c r="B947" s="26" t="s">
         <v>1423</v>
       </c>
-      <c r="C947" s="31" t="n">
+      <c r="C947" s="26" t="n">
         <v>5215</v>
       </c>
-      <c r="D947" s="30" t="s">
+      <c r="D947" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E947" s="31" t="n">
+      <c r="E947" s="26" t="n">
         <v>10</v>
       </c>
       <c r="F947" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G947" s="31" t="s">
+      <c r="G947" s="26" t="s">
         <v>1427</v>
       </c>
       <c r="H947" s="1" t="s">
@@ -33230,19 +33268,19 @@
       <c r="B948" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="C948" s="31" t="n">
+      <c r="C948" s="26" t="n">
         <v>5216</v>
       </c>
-      <c r="D948" s="30" t="s">
+      <c r="D948" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E948" s="31" t="n">
+      <c r="E948" s="26" t="n">
         <v>1</v>
       </c>
       <c r="F948" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G948" s="31" t="s">
+      <c r="G948" s="26" t="s">
         <v>1141</v>
       </c>
       <c r="H948" s="1" t="s">
@@ -33256,19 +33294,19 @@
       <c r="A949" s="22" t="s">
         <v>1417</v>
       </c>
-      <c r="B949" s="31" t="s">
+      <c r="B949" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="C949" s="31" t="n">
+      <c r="C949" s="26" t="n">
         <v>5217</v>
       </c>
-      <c r="D949" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E949" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G949" s="31" t="s">
+      <c r="D949" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E949" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G949" s="26" t="s">
         <v>117</v>
       </c>
       <c r="H949" s="1" t="s">
@@ -33282,16 +33320,16 @@
       <c r="B950" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="C950" s="31" t="n">
+      <c r="C950" s="26" t="n">
         <v>5218</v>
       </c>
-      <c r="D950" s="30" t="s">
+      <c r="D950" s="32" t="s">
         <v>1144</v>
       </c>
-      <c r="E950" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G950" s="31" t="s">
+      <c r="E950" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G950" s="26" t="s">
         <v>1146</v>
       </c>
       <c r="H950" s="1" t="s">
@@ -33308,16 +33346,16 @@
       <c r="B951" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="C951" s="31" t="n">
+      <c r="C951" s="26" t="n">
         <v>5234</v>
       </c>
-      <c r="D951" s="30" t="s">
+      <c r="D951" s="32" t="s">
         <v>1144</v>
       </c>
-      <c r="E951" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G951" s="31" t="s">
+      <c r="E951" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G951" s="26" t="s">
         <v>1149</v>
       </c>
       <c r="H951" s="1" t="s">
@@ -33331,16 +33369,16 @@
       <c r="B952" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="C952" s="31" t="n">
+      <c r="C952" s="26" t="n">
         <v>5250</v>
       </c>
-      <c r="D952" s="30" t="s">
+      <c r="D952" s="32" t="s">
         <v>1144</v>
       </c>
-      <c r="E952" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G952" s="31" t="s">
+      <c r="E952" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G952" s="26" t="s">
         <v>1151</v>
       </c>
       <c r="H952" s="1" t="s">
@@ -33354,16 +33392,16 @@
       <c r="B953" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="C953" s="31" t="n">
+      <c r="C953" s="26" t="n">
         <v>5266</v>
       </c>
-      <c r="D953" s="30" t="s">
+      <c r="D953" s="32" t="s">
         <v>1144</v>
       </c>
-      <c r="E953" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G953" s="31" t="s">
+      <c r="E953" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G953" s="26" t="s">
         <v>1153</v>
       </c>
       <c r="H953" s="1" t="s">
@@ -33377,16 +33415,16 @@
       <c r="B954" s="1" t="s">
         <v>1154</v>
       </c>
-      <c r="C954" s="31" t="n">
+      <c r="C954" s="26" t="n">
         <v>5282</v>
       </c>
-      <c r="D954" s="30" t="s">
+      <c r="D954" s="32" t="s">
         <v>1144</v>
       </c>
-      <c r="E954" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G954" s="31" t="s">
+      <c r="E954" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G954" s="26" t="s">
         <v>1155</v>
       </c>
       <c r="H954" s="1" t="s">
@@ -33400,16 +33438,16 @@
       <c r="B955" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="C955" s="31" t="n">
+      <c r="C955" s="26" t="n">
         <v>5298</v>
       </c>
-      <c r="D955" s="30" t="s">
+      <c r="D955" s="32" t="s">
         <v>1144</v>
       </c>
-      <c r="E955" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G955" s="31" t="s">
+      <c r="E955" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G955" s="26" t="s">
         <v>1157</v>
       </c>
       <c r="H955" s="1" t="s">
@@ -33423,16 +33461,16 @@
       <c r="B956" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="C956" s="31" t="n">
+      <c r="C956" s="26" t="n">
         <v>5314</v>
       </c>
-      <c r="D956" s="30" t="s">
+      <c r="D956" s="32" t="s">
         <v>1144</v>
       </c>
-      <c r="E956" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G956" s="31" t="s">
+      <c r="E956" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G956" s="26" t="s">
         <v>1159</v>
       </c>
       <c r="H956" s="1" t="s">
@@ -33446,16 +33484,16 @@
       <c r="B957" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="C957" s="31" t="n">
+      <c r="C957" s="26" t="n">
         <v>5330</v>
       </c>
-      <c r="D957" s="30" t="s">
+      <c r="D957" s="32" t="s">
         <v>1144</v>
       </c>
-      <c r="E957" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G957" s="31" t="s">
+      <c r="E957" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G957" s="26" t="s">
         <v>1161</v>
       </c>
       <c r="H957" s="1" t="s">
@@ -33469,12 +33507,12 @@
       <c r="B958" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C958" s="24" t="s">
+      <c r="C958" s="25" t="s">
         <v>1428</v>
       </c>
-      <c r="D958" s="30"/>
-      <c r="E958" s="31"/>
-      <c r="G958" s="31" t="s">
+      <c r="D958" s="32"/>
+      <c r="E958" s="26"/>
+      <c r="G958" s="26" t="s">
         <v>117</v>
       </c>
     </row>
@@ -33485,14 +33523,14 @@
       <c r="B959" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C959" s="31" t="n">
+      <c r="C959" s="26" t="n">
         <v>5350</v>
       </c>
-      <c r="D959" s="30" t="s">
+      <c r="D959" s="32" t="s">
         <v>493</v>
       </c>
-      <c r="E959" s="31"/>
-      <c r="G959" s="31" t="s">
+      <c r="E959" s="26"/>
+      <c r="G959" s="26" t="s">
         <v>494</v>
       </c>
       <c r="H959" s="1" t="s">
@@ -33503,13 +33541,13 @@
       <c r="A960" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B960" s="31" t="s">
+      <c r="B960" s="26" t="s">
         <v>1429</v>
       </c>
       <c r="C960" s="1" t="n">
         <v>5400</v>
       </c>
-      <c r="D960" s="30" t="s">
+      <c r="D960" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E960" s="1" t="n">
@@ -33538,7 +33576,7 @@
       <c r="C961" s="1" t="n">
         <v>5401</v>
       </c>
-      <c r="D961" s="30" t="s">
+      <c r="D961" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E961" s="1" t="n">
@@ -33567,7 +33605,7 @@
       <c r="C962" s="1" t="n">
         <v>5402</v>
       </c>
-      <c r="D962" s="30" t="s">
+      <c r="D962" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E962" s="1" t="n">
@@ -33590,13 +33628,13 @@
       <c r="A963" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B963" s="26" t="s">
+      <c r="B963" s="28" t="s">
         <v>1438</v>
       </c>
       <c r="C963" s="1" t="n">
         <v>5403</v>
       </c>
-      <c r="D963" s="30" t="s">
+      <c r="D963" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E963" s="1" t="n">
@@ -33622,7 +33660,7 @@
       <c r="C964" s="1" t="n">
         <v>5404</v>
       </c>
-      <c r="D964" s="30" t="s">
+      <c r="D964" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E964" s="1" t="n">
@@ -33651,7 +33689,7 @@
       <c r="C965" s="1" t="n">
         <v>5405</v>
       </c>
-      <c r="D965" s="30" t="s">
+      <c r="D965" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E965" s="1" t="n">
@@ -33680,7 +33718,7 @@
       <c r="C966" s="1" t="n">
         <v>5406</v>
       </c>
-      <c r="D966" s="30" t="s">
+      <c r="D966" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E966" s="1" t="n">
@@ -33709,7 +33747,7 @@
       <c r="C967" s="1" t="n">
         <v>5407</v>
       </c>
-      <c r="D967" s="30" t="s">
+      <c r="D967" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E967" s="1" t="n">
@@ -33738,7 +33776,7 @@
       <c r="C968" s="1" t="n">
         <v>5420</v>
       </c>
-      <c r="D968" s="30" t="s">
+      <c r="D968" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E968" s="1" t="n">
@@ -33767,7 +33805,7 @@
       <c r="C969" s="1" t="n">
         <v>5421</v>
       </c>
-      <c r="D969" s="30" t="s">
+      <c r="D969" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E969" s="1" t="n">
@@ -33796,7 +33834,7 @@
       <c r="C970" s="1" t="n">
         <v>5422</v>
       </c>
-      <c r="D970" s="30" t="s">
+      <c r="D970" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E970" s="1" t="n">
@@ -33825,7 +33863,7 @@
       <c r="C971" s="1" t="n">
         <v>5423</v>
       </c>
-      <c r="D971" s="30" t="s">
+      <c r="D971" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E971" s="1" t="n">
@@ -33854,7 +33892,7 @@
       <c r="C972" s="1" t="n">
         <v>5424</v>
       </c>
-      <c r="D972" s="30" t="s">
+      <c r="D972" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E972" s="1" t="n">
@@ -33883,7 +33921,7 @@
       <c r="C973" s="1" t="n">
         <v>5425</v>
       </c>
-      <c r="D973" s="30" t="s">
+      <c r="D973" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E973" s="1" t="n">
@@ -33912,7 +33950,7 @@
       <c r="C974" s="1" t="n">
         <v>5426</v>
       </c>
-      <c r="D974" s="30" t="s">
+      <c r="D974" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E974" s="1" t="n">
@@ -33941,7 +33979,7 @@
       <c r="C975" s="1" t="n">
         <v>5427</v>
       </c>
-      <c r="D975" s="30" t="s">
+      <c r="D975" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E975" s="1" t="n">
@@ -33996,7 +34034,7 @@
       <c r="C977" s="1" t="n">
         <v>5430</v>
       </c>
-      <c r="D977" s="30" t="s">
+      <c r="D977" s="32" t="s">
         <v>20</v>
       </c>
       <c r="E977" s="1" t="n">
@@ -34244,7 +34282,7 @@
       <c r="A987" s="1" t="s">
         <v>1485</v>
       </c>
-      <c r="B987" s="31" t="s">
+      <c r="B987" s="26" t="s">
         <v>1486</v>
       </c>
       <c r="C987" s="1" t="n">
@@ -34331,7 +34369,7 @@
       <c r="A990" s="1" t="s">
         <v>1485</v>
       </c>
-      <c r="B990" s="31" t="s">
+      <c r="B990" s="26" t="s">
         <v>117</v>
       </c>
       <c r="C990" s="23" t="s">
@@ -34342,7 +34380,7 @@
       <c r="A991" s="1" t="s">
         <v>1485</v>
       </c>
-      <c r="B991" s="31" t="s">
+      <c r="B991" s="26" t="s">
         <v>1486</v>
       </c>
       <c r="C991" s="1" t="n">
@@ -34429,7 +34467,7 @@
       <c r="A994" s="1" t="s">
         <v>1485</v>
       </c>
-      <c r="B994" s="31" t="s">
+      <c r="B994" s="26" t="s">
         <v>117</v>
       </c>
       <c r="C994" s="23" t="s">
@@ -34486,58 +34524,58 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>1500</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="34" t="s">
         <v>1501</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="34"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
     </row>
     <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="34" t="s">
         <v>1502</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="35" t="s">
         <v>1503</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="35" t="s">
         <v>1504</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="35" t="s">
         <v>1505</v>
       </c>
     </row>
@@ -34705,24 +34743,24 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="33" t="n">
+      <c r="A28" s="34" t="n">
         <v>223</v>
       </c>
-      <c r="B28" s="33" t="n">
+      <c r="B28" s="34" t="n">
         <v>277</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="34" t="s">
         <v>1507</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="33" t="n">
+      <c r="A29" s="34" t="n">
         <v>224</v>
       </c>
-      <c r="B29" s="33" t="n">
+      <c r="B29" s="34" t="n">
         <v>278</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="34" t="s">
         <v>1508</v>
       </c>
     </row>
@@ -34738,57 +34776,57 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="33" t="n">
+      <c r="A31" s="34" t="n">
         <v>226</v>
       </c>
-      <c r="B31" s="33" t="n">
+      <c r="B31" s="34" t="n">
         <v>279</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="34" t="s">
         <v>1510</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="33" t="n">
+      <c r="A32" s="34" t="n">
         <v>227</v>
       </c>
-      <c r="B32" s="33" t="n">
+      <c r="B32" s="34" t="n">
         <v>276</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="34" t="s">
         <v>1511</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="33" t="n">
+      <c r="A33" s="34" t="n">
         <v>228</v>
       </c>
-      <c r="B33" s="33" t="n">
+      <c r="B33" s="34" t="n">
         <v>275</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="34" t="s">
         <v>1512</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="33" t="n">
+      <c r="A34" s="34" t="n">
         <v>229</v>
       </c>
-      <c r="B34" s="33" t="n">
+      <c r="B34" s="34" t="n">
         <v>274</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="34" t="s">
         <v>1513</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="33" t="n">
+      <c r="A35" s="34" t="n">
         <v>230</v>
       </c>
-      <c r="B35" s="33" t="n">
+      <c r="B35" s="34" t="n">
         <v>273</v>
       </c>
-      <c r="C35" s="33" t="s">
+      <c r="C35" s="34" t="s">
         <v>1514</v>
       </c>
     </row>
@@ -34892,35 +34930,35 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="33" t="n">
+      <c r="A45" s="34" t="n">
         <v>242</v>
       </c>
-      <c r="B45" s="33" t="n">
+      <c r="B45" s="34" t="n">
         <v>261</v>
       </c>
-      <c r="C45" s="33" t="s">
+      <c r="C45" s="34" t="s">
         <v>1524</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="33" t="n">
+      <c r="A46" s="34" t="n">
         <v>243</v>
       </c>
-      <c r="B46" s="33" t="n">
+      <c r="B46" s="34" t="n">
         <v>260</v>
       </c>
-      <c r="C46" s="33" t="s">
+      <c r="C46" s="34" t="s">
         <v>1525</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="33" t="n">
+      <c r="A47" s="34" t="n">
         <v>244</v>
       </c>
-      <c r="B47" s="33" t="n">
+      <c r="B47" s="34" t="n">
         <v>259</v>
       </c>
-      <c r="C47" s="33"/>
+      <c r="C47" s="34"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="22" t="n">
@@ -34929,7 +34967,7 @@
       <c r="B48" s="22" t="n">
         <v>258</v>
       </c>
-      <c r="C48" s="33" t="s">
+      <c r="C48" s="34" t="s">
         <v>1526</v>
       </c>
     </row>
@@ -34986,7 +35024,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C178"/>
+  <dimension ref="A1:C179"/>
   <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="8.57"/>
@@ -35219,7 +35257,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="35" t="s">
+      <c r="C39" s="36" t="s">
         <v>1578</v>
       </c>
     </row>
@@ -36005,14 +36043,14 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="22" t="s">
+      <c r="B171" s="22" t="s">
         <v>1751</v>
       </c>
-      <c r="B171" s="22" t="s">
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="22" t="s">
         <v>1752</v>
       </c>
-    </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B172" s="22" t="s">
         <v>1753</v>
       </c>
@@ -36033,18 +36071,23 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="31" t="s">
+      <c r="B176" s="22" t="s">
         <v>1757</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="31" t="s">
+      <c r="B177" s="26" t="s">
         <v>1758</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="31" t="s">
+      <c r="B178" s="26" t="s">
         <v>1759</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B179" s="26" t="s">
+        <v>1760</v>
       </c>
     </row>
   </sheetData>
